--- a/irrbb_calc/output/eba_sot_results.xlsx
+++ b/irrbb_calc/output/eba_sot_results.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1410564079.41</v>
+        <v>-1341385513.46</v>
       </c>
       <c r="E2" t="n">
         <v>0.999906031812547</v>
@@ -495,10 +495,10 @@
         <v>1.270756758997571e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>-17924.83837909444</v>
+        <v>-17045.74707650722</v>
       </c>
       <c r="I2" t="n">
-        <v>-17924.83837909444</v>
+        <v>-17045.74707650722</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-210789268.91</v>
+        <v>-275079901.81</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983821828874917</v>
@@ -530,10 +530,10 @@
         <v>-0.001074720528931317</v>
       </c>
       <c r="H3" t="n">
-        <v>226539.5545760007</v>
+        <v>295634.0175716178</v>
       </c>
       <c r="I3" t="n">
-        <v>113269.7772880004</v>
+        <v>147817.0087858089</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-466347525.5</v>
+        <v>-460380476.87</v>
       </c>
       <c r="E4" t="n">
         <v>0.9936563817038003</v>
@@ -565,10 +565,10 @@
         <v>-0.004131807575030844</v>
       </c>
       <c r="H4" t="n">
-        <v>1926858.238457789</v>
+        <v>1902203.541727778</v>
       </c>
       <c r="I4" t="n">
-        <v>963429.1192288947</v>
+        <v>951101.770863889</v>
       </c>
     </row>
     <row r="5">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-928106565.37</v>
+        <v>-774901251.0700001</v>
       </c>
       <c r="E5" t="n">
         <v>0.9856536327098718</v>
@@ -600,10 +600,10 @@
         <v>-0.009198654711137122</v>
       </c>
       <c r="H5" t="n">
-        <v>8537331.829978043</v>
+        <v>7128049.043821106</v>
       </c>
       <c r="I5" t="n">
-        <v>4268665.914989022</v>
+        <v>3564024.521910553</v>
       </c>
     </row>
     <row r="6">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>325613046.1</v>
+        <v>14337145.59999999</v>
       </c>
       <c r="E6" t="n">
         <v>0.9761318955535195</v>
@@ -635,10 +635,10 @@
         <v>-0.01513456126685975</v>
       </c>
       <c r="H6" t="n">
-        <v>-4928010.595489277</v>
+        <v>-216986.4084750885</v>
       </c>
       <c r="I6" t="n">
-        <v>-4928010.595489277</v>
+        <v>-216986.4084750885</v>
       </c>
     </row>
     <row r="7">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>263741483.93</v>
+        <v>505596029.58</v>
       </c>
       <c r="E7" t="n">
         <v>0.9667342819189046</v>
@@ -670,10 +670,10 @@
         <v>-0.02091896253201642</v>
       </c>
       <c r="H7" t="n">
-        <v>-5517198.22047008</v>
+        <v>-10576544.39912028</v>
       </c>
       <c r="I7" t="n">
-        <v>-5517198.22047008</v>
+        <v>-10576544.39912028</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>589973763.67</v>
+        <v>526743176.9999999</v>
       </c>
       <c r="E8" t="n">
         <v>0.9524015829683793</v>
@@ -705,10 +705,10 @@
         <v>-0.02930239133147783</v>
       </c>
       <c r="H8" t="n">
-        <v>-17287642.09836316</v>
+        <v>-15434834.70363989</v>
       </c>
       <c r="I8" t="n">
-        <v>-17287642.09836316</v>
+        <v>-15434834.70363989</v>
       </c>
     </row>
     <row r="9">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>612295005.0700001</v>
+        <v>380413008.79</v>
       </c>
       <c r="E9" t="n">
         <v>0.9333610479054046</v>
@@ -740,10 +740,10 @@
         <v>-0.03995420556806362</v>
       </c>
       <c r="H9" t="n">
-        <v>-24463760.50086534</v>
+        <v>-15199099.55396125</v>
       </c>
       <c r="I9" t="n">
-        <v>-24463760.50086534</v>
+        <v>-15199099.55396125</v>
       </c>
     </row>
     <row r="10">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>773886472.84</v>
+        <v>963113319.4399999</v>
       </c>
       <c r="E10" t="n">
         <v>0.9066754799235061</v>
@@ -775,10 +775,10 @@
         <v>-0.05493320652757383</v>
       </c>
       <c r="H10" t="n">
-        <v>-42512065.44141538</v>
+        <v>-52906902.88625471</v>
       </c>
       <c r="I10" t="n">
-        <v>-42512065.44141538</v>
+        <v>-52906902.88625471</v>
       </c>
     </row>
     <row r="11">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>752632597.09</v>
+        <v>1410720811.72</v>
       </c>
       <c r="E11" t="n">
         <v>0.8730418834956067</v>
@@ -810,10 +810,10 @@
         <v>-0.07314463828611695</v>
       </c>
       <c r="H11" t="n">
-        <v>-55051039.07648885</v>
+        <v>-103186663.4959567</v>
       </c>
       <c r="I11" t="n">
-        <v>-55051039.07648885</v>
+        <v>-103186663.4959567</v>
       </c>
     </row>
     <row r="12">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1376408988.27</v>
+        <v>805426893.5699999</v>
       </c>
       <c r="E12" t="n">
         <v>0.839886760163754</v>
@@ -845,10 +845,10 @@
         <v>-0.0893662269184845</v>
       </c>
       <c r="H12" t="n">
-        <v>-123004477.9783785</v>
+        <v>-71977962.53702669</v>
       </c>
       <c r="I12" t="n">
-        <v>-123004477.9783785</v>
+        <v>-71977962.53702669</v>
       </c>
     </row>
     <row r="13">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>171337663.91</v>
+        <v>167532998.8</v>
       </c>
       <c r="E13" t="n">
         <v>0.8060794216350962</v>
@@ -880,10 +880,10 @@
         <v>-0.1035535335270944</v>
       </c>
       <c r="H13" t="n">
-        <v>-17742620.52415822</v>
+        <v>-17348634.00813047</v>
       </c>
       <c r="I13" t="n">
-        <v>-17742620.52415822</v>
+        <v>-17348634.00813047</v>
       </c>
     </row>
     <row r="14">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>304374885.85</v>
+        <v>301626600.17</v>
       </c>
       <c r="E14" t="n">
         <v>0.7725125366488534</v>
@@ -915,10 +915,10 @@
         <v>-0.1158645673464029</v>
       </c>
       <c r="H14" t="n">
-        <v>-35266264.46012104</v>
+        <v>-34947835.52886352</v>
       </c>
       <c r="I14" t="n">
-        <v>-35266264.46012104</v>
+        <v>-34947835.52886352</v>
       </c>
     </row>
     <row r="15">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>295856253.29</v>
+        <v>294575354.51</v>
       </c>
       <c r="E15" t="n">
         <v>0.7390723504327896</v>
@@ -950,10 +950,10 @@
         <v>-0.1263599384343468</v>
       </c>
       <c r="H15" t="n">
-        <v>-37384377.95114091</v>
+        <v>-37222523.66015948</v>
       </c>
       <c r="I15" t="n">
-        <v>-37384377.95114091</v>
+        <v>-37222523.66015948</v>
       </c>
     </row>
     <row r="16">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>240713355.56</v>
+        <v>241238577.56</v>
       </c>
       <c r="E16" t="n">
         <v>0.7058360643204235</v>
@@ -985,10 +985,10 @@
         <v>-0.135125484853127</v>
       </c>
       <c r="H16" t="n">
-        <v>-32526508.88066816</v>
+        <v>-32597479.75807369</v>
       </c>
       <c r="I16" t="n">
-        <v>-32526508.88066816</v>
+        <v>-32597479.75807369</v>
       </c>
     </row>
     <row r="17">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>150836878.06</v>
+        <v>151684434.17</v>
       </c>
       <c r="E17" t="n">
         <v>0.6740936305925465</v>
@@ -1020,10 +1020,10 @@
         <v>-0.142505629537688</v>
       </c>
       <c r="H17" t="n">
-        <v>-21495104.26543977</v>
+        <v>-21615885.78246384</v>
       </c>
       <c r="I17" t="n">
-        <v>-21495104.26543977</v>
+        <v>-21615885.78246384</v>
       </c>
     </row>
     <row r="18">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12616901.91</v>
+        <v>12178049.77</v>
       </c>
       <c r="E18" t="n">
         <v>0.5835756277426192</v>
@@ -1055,10 +1055,10 @@
         <v>-0.1566226182330579</v>
       </c>
       <c r="H18" t="n">
-        <v>-1976092.211133869</v>
+        <v>-1907358.039949888</v>
       </c>
       <c r="I18" t="n">
-        <v>-1976092.211133869</v>
+        <v>-1907358.039949888</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1410564079.41</v>
+        <v>-1341385513.46</v>
       </c>
       <c r="E19" t="n">
         <v>0.999906031812547</v>
@@ -1090,10 +1090,10 @@
         <v>8.119444430232381e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-114529.9665805139</v>
+        <v>-108913.051360572</v>
       </c>
       <c r="I19" t="n">
-        <v>-114529.9665805139</v>
+        <v>-108913.051360572</v>
       </c>
     </row>
     <row r="20">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-210789268.91</v>
+        <v>-275079901.81</v>
       </c>
       <c r="E20" t="n">
         <v>0.9983821828874917</v>
@@ -1125,10 +1125,10 @@
         <v>0.001073618328581993</v>
       </c>
       <c r="H20" t="n">
-        <v>-226307.2225701745</v>
+        <v>-295330.824407751</v>
       </c>
       <c r="I20" t="n">
-        <v>-226307.2225701745</v>
+        <v>-295330.824407751</v>
       </c>
     </row>
     <row r="21">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-466347525.5</v>
+        <v>-460380476.87</v>
       </c>
       <c r="E21" t="n">
         <v>0.9936563817038003</v>
@@ -1160,10 +1160,10 @@
         <v>0.004148675157226389</v>
       </c>
       <c r="H21" t="n">
-        <v>-1934724.39367585</v>
+        <v>-1909969.047262607</v>
       </c>
       <c r="I21" t="n">
-        <v>-1934724.39367585</v>
+        <v>-1909969.047262607</v>
       </c>
     </row>
     <row r="22">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-928106565.37</v>
+        <v>-774901251.0700001</v>
       </c>
       <c r="E22" t="n">
         <v>0.9856536327098718</v>
@@ -1195,10 +1195,10 @@
         <v>0.009282592027197278</v>
       </c>
       <c r="H22" t="n">
-        <v>-8615234.604093011</v>
+        <v>-7193092.175047579</v>
       </c>
       <c r="I22" t="n">
-        <v>-8615234.604093011</v>
+        <v>-7193092.175047579</v>
       </c>
     </row>
     <row r="23">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>325613046.1</v>
+        <v>14337145.59999999</v>
       </c>
       <c r="E23" t="n">
         <v>0.9761318955535195</v>
@@ -1230,10 +1230,10 @@
         <v>0.01537076312862229</v>
       </c>
       <c r="H23" t="n">
-        <v>5004921.003192269</v>
+        <v>220372.8689581691</v>
       </c>
       <c r="I23" t="n">
-        <v>2502460.501596135</v>
+        <v>110186.4344790845</v>
       </c>
     </row>
     <row r="24">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>263741483.93</v>
+        <v>505596029.58</v>
       </c>
       <c r="E24" t="n">
         <v>0.9667342819189046</v>
@@ -1265,10 +1265,10 @@
         <v>0.02137897737503558</v>
       </c>
       <c r="H24" t="n">
-        <v>5638523.21779778</v>
+        <v>10809126.07729864</v>
       </c>
       <c r="I24" t="n">
-        <v>2819261.60889889</v>
+        <v>5404563.03864932</v>
       </c>
     </row>
     <row r="25">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>589973763.67</v>
+        <v>526743176.9999999</v>
       </c>
       <c r="E25" t="n">
         <v>0.9524015829683793</v>
@@ -1300,10 +1300,10 @@
         <v>0.03023239035728253</v>
       </c>
       <c r="H25" t="n">
-        <v>17836317.12382659</v>
+        <v>15924705.34509917</v>
       </c>
       <c r="I25" t="n">
-        <v>8918158.561913297</v>
+        <v>7962352.672549583</v>
       </c>
     </row>
     <row r="26">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>612295005.0700001</v>
+        <v>380413008.79</v>
       </c>
       <c r="E26" t="n">
         <v>0.9333610479054046</v>
@@ -1335,10 +1335,10 @@
         <v>0.04174093883572272</v>
       </c>
       <c r="H26" t="n">
-        <v>25557768.3560454</v>
+        <v>15878796.13221664</v>
       </c>
       <c r="I26" t="n">
-        <v>12778884.1780227</v>
+        <v>7939398.06610832</v>
       </c>
     </row>
     <row r="27">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>773886472.84</v>
+        <v>963113319.4399999</v>
       </c>
       <c r="E27" t="n">
         <v>0.9066754799235061</v>
@@ -1370,10 +1370,10 @@
         <v>0.05847495853512397</v>
       </c>
       <c r="H27" t="n">
-        <v>45252979.41021234</v>
+        <v>56318011.4188796</v>
       </c>
       <c r="I27" t="n">
-        <v>22626489.70510617</v>
+        <v>28159005.7094398</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>752632597.09</v>
+        <v>1410720811.72</v>
       </c>
       <c r="E28" t="n">
         <v>0.8730418834956067</v>
@@ -1405,10 +1405,10 @@
         <v>0.07983268361646123</v>
       </c>
       <c r="H28" t="n">
-        <v>60084680.00292151</v>
+        <v>112621628.2332001</v>
       </c>
       <c r="I28" t="n">
-        <v>30042340.00146076</v>
+        <v>56310814.11660007</v>
       </c>
     </row>
     <row r="29">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1376408988.27</v>
+        <v>805426893.5699999</v>
       </c>
       <c r="E29" t="n">
         <v>0.839886760163754</v>
@@ -1440,10 +1440,10 @@
         <v>0.1000071588498553</v>
       </c>
       <c r="H29" t="n">
-        <v>137650752.3322866</v>
+        <v>80548455.28720051</v>
       </c>
       <c r="I29" t="n">
-        <v>68825376.16614328</v>
+        <v>40274227.64360026</v>
       </c>
     </row>
     <row r="30">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>171337663.91</v>
+        <v>167532998.8</v>
       </c>
       <c r="E30" t="n">
         <v>0.8060794216350962</v>
@@ -1475,10 +1475,10 @@
         <v>0.1188174585554111</v>
       </c>
       <c r="H30" t="n">
-        <v>20357905.78060739</v>
+        <v>19905845.14158275</v>
       </c>
       <c r="I30" t="n">
-        <v>10178952.89030369</v>
+        <v>9952922.570791373</v>
       </c>
     </row>
     <row r="31">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>304374885.85</v>
+        <v>301626600.17</v>
       </c>
       <c r="E31" t="n">
         <v>0.7725125366488534</v>
@@ -1510,10 +1510,10 @@
         <v>0.1363083780988569</v>
       </c>
       <c r="H31" t="n">
-        <v>41488847.02423821</v>
+        <v>41114232.66064509</v>
       </c>
       <c r="I31" t="n">
-        <v>20744423.5121191</v>
+        <v>20557116.33032255</v>
       </c>
     </row>
     <row r="32">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>295856253.29</v>
+        <v>294575354.51</v>
       </c>
       <c r="E32" t="n">
         <v>0.7390723504327896</v>
@@ -1545,10 +1545,10 @@
         <v>0.1524189448946068</v>
       </c>
       <c r="H32" t="n">
-        <v>45094097.96693335</v>
+        <v>44898864.72636896</v>
       </c>
       <c r="I32" t="n">
-        <v>22547048.98346668</v>
+        <v>22449432.36318448</v>
       </c>
     </row>
     <row r="33">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>240713355.56</v>
+        <v>241238577.56</v>
       </c>
       <c r="E33" t="n">
         <v>0.7058360643204235</v>
@@ -1580,10 +1580,10 @@
         <v>0.1671173700222426</v>
       </c>
       <c r="H33" t="n">
-        <v>40227382.91041616</v>
+        <v>40315156.62973399</v>
       </c>
       <c r="I33" t="n">
-        <v>20113691.45520808</v>
+        <v>20157578.31486699</v>
       </c>
     </row>
     <row r="34">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>150836878.06</v>
+        <v>151684434.17</v>
       </c>
       <c r="E34" t="n">
         <v>0.6740936305925465</v>
@@ -1615,10 +1615,10 @@
         <v>0.1807074230390667</v>
       </c>
       <c r="H34" t="n">
-        <v>27257343.53348054</v>
+        <v>27410503.21399966</v>
       </c>
       <c r="I34" t="n">
-        <v>13628671.76674027</v>
+        <v>13705251.60699983</v>
       </c>
     </row>
     <row r="35">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12616901.91</v>
+        <v>12178049.77</v>
       </c>
       <c r="E35" t="n">
         <v>0.5835756277426192</v>
@@ -1650,10 +1650,10 @@
         <v>0.2140775985160066</v>
       </c>
       <c r="H35" t="n">
-        <v>2700996.061604817</v>
+        <v>2607047.649370006</v>
       </c>
       <c r="I35" t="n">
-        <v>1350498.030802408</v>
+        <v>1303523.824685003</v>
       </c>
     </row>
     <row r="36">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-1410564079.41</v>
+        <v>-1341385513.46</v>
       </c>
       <c r="E36" t="n">
         <v>0.999906031812547</v>
@@ -1685,10 +1685,10 @@
         <v>7.797724224745117e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>-109991.8969257065</v>
+        <v>-104597.5431302921</v>
       </c>
       <c r="I36" t="n">
-        <v>-109991.8969257065</v>
+        <v>-104597.5431302921</v>
       </c>
     </row>
     <row r="37">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-210789268.91</v>
+        <v>-275079901.81</v>
       </c>
       <c r="E37" t="n">
         <v>0.9983821828874917</v>
@@ -1720,10 +1720,10 @@
         <v>0.000857634379940464</v>
       </c>
       <c r="H37" t="n">
-        <v>-180780.1239397316</v>
+        <v>-235917.9810229031</v>
       </c>
       <c r="I37" t="n">
-        <v>-180780.1239397316</v>
+        <v>-235917.9810229031</v>
       </c>
     </row>
     <row r="38">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-466347525.5</v>
+        <v>-460380476.87</v>
       </c>
       <c r="E38" t="n">
         <v>0.9936563817038003</v>
@@ -1755,10 +1755,10 @@
         <v>0.002842264830571484</v>
       </c>
       <c r="H38" t="n">
-        <v>-1325483.170552688</v>
+        <v>-1308523.238089329</v>
       </c>
       <c r="I38" t="n">
-        <v>-1325483.170552688</v>
+        <v>-1308523.238089329</v>
       </c>
     </row>
     <row r="39">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-928106565.37</v>
+        <v>-774901251.0700001</v>
       </c>
       <c r="E39" t="n">
         <v>0.9856536327098718</v>
@@ -1790,10 +1790,10 @@
         <v>0.004190624857375314</v>
       </c>
       <c r="H39" t="n">
-        <v>-3889346.443132748</v>
+        <v>-3247320.444745171</v>
       </c>
       <c r="I39" t="n">
-        <v>-3889346.443132748</v>
+        <v>-3247320.444745171</v>
       </c>
     </row>
     <row r="40">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>325613046.1</v>
+        <v>14337145.59999999</v>
       </c>
       <c r="E40" t="n">
         <v>0.9761318955535195</v>
@@ -1825,10 +1825,10 @@
         <v>0.003588231255082563</v>
       </c>
       <c r="H40" t="n">
-        <v>1168374.909078659</v>
+        <v>51444.99395058941</v>
       </c>
       <c r="I40" t="n">
-        <v>584187.4545393297</v>
+        <v>25722.4969752947</v>
       </c>
     </row>
     <row r="41">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>263741483.93</v>
+        <v>505596029.58</v>
       </c>
       <c r="E41" t="n">
         <v>0.9667342819189046</v>
@@ -1860,10 +1860,10 @@
         <v>0.001347768023809648</v>
       </c>
       <c r="H41" t="n">
-        <v>355462.3385929601</v>
+        <v>681426.1616330409</v>
       </c>
       <c r="I41" t="n">
-        <v>177731.16929648</v>
+        <v>340713.0808165204</v>
       </c>
     </row>
     <row r="42">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>589973763.67</v>
+        <v>526743176.9999999</v>
       </c>
       <c r="E42" t="n">
         <v>0.9524015829683793</v>
@@ -1895,10 +1895,10 @@
         <v>-0.003700723745374557</v>
       </c>
       <c r="H42" t="n">
-        <v>-2183329.916361566</v>
+        <v>-1949330.982837933</v>
       </c>
       <c r="I42" t="n">
-        <v>-2183329.916361566</v>
+        <v>-1949330.982837933</v>
       </c>
     </row>
     <row r="43">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>612295005.0700001</v>
+        <v>380413008.79</v>
       </c>
       <c r="E43" t="n">
         <v>0.9333610479054046</v>
@@ -1930,10 +1930,10 @@
         <v>-0.01168774742577749</v>
       </c>
       <c r="H43" t="n">
-        <v>-7156349.369323311</v>
+        <v>-4446171.164217594</v>
       </c>
       <c r="I43" t="n">
-        <v>-7156349.369323311</v>
+        <v>-4446171.164217594</v>
       </c>
     </row>
     <row r="44">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>773886472.84</v>
+        <v>963113319.4399999</v>
       </c>
       <c r="E44" t="n">
         <v>0.9066754799235061</v>
@@ -1965,10 +1965,10 @@
         <v>-0.02354447052112385</v>
       </c>
       <c r="H44" t="n">
-        <v>-18220747.24647789</v>
+        <v>-22675993.15805682</v>
       </c>
       <c r="I44" t="n">
-        <v>-18220747.24647789</v>
+        <v>-22675993.15805682</v>
       </c>
     </row>
     <row r="45">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>752632597.09</v>
+        <v>1410720811.72</v>
       </c>
       <c r="E45" t="n">
         <v>0.8730418834956067</v>
@@ -2000,10 +2000,10 @@
         <v>-0.03709517753986769</v>
       </c>
       <c r="H45" t="n">
-        <v>-27919039.81134525</v>
+        <v>-52330938.96993966</v>
       </c>
       <c r="I45" t="n">
-        <v>-27919039.81134525</v>
+        <v>-52330938.96993966</v>
       </c>
     </row>
     <row r="46">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1376408988.27</v>
+        <v>805426893.5699999</v>
       </c>
       <c r="E46" t="n">
         <v>0.839886760163754</v>
@@ -2035,10 +2035,10 @@
         <v>-0.04807062925974992</v>
       </c>
       <c r="H46" t="n">
-        <v>-66164846.18491465</v>
+        <v>-38717377.59663552</v>
       </c>
       <c r="I46" t="n">
-        <v>-66164846.18491465</v>
+        <v>-38717377.59663552</v>
       </c>
     </row>
     <row r="47">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>171337663.91</v>
+        <v>167532998.8</v>
       </c>
       <c r="E47" t="n">
         <v>0.8060794216350962</v>
@@ -2070,10 +2070,10 @@
         <v>-0.05707337113962196</v>
       </c>
       <c r="H47" t="n">
-        <v>-9778818.082531242</v>
+        <v>-9561673.018646242</v>
       </c>
       <c r="I47" t="n">
-        <v>-9778818.082531242</v>
+        <v>-9561673.018646242</v>
       </c>
     </row>
     <row r="48">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>304374885.85</v>
+        <v>301626600.17</v>
       </c>
       <c r="E48" t="n">
         <v>0.7725125366488534</v>
@@ -2105,10 +2105,10 @@
         <v>-0.06464828621749663</v>
       </c>
       <c r="H48" t="n">
-        <v>-19677314.73784867</v>
+        <v>-19499642.77860058</v>
       </c>
       <c r="I48" t="n">
-        <v>-19677314.73784867</v>
+        <v>-19499642.77860058</v>
       </c>
     </row>
     <row r="49">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>295856253.29</v>
+        <v>294575354.51</v>
       </c>
       <c r="E49" t="n">
         <v>0.7390723504327896</v>
@@ -2140,10 +2140,10 @@
         <v>-0.07106709005817402</v>
       </c>
       <c r="H49" t="n">
-        <v>-21025642.99683437</v>
+        <v>-20934613.24788071</v>
       </c>
       <c r="I49" t="n">
-        <v>-21025642.99683437</v>
+        <v>-20934613.24788071</v>
       </c>
     </row>
     <row r="50">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>240713355.56</v>
+        <v>241238577.56</v>
       </c>
       <c r="E50" t="n">
         <v>0.7058360643204235</v>
@@ -2175,10 +2175,10 @@
         <v>-0.07648141160373034</v>
       </c>
       <c r="H50" t="n">
-        <v>-18410097.22509945</v>
+        <v>-18450266.94506479</v>
       </c>
       <c r="I50" t="n">
-        <v>-18410097.22509945</v>
+        <v>-18450266.94506479</v>
       </c>
     </row>
     <row r="51">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>150836878.06</v>
+        <v>151684434.17</v>
       </c>
       <c r="E51" t="n">
         <v>0.6740936305925465</v>
@@ -2210,10 +2210,10 @@
         <v>-0.08112320091848635</v>
       </c>
       <c r="H51" t="n">
-        <v>-12236370.36477861</v>
+        <v>-12305126.82937982</v>
       </c>
       <c r="I51" t="n">
-        <v>-12236370.36477861</v>
+        <v>-12305126.82937982</v>
       </c>
     </row>
     <row r="52">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12616901.91</v>
+        <v>12178049.77</v>
       </c>
       <c r="E52" t="n">
         <v>0.5835756277426192</v>
@@ -2245,10 +2245,10 @@
         <v>-0.09061680299551267</v>
       </c>
       <c r="H52" t="n">
-        <v>-1143303.314792177</v>
+        <v>-1103535.936877638</v>
       </c>
       <c r="I52" t="n">
-        <v>-1143303.314792177</v>
+        <v>-1103535.936877638</v>
       </c>
     </row>
     <row r="53">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1410564079.41</v>
+        <v>-1341385513.46</v>
       </c>
       <c r="E53" t="n">
         <v>0.999906031812547</v>
@@ -2280,10 +2280,10 @@
         <v>8.749858685930256e-06</v>
       </c>
       <c r="H53" t="n">
-        <v>-12342.23636228681</v>
+        <v>-11736.933686129</v>
       </c>
       <c r="I53" t="n">
-        <v>-12342.23636228681</v>
+        <v>-11736.933686129</v>
       </c>
     </row>
     <row r="54">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-210789268.91</v>
+        <v>-275079901.81</v>
       </c>
       <c r="E54" t="n">
         <v>0.9983821828874917</v>
@@ -2315,10 +2315,10 @@
         <v>-0.00107465764159409</v>
       </c>
       <c r="H54" t="n">
-        <v>226526.298600163</v>
+        <v>295616.7185290685</v>
       </c>
       <c r="I54" t="n">
-        <v>113263.1493000815</v>
+        <v>147808.3592645342</v>
       </c>
     </row>
     <row r="55">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-466347525.5</v>
+        <v>-460380476.87</v>
       </c>
       <c r="E55" t="n">
         <v>0.9936563817038003</v>
@@ -2350,10 +2350,10 @@
         <v>-0.003624512892459575</v>
       </c>
       <c r="H55" t="n">
-        <v>1690282.61854137</v>
+        <v>1668654.973852002</v>
       </c>
       <c r="I55" t="n">
-        <v>845141.3092706852</v>
+        <v>834327.486926001</v>
       </c>
     </row>
     <row r="56">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-928106565.37</v>
+        <v>-774901251.0700001</v>
       </c>
       <c r="E56" t="n">
         <v>0.9856536327098718</v>
@@ -2385,10 +2385,10 @@
         <v>-0.00575832701755552</v>
       </c>
       <c r="H56" t="n">
-        <v>5344341.11054073</v>
+        <v>4462134.809973955</v>
       </c>
       <c r="I56" t="n">
-        <v>2672170.555270365</v>
+        <v>2231067.404986978</v>
       </c>
     </row>
     <row r="57">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>325613046.1</v>
+        <v>14337145.59999999</v>
       </c>
       <c r="E57" t="n">
         <v>0.9761318955535195</v>
@@ -2420,10 +2420,10 @@
         <v>-0.005916553585663675</v>
       </c>
       <c r="H57" t="n">
-        <v>-1926507.035441826</v>
+        <v>-84826.49020786211</v>
       </c>
       <c r="I57" t="n">
-        <v>-1926507.035441826</v>
+        <v>-84826.49020786211</v>
       </c>
     </row>
     <row r="58">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>263741483.93</v>
+        <v>505596029.58</v>
       </c>
       <c r="E58" t="n">
         <v>0.9667342819189046</v>
@@ -2455,10 +2455,10 @@
         <v>-0.004299740059850787</v>
       </c>
       <c r="H58" t="n">
-        <v>-1134019.823898314</v>
+        <v>-2173931.502486629</v>
       </c>
       <c r="I58" t="n">
-        <v>-1134019.823898314</v>
+        <v>-2173931.502486629</v>
       </c>
     </row>
     <row r="59">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>589973763.67</v>
+        <v>526743176.9999999</v>
       </c>
       <c r="E59" t="n">
         <v>0.9524015829683793</v>
@@ -2490,10 +2490,10 @@
         <v>5.935525280276188e-06</v>
       </c>
       <c r="H59" t="n">
-        <v>3501.804188962974</v>
+        <v>3126.497443296495</v>
       </c>
       <c r="I59" t="n">
-        <v>1750.902094481487</v>
+        <v>1563.248721648247</v>
       </c>
     </row>
     <row r="60">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>612295005.0700001</v>
+        <v>380413008.79</v>
       </c>
       <c r="E60" t="n">
         <v>0.9333610479054046</v>
@@ -2525,10 +2525,10 @@
         <v>0.007262963541339373</v>
       </c>
       <c r="H60" t="n">
-        <v>4447076.298367617</v>
+        <v>2762925.813492985</v>
       </c>
       <c r="I60" t="n">
-        <v>2223538.149183808</v>
+        <v>1381462.906746492</v>
       </c>
     </row>
     <row r="61">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>773886472.84</v>
+        <v>963113319.4399999</v>
       </c>
       <c r="E61" t="n">
         <v>0.9066754799235061</v>
@@ -2560,10 +2560,10 @@
         <v>0.01838001221226671</v>
       </c>
       <c r="H61" t="n">
-        <v>14224042.82170721</v>
+        <v>17702034.57310392</v>
       </c>
       <c r="I61" t="n">
-        <v>7112021.410853603</v>
+        <v>8851017.286551962</v>
       </c>
     </row>
     <row r="62">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>752632597.09</v>
+        <v>1410720811.72</v>
       </c>
       <c r="E62" t="n">
         <v>0.8730418834956067</v>
@@ -2595,10 +2595,10 @@
         <v>0.03130191235040702</v>
       </c>
       <c r="H62" t="n">
-        <v>23558839.58617039</v>
+        <v>44158259.19935449</v>
       </c>
       <c r="I62" t="n">
-        <v>11779419.79308519</v>
+        <v>22079129.59967725</v>
       </c>
     </row>
     <row r="63">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1376408988.27</v>
+        <v>805426893.5699999</v>
       </c>
       <c r="E63" t="n">
         <v>0.839886760163754</v>
@@ -2630,10 +2630,10 @@
         <v>0.04188199495808165</v>
       </c>
       <c r="H63" t="n">
-        <v>57646754.3069824</v>
+        <v>33732885.0956021</v>
       </c>
       <c r="I63" t="n">
-        <v>28823377.1534912</v>
+        <v>16866442.54780105</v>
       </c>
     </row>
     <row r="64">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>171337663.91</v>
+        <v>167532998.8</v>
       </c>
       <c r="E64" t="n">
         <v>0.8060794216350962</v>
@@ -2665,10 +2665,10 @@
         <v>0.05069529339115386</v>
       </c>
       <c r="H64" t="n">
-        <v>8686013.140872365</v>
+        <v>8493134.526865829</v>
       </c>
       <c r="I64" t="n">
-        <v>4343006.570436182</v>
+        <v>4246567.263432914</v>
       </c>
     </row>
     <row r="65">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>304374885.85</v>
+        <v>301626600.17</v>
       </c>
       <c r="E65" t="n">
         <v>0.7725125366488534</v>
@@ -2700,10 +2700,10 @@
         <v>0.05828777906690807</v>
       </c>
       <c r="H65" t="n">
-        <v>17741336.09994017</v>
+        <v>17581144.63141158</v>
       </c>
       <c r="I65" t="n">
-        <v>8870668.049970083</v>
+        <v>8790572.315705789</v>
       </c>
     </row>
     <row r="66">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>295856253.29</v>
+        <v>294575354.51</v>
       </c>
       <c r="E66" t="n">
         <v>0.7390723504327896</v>
@@ -2735,10 +2735,10 @@
         <v>0.06493454530509235</v>
       </c>
       <c r="H66" t="n">
-        <v>19211291.28305439</v>
+        <v>19128116.70319324</v>
       </c>
       <c r="I66" t="n">
-        <v>9605645.641527193</v>
+        <v>9564058.351596618</v>
       </c>
     </row>
     <row r="67">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>240713355.56</v>
+        <v>241238577.56</v>
       </c>
       <c r="E67" t="n">
         <v>0.7058360643204235</v>
@@ -2770,10 +2770,10 @@
         <v>0.0707747284866409</v>
       </c>
       <c r="H67" t="n">
-        <v>17036422.38286725</v>
+        <v>17073594.82731246</v>
       </c>
       <c r="I67" t="n">
-        <v>8518211.191433627</v>
+        <v>8536797.413656231</v>
       </c>
     </row>
     <row r="68">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>150836878.06</v>
+        <v>151684434.17</v>
       </c>
       <c r="E68" t="n">
         <v>0.6740936305925465</v>
@@ -2805,10 +2805,10 @@
         <v>0.07601335275394061</v>
       </c>
       <c r="H68" t="n">
-        <v>11465616.82027791</v>
+        <v>11530042.40184609</v>
       </c>
       <c r="I68" t="n">
-        <v>5732808.410138953</v>
+        <v>5765021.200923046</v>
       </c>
     </row>
     <row r="69">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12616901.91</v>
+        <v>12178049.77</v>
       </c>
       <c r="E69" t="n">
         <v>0.5835756277426192</v>
@@ -2840,10 +2840,10 @@
         <v>0.08811450570325163</v>
       </c>
       <c r="H69" t="n">
-        <v>1111732.075306061</v>
+        <v>1073062.835913147</v>
       </c>
       <c r="I69" t="n">
-        <v>555866.0376530307</v>
+        <v>536531.4179565737</v>
       </c>
     </row>
     <row r="70">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-1410564079.41</v>
+        <v>-1341385513.46</v>
       </c>
       <c r="E70" t="n">
         <v>0.999906031812547</v>
@@ -2875,10 +2875,10 @@
         <v>-8.56716656616463e-07</v>
       </c>
       <c r="H70" t="n">
-        <v>1208.453742055414</v>
+        <v>1149.187312325209</v>
       </c>
       <c r="I70" t="n">
-        <v>604.2268710277071</v>
+        <v>574.5936561626044</v>
       </c>
     </row>
     <row r="71">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-210789268.91</v>
+        <v>-275079901.81</v>
       </c>
       <c r="E71" t="n">
         <v>0.9983821828874917</v>
@@ -2910,10 +2910,10 @@
         <v>-0.001389003495161578</v>
       </c>
       <c r="H71" t="n">
-        <v>292787.0312585438</v>
+        <v>382086.9450627937</v>
       </c>
       <c r="I71" t="n">
-        <v>146393.5156292719</v>
+        <v>191043.4725313969</v>
       </c>
     </row>
     <row r="72">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-466347525.5</v>
+        <v>-460380476.87</v>
       </c>
       <c r="E72" t="n">
         <v>0.9936563817038003</v>
@@ -2945,10 +2945,10 @@
         <v>-0.004887294219023786</v>
       </c>
       <c r="H72" t="n">
-        <v>2279177.565432197</v>
+        <v>2250014.843158165</v>
       </c>
       <c r="I72" t="n">
-        <v>1139588.782716099</v>
+        <v>1125007.421579082</v>
       </c>
     </row>
     <row r="73">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-928106565.37</v>
+        <v>-774901251.0700001</v>
       </c>
       <c r="E73" t="n">
         <v>0.9856536327098718</v>
@@ -2980,10 +2980,10 @@
         <v>-0.008818310314522182</v>
       </c>
       <c r="H73" t="n">
-        <v>8184331.698378026</v>
+        <v>6833319.695046725</v>
       </c>
       <c r="I73" t="n">
-        <v>4092165.849189013</v>
+        <v>3416659.847523362</v>
       </c>
     </row>
     <row r="74">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>325613046.1</v>
+        <v>14337145.59999999</v>
       </c>
       <c r="E74" t="n">
         <v>0.9761318955535195</v>
@@ -3015,10 +3015,10 @@
         <v>-0.01134588039219331</v>
       </c>
       <c r="H74" t="n">
-        <v>-3694366.675188325</v>
+        <v>-162667.5391430604</v>
       </c>
       <c r="I74" t="n">
-        <v>-3694366.675188325</v>
+        <v>-162667.5391430604</v>
       </c>
     </row>
     <row r="75">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>263741483.93</v>
+        <v>505596029.58</v>
       </c>
       <c r="E75" t="n">
         <v>0.9667342819189046</v>
@@ -3050,10 +3050,10 @@
         <v>-0.01225043827690986</v>
       </c>
       <c r="H75" t="n">
-        <v>-3230948.769945079</v>
+        <v>-6193772.953420481</v>
       </c>
       <c r="I75" t="n">
-        <v>-3230948.769945079</v>
+        <v>-6193772.953420481</v>
       </c>
     </row>
     <row r="76">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>589973763.67</v>
+        <v>526743176.9999999</v>
       </c>
       <c r="E76" t="n">
         <v>0.9524015829683793</v>
@@ -3085,10 +3085,10 @@
         <v>-0.01186315201310806</v>
       </c>
       <c r="H76" t="n">
-        <v>-6998948.442162698</v>
+        <v>-6248834.380618484</v>
       </c>
       <c r="I76" t="n">
-        <v>-6998948.442162698</v>
+        <v>-6248834.380618484</v>
       </c>
     </row>
     <row r="77">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>612295005.0700001</v>
+        <v>380413008.79</v>
       </c>
       <c r="E77" t="n">
         <v>0.9333610479054046</v>
@@ -3120,10 +3120,10 @@
         <v>-0.009881694503488636</v>
       </c>
       <c r="H77" t="n">
-        <v>-6050512.186113766</v>
+        <v>-3759125.138015717</v>
       </c>
       <c r="I77" t="n">
-        <v>-6050512.186113766</v>
+        <v>-3759125.138015717</v>
       </c>
     </row>
     <row r="78">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>773886472.84</v>
+        <v>963113319.4399999</v>
       </c>
       <c r="E78" t="n">
         <v>0.9066754799235061</v>
@@ -3155,10 +3155,10 @@
         <v>-0.006489882432710758</v>
       </c>
       <c r="H78" t="n">
-        <v>-5022432.224996808</v>
+        <v>-6250492.212543401</v>
       </c>
       <c r="I78" t="n">
-        <v>-5022432.224996808</v>
+        <v>-6250492.212543401</v>
       </c>
     </row>
     <row r="79">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>752632597.09</v>
+        <v>1410720811.72</v>
       </c>
       <c r="E79" t="n">
         <v>0.8730418834956067</v>
@@ -3190,10 +3190,10 @@
         <v>-0.003224039784762822</v>
       </c>
       <c r="H79" t="n">
-        <v>-2426517.436327528</v>
+        <v>-4548220.022178182</v>
       </c>
       <c r="I79" t="n">
-        <v>-2426517.436327528</v>
+        <v>-4548220.022178182</v>
       </c>
     </row>
     <row r="80">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1376408988.27</v>
+        <v>805426893.5699999</v>
       </c>
       <c r="E80" t="n">
         <v>0.839886760163754</v>
@@ -3225,10 +3225,10 @@
         <v>-0.001468318235875343</v>
       </c>
       <c r="H80" t="n">
-        <v>-2021006.417499573</v>
+        <v>-1182622.99549326</v>
       </c>
       <c r="I80" t="n">
-        <v>-2021006.417499573</v>
+        <v>-1182622.99549326</v>
       </c>
     </row>
     <row r="81">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>171337663.91</v>
+        <v>167532998.8</v>
       </c>
       <c r="E81" t="n">
         <v>0.8060794216350962</v>
@@ -3260,10 +3260,10 @@
         <v>-0.000633919618590939</v>
       </c>
       <c r="H81" t="n">
-        <v>-108614.3065560897</v>
+        <v>-106202.4547006923</v>
       </c>
       <c r="I81" t="n">
-        <v>-108614.3065560897</v>
+        <v>-106202.4547006923</v>
       </c>
     </row>
     <row r="82">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>304374885.85</v>
+        <v>301626600.17</v>
       </c>
       <c r="E82" t="n">
         <v>0.7725125366488534</v>
@@ -3295,10 +3295,10 @@
         <v>-0.0002643337202767881</v>
       </c>
       <c r="H82" t="n">
-        <v>-80456.54593555322</v>
+        <v>-79730.0813573754</v>
       </c>
       <c r="I82" t="n">
-        <v>-80456.54593555322</v>
+        <v>-79730.0813573754</v>
       </c>
     </row>
     <row r="83">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>295856253.29</v>
+        <v>294575354.51</v>
       </c>
       <c r="E83" t="n">
         <v>0.7390723504327896</v>
@@ -3330,10 +3330,10 @@
         <v>-0.0001074027017012869</v>
       </c>
       <c r="H83" t="n">
-        <v>-31775.76091856624</v>
+        <v>-31638.18892898835</v>
       </c>
       <c r="I83" t="n">
-        <v>-31775.76091856624</v>
+        <v>-31638.18892898835</v>
       </c>
     </row>
     <row r="84">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>240713355.56</v>
+        <v>241238577.56</v>
       </c>
       <c r="E84" t="n">
         <v>0.7058360643204235</v>
@@ -3365,10 +3365,10 @@
         <v>-4.329964913651896e-05</v>
       </c>
       <c r="H84" t="n">
-        <v>-10422.80383822213</v>
+        <v>-10445.54576654092</v>
       </c>
       <c r="I84" t="n">
-        <v>-10422.80383822213</v>
+        <v>-10445.54576654092</v>
       </c>
     </row>
     <row r="85">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>150836878.06</v>
+        <v>151684434.17</v>
       </c>
       <c r="E85" t="n">
         <v>0.6740936305925465</v>
@@ -3400,10 +3400,10 @@
         <v>-1.696070784418247e-05</v>
       </c>
       <c r="H85" t="n">
-        <v>-2558.300220904236</v>
+        <v>-2572.675372467498</v>
       </c>
       <c r="I85" t="n">
-        <v>-2558.300220904236</v>
+        <v>-2572.675372467498</v>
       </c>
     </row>
     <row r="86">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12616901.91</v>
+        <v>12178049.77</v>
       </c>
       <c r="E86" t="n">
         <v>0.5835756277426192</v>
@@ -3435,10 +3435,10 @@
         <v>-1.008678731428958e-06</v>
       </c>
       <c r="H86" t="n">
-        <v>-12.7264006131424</v>
+        <v>-12.28373979328231</v>
       </c>
       <c r="I86" t="n">
-        <v>-12.7264006131424</v>
+        <v>-12.28373979328231</v>
       </c>
     </row>
     <row r="87">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-1410564079.41</v>
+        <v>-1341385513.46</v>
       </c>
       <c r="E87" t="n">
         <v>0.999906031812547</v>
@@ -3470,10 +3470,10 @@
         <v>9.39681874529974e-05</v>
       </c>
       <c r="H87" t="n">
-        <v>-132548.1498284636</v>
+        <v>-126047.5653755445</v>
       </c>
       <c r="I87" t="n">
-        <v>-132548.1498284636</v>
+        <v>-126047.5653755445</v>
       </c>
     </row>
     <row r="88">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-210789268.91</v>
+        <v>-275079901.81</v>
       </c>
       <c r="E88" t="n">
         <v>0.9983821828874917</v>
@@ -3505,10 +3505,10 @@
         <v>0.001387899570778783</v>
       </c>
       <c r="H88" t="n">
-        <v>-292554.3358449625</v>
+        <v>-381783.2776519689</v>
       </c>
       <c r="I88" t="n">
-        <v>-292554.3358449625</v>
+        <v>-381783.2776519689</v>
       </c>
     </row>
     <row r="89">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-466347525.5</v>
+        <v>-460380476.87</v>
       </c>
       <c r="E89" t="n">
         <v>0.9936563817038003</v>
@@ -3540,10 +3540,10 @@
         <v>0.004911064643535079</v>
       </c>
       <c r="H89" t="n">
-        <v>-2290262.844083124</v>
+        <v>-2260958.282530076</v>
       </c>
       <c r="I89" t="n">
-        <v>-2290262.844083124</v>
+        <v>-2260958.282530076</v>
       </c>
     </row>
     <row r="90">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-928106565.37</v>
+        <v>-774901251.0700001</v>
       </c>
       <c r="E90" t="n">
         <v>0.9856536327098718</v>
@@ -3575,10 +3575,10 @@
         <v>0.008895199983645741</v>
       </c>
       <c r="H90" t="n">
-        <v>-8255693.505100729</v>
+        <v>-6892901.595844928</v>
       </c>
       <c r="I90" t="n">
-        <v>-8255693.505100729</v>
+        <v>-6892901.595844928</v>
       </c>
     </row>
     <row r="91">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>325613046.1</v>
+        <v>14337145.59999999</v>
       </c>
       <c r="E91" t="n">
         <v>0.9761318955535195</v>
@@ -3610,10 +3610,10 @@
         <v>0.01147716903300178</v>
       </c>
       <c r="H91" t="n">
-        <v>3737115.9694403</v>
+        <v>164549.8435019575</v>
       </c>
       <c r="I91" t="n">
-        <v>1868557.98472015</v>
+        <v>82274.92175097877</v>
       </c>
     </row>
     <row r="92">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>263741483.93</v>
+        <v>505596029.58</v>
       </c>
       <c r="E92" t="n">
         <v>0.9667342819189046</v>
@@ -3645,10 +3645,10 @@
         <v>0.01240503278375416</v>
       </c>
       <c r="H92" t="n">
-        <v>3271721.75458762</v>
+        <v>6271935.322275835</v>
       </c>
       <c r="I92" t="n">
-        <v>1635860.87729381</v>
+        <v>3135967.661137918</v>
       </c>
     </row>
     <row r="93">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>589973763.67</v>
+        <v>526743176.9999999</v>
       </c>
       <c r="E93" t="n">
         <v>0.9524015829683793</v>
@@ -3680,10 +3680,10 @@
         <v>0.01201262797217995</v>
       </c>
       <c r="H93" t="n">
-        <v>7087135.336314522</v>
+        <v>6327569.822185132</v>
       </c>
       <c r="I93" t="n">
-        <v>3543567.668157261</v>
+        <v>3163784.911092566</v>
       </c>
     </row>
     <row r="94">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>612295005.0700001</v>
+        <v>380413008.79</v>
       </c>
       <c r="E94" t="n">
         <v>0.9333610479054046</v>
@@ -3715,10 +3715,10 @@
         <v>0.009987366679108822</v>
       </c>
       <c r="H94" t="n">
-        <v>6115214.731420886</v>
+        <v>3799324.208288778</v>
       </c>
       <c r="I94" t="n">
-        <v>3057607.365710443</v>
+        <v>1899662.104144389</v>
       </c>
     </row>
     <row r="95">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>773886472.84</v>
+        <v>963113319.4399999</v>
       </c>
       <c r="E95" t="n">
         <v>0.9066754799235061</v>
@@ -3750,10 +3750,10 @@
         <v>0.006535572677782708</v>
       </c>
       <c r="H95" t="n">
-        <v>5057791.287598734</v>
+        <v>6294497.096140673</v>
       </c>
       <c r="I95" t="n">
-        <v>2528895.643799367</v>
+        <v>3147248.548070337</v>
       </c>
     </row>
     <row r="96">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>752632597.09</v>
+        <v>1410720811.72</v>
       </c>
       <c r="E96" t="n">
         <v>0.8730418834956067</v>
@@ -3785,10 +3785,10 @@
         <v>0.003235551599104936</v>
       </c>
       <c r="H96" t="n">
-        <v>2435181.60305305</v>
+        <v>4564459.978251259</v>
       </c>
       <c r="I96" t="n">
-        <v>1217590.801526525</v>
+        <v>2282229.989125629</v>
       </c>
     </row>
     <row r="97">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1376408988.27</v>
+        <v>805426893.5699999</v>
       </c>
       <c r="E97" t="n">
         <v>0.839886760163754</v>
@@ -3820,10 +3820,10 @@
         <v>0.001470791926687531</v>
       </c>
       <c r="H97" t="n">
-        <v>2024411.227767669</v>
+        <v>1184615.372599773</v>
       </c>
       <c r="I97" t="n">
-        <v>1012205.613883834</v>
+        <v>592307.6862998867</v>
       </c>
     </row>
     <row r="98">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>171337663.91</v>
+        <v>167532998.8</v>
       </c>
       <c r="E98" t="n">
         <v>0.8060794216350962</v>
@@ -3855,10 +3855,10 @@
         <v>0.000634385103338575</v>
       </c>
       <c r="H98" t="n">
-        <v>108694.0616253354</v>
+        <v>106280.4387563594</v>
       </c>
       <c r="I98" t="n">
-        <v>54347.03081266769</v>
+        <v>53140.21937817969</v>
       </c>
     </row>
     <row r="99">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>304374885.85</v>
+        <v>301626600.17</v>
       </c>
       <c r="E99" t="n">
         <v>0.7725125366488534</v>
@@ -3890,10 +3890,10 @@
         <v>0.0002641556154886482</v>
       </c>
       <c r="H99" t="n">
-        <v>80402.33531099379</v>
+        <v>79676.36021565476</v>
       </c>
       <c r="I99" t="n">
-        <v>40201.16765549689</v>
+        <v>39838.18010782738</v>
       </c>
     </row>
     <row r="100">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>295856253.29</v>
+        <v>294575354.51</v>
       </c>
       <c r="E100" t="n">
         <v>0.7390723504327896</v>
@@ -3925,10 +3925,10 @@
         <v>0.0001072133542818765</v>
       </c>
       <c r="H100" t="n">
-        <v>31719.74130048936</v>
+        <v>31582.41184579</v>
       </c>
       <c r="I100" t="n">
-        <v>15859.87065024468</v>
+        <v>15791.205922895</v>
       </c>
     </row>
     <row r="101">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>240713355.56</v>
+        <v>241238577.56</v>
       </c>
       <c r="E101" t="n">
         <v>0.7058360643204235</v>
@@ -3960,10 +3960,10 @@
         <v>4.218442338066453e-05</v>
       </c>
       <c r="H101" t="n">
-        <v>10154.35410432348</v>
+        <v>10176.51029154032</v>
       </c>
       <c r="I101" t="n">
-        <v>5077.177052161739</v>
+        <v>5088.255145770158</v>
       </c>
     </row>
     <row r="102">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>150836878.06</v>
+        <v>151684434.17</v>
       </c>
       <c r="E102" t="n">
         <v>0.6740936305925465</v>
@@ -3995,10 +3995,10 @@
         <v>1.659944883869446e-05</v>
       </c>
       <c r="H102" t="n">
-        <v>2503.809040345366</v>
+        <v>2517.878004631233</v>
       </c>
       <c r="I102" t="n">
-        <v>1251.904520172683</v>
+        <v>1258.939002315617</v>
       </c>
     </row>
     <row r="103">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12616901.91</v>
+        <v>12178049.77</v>
       </c>
       <c r="E103" t="n">
         <v>0.5835756277426192</v>
@@ -4030,10 +4030,10 @@
         <v>8.933136881328352e-07</v>
       </c>
       <c r="H103" t="n">
-        <v>11.27085117803231</v>
+        <v>10.87881855430392</v>
       </c>
       <c r="I103" t="n">
-        <v>5.635425589016156</v>
+        <v>5.439409277151962</v>
       </c>
     </row>
     <row r="104">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-1410564079.41</v>
+        <v>-1341385513.46</v>
       </c>
       <c r="E104" t="n">
         <v>0.999906031812547</v>
@@ -4065,10 +4065,10 @@
         <v>6.06503826584559e-05</v>
       </c>
       <c r="H104" t="n">
-        <v>-85551.25118048908</v>
+        <v>-81355.54468385836</v>
       </c>
       <c r="I104" t="n">
-        <v>-85551.25118048908</v>
+        <v>-81355.54468385836</v>
       </c>
     </row>
     <row r="105">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-210789268.91</v>
+        <v>-275079901.81</v>
       </c>
       <c r="E105" t="n">
         <v>0.9983821828874917</v>
@@ -4100,10 +4100,10 @@
         <v>0.0004286357166750632</v>
       </c>
       <c r="H105" t="n">
-        <v>-90351.80934665047</v>
+        <v>-117909.0708552354</v>
       </c>
       <c r="I105" t="n">
-        <v>-90351.80934665047</v>
+        <v>-117909.0708552354</v>
       </c>
     </row>
     <row r="106">
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-466347525.5</v>
+        <v>-460380476.87</v>
       </c>
       <c r="E106" t="n">
         <v>0.9936563817038003</v>
@@ -4135,10 +4135,10 @@
         <v>0.001657282796573178</v>
       </c>
       <c r="H106" t="n">
-        <v>-772869.7312356216</v>
+        <v>-762980.6441948072</v>
       </c>
       <c r="I106" t="n">
-        <v>-772869.7312356216</v>
+        <v>-762980.6441948072</v>
       </c>
     </row>
     <row r="107">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-928106565.37</v>
+        <v>-774901251.0700001</v>
       </c>
       <c r="E107" t="n">
         <v>0.9856536327098718</v>
@@ -4170,10 +4170,10 @@
         <v>0.003701791136432875</v>
       </c>
       <c r="H107" t="n">
-        <v>-3435656.657351824</v>
+        <v>-2868522.582821672</v>
       </c>
       <c r="I107" t="n">
-        <v>-3435656.657351824</v>
+        <v>-2868522.582821672</v>
       </c>
     </row>
     <row r="108">
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>325613046.1</v>
+        <v>14337145.59999999</v>
       </c>
       <c r="E108" t="n">
         <v>0.9761318955535195</v>
@@ -4205,10 +4205,10 @@
         <v>0.00611886473883394</v>
       </c>
       <c r="H108" t="n">
-        <v>1992382.1862856</v>
+        <v>87727.05466736809</v>
       </c>
       <c r="I108" t="n">
-        <v>996191.0931428</v>
+        <v>43863.52733368405</v>
       </c>
     </row>
     <row r="109">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>263741483.93</v>
+        <v>505596029.58</v>
       </c>
       <c r="E109" t="n">
         <v>0.9667342819189046</v>
@@ -4240,10 +4240,10 @@
         <v>0.008494727267819302</v>
       </c>
       <c r="H109" t="n">
-        <v>2240411.975195298</v>
+        <v>4294900.3789744</v>
       </c>
       <c r="I109" t="n">
-        <v>1120205.987597649</v>
+        <v>2147450.1894872</v>
       </c>
     </row>
     <row r="110">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>589973763.67</v>
+        <v>526743176.9999999</v>
       </c>
       <c r="E110" t="n">
         <v>0.9524015829683793</v>
@@ -4275,10 +4275,10 @@
         <v>0.01197966122818617</v>
       </c>
       <c r="H110" t="n">
-        <v>7067685.822284567</v>
+        <v>6310204.814718503</v>
       </c>
       <c r="I110" t="n">
-        <v>3533842.911142284</v>
+        <v>3155102.407359251</v>
       </c>
     </row>
     <row r="111">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>612295005.0700001</v>
+        <v>380413008.79</v>
       </c>
       <c r="E111" t="n">
         <v>0.9333610479054046</v>
@@ -4310,10 +4310,10 @@
         <v>0.01647754477361008</v>
       </c>
       <c r="H111" t="n">
-        <v>10089118.36069873</v>
+        <v>6268272.384800948</v>
       </c>
       <c r="I111" t="n">
-        <v>5044559.180349367</v>
+        <v>3134136.192400474</v>
       </c>
     </row>
     <row r="112">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>773886472.84</v>
+        <v>963113319.4399999</v>
       </c>
       <c r="E112" t="n">
         <v>0.9066754799235061</v>
@@ -4345,10 +4345,10 @@
         <v>0.02295203256100853</v>
       </c>
       <c r="H112" t="n">
-        <v>17762267.52314772</v>
+        <v>22105408.26772789</v>
       </c>
       <c r="I112" t="n">
-        <v>8881133.761573862</v>
+        <v>11052704.13386394</v>
       </c>
     </row>
     <row r="113">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>752632597.09</v>
+        <v>1410720811.72</v>
       </c>
       <c r="E113" t="n">
         <v>0.8730418834956067</v>
@@ -4380,10 +4380,10 @@
         <v>0.03109727088065561</v>
       </c>
       <c r="H113" t="n">
-        <v>23404819.74531907</v>
+        <v>43869567.21903521</v>
       </c>
       <c r="I113" t="n">
-        <v>11702409.87265953</v>
+        <v>21934783.6095176</v>
       </c>
     </row>
     <row r="114">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1376408988.27</v>
+        <v>805426893.5699999</v>
       </c>
       <c r="E114" t="n">
         <v>0.839886760163754</v>
@@ -4415,10 +4415,10 @@
         <v>0.0386581374619398</v>
       </c>
       <c r="H114" t="n">
-        <v>53209407.87239115</v>
+        <v>31136303.56717221</v>
       </c>
       <c r="I114" t="n">
-        <v>26604703.93619557</v>
+        <v>15568151.78358611</v>
       </c>
     </row>
     <row r="115">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>171337663.91</v>
+        <v>167532998.8</v>
       </c>
       <c r="E115" t="n">
         <v>0.8060794216350962</v>
@@ -4450,10 +4450,10 @@
         <v>0.04557620122769612</v>
       </c>
       <c r="H115" t="n">
-        <v>7808919.848245528</v>
+        <v>7635517.665588174</v>
       </c>
       <c r="I115" t="n">
-        <v>3904459.924122764</v>
+        <v>3817758.832794087</v>
       </c>
     </row>
     <row r="116">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>304374885.85</v>
+        <v>301626600.17</v>
       </c>
       <c r="E116" t="n">
         <v>0.7725125366488534</v>
@@ -4485,10 +4485,10 @@
         <v>0.05188104408575822</v>
       </c>
       <c r="H116" t="n">
-        <v>15791286.87138148</v>
+        <v>15648702.94085714</v>
       </c>
       <c r="I116" t="n">
-        <v>7895643.435690738</v>
+        <v>7824351.470428569</v>
       </c>
     </row>
     <row r="117">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>295856253.29</v>
+        <v>294575354.51</v>
       </c>
       <c r="E117" t="n">
         <v>0.7390723504327896</v>
@@ -4520,10 +4520,10 @@
         <v>0.05756191118833565</v>
       </c>
       <c r="H117" t="n">
-        <v>17030051.37639272</v>
+        <v>16956320.39457711</v>
       </c>
       <c r="I117" t="n">
-        <v>8515025.688196359</v>
+        <v>8478160.197288554</v>
       </c>
     </row>
     <row r="118">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>240713355.56</v>
+        <v>241238577.56</v>
       </c>
       <c r="E118" t="n">
         <v>0.7058360643204235</v>
@@ -4555,10 +4555,10 @@
         <v>0.06261909581715475</v>
       </c>
       <c r="H118" t="n">
-        <v>15073252.67628048</v>
+        <v>15106141.60302376</v>
       </c>
       <c r="I118" t="n">
-        <v>7536626.33814024</v>
+        <v>7553070.801511878</v>
       </c>
     </row>
     <row r="119">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>150836878.06</v>
+        <v>151684434.17</v>
       </c>
       <c r="E119" t="n">
         <v>0.6740936305925465</v>
@@ -4590,10 +4590,10 @@
         <v>0.06717920059908133</v>
       </c>
       <c r="H119" t="n">
-        <v>10133100.88893191</v>
+        <v>10190039.03086458</v>
       </c>
       <c r="I119" t="n">
-        <v>5066550.444465955</v>
+        <v>5095019.515432288</v>
       </c>
     </row>
     <row r="120">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12616901.91</v>
+        <v>12178049.77</v>
       </c>
       <c r="E120" t="n">
         <v>0.5835756277426192</v>
@@ -4625,10 +4625,10 @@
         <v>0.07770212208989746</v>
       </c>
       <c r="H120" t="n">
-        <v>980360.0526070805</v>
+        <v>946260.3100453877</v>
       </c>
       <c r="I120" t="n">
-        <v>490180.0263035403</v>
+        <v>473130.1550226939</v>
       </c>
     </row>
   </sheetData>
@@ -4704,22 +4704,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D2" t="n">
-        <v>1973036350.02</v>
+        <v>2041758857.86</v>
       </c>
       <c r="E2" t="n">
-        <v>-121961996.8800001</v>
+        <v>-129744181.2500002</v>
       </c>
       <c r="F2" t="n">
-        <v>-121961996.8800001</v>
+        <v>-129744181.2500002</v>
       </c>
       <c r="G2" t="n">
-        <v>-10.16349974000001</v>
+        <v>-10.81201510416669</v>
       </c>
       <c r="H2" t="n">
-        <v>-10.16349974000001</v>
+        <v>-10.81201510416669</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4737,22 +4737,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D3" t="n">
-        <v>2229316540.08</v>
+        <v>2312912010.57</v>
       </c>
       <c r="E3" t="n">
-        <v>134318193.1799998</v>
+        <v>141408971.46</v>
       </c>
       <c r="F3" t="n">
-        <v>67159096.58999991</v>
+        <v>70704485.73000002</v>
       </c>
       <c r="G3" t="n">
-        <v>11.19318276499999</v>
+        <v>11.784080955</v>
       </c>
       <c r="H3" t="n">
-        <v>5.596591382499993</v>
+        <v>5.892040477500002</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4770,22 +4770,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D4" t="n">
-        <v>2049526125.86</v>
+        <v>2125095296.74</v>
       </c>
       <c r="E4" t="n">
-        <v>-45472221.0400002</v>
+        <v>-46407742.37000012</v>
       </c>
       <c r="F4" t="n">
-        <v>-45472221.0400002</v>
+        <v>-46407742.37000012</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.78935175333335</v>
+        <v>-3.867311864166677</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.78935175333335</v>
+        <v>-3.867311864166677</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4803,22 +4803,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D5" t="n">
-        <v>2129901580.06</v>
+        <v>2206059950.06</v>
       </c>
       <c r="E5" t="n">
-        <v>34903233.15999985</v>
+        <v>34556910.94999981</v>
       </c>
       <c r="F5" t="n">
-        <v>17451616.57999992</v>
+        <v>17278455.4749999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.908602763333321</v>
+        <v>2.879742579166651</v>
       </c>
       <c r="H5" t="n">
-        <v>1.45430138166666</v>
+        <v>1.439871289583325</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4836,22 +4836,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D6" t="n">
-        <v>2073987061.46</v>
+        <v>2147302576.07</v>
       </c>
       <c r="E6" t="n">
-        <v>-21011285.44000006</v>
+        <v>-24200463.0400002</v>
       </c>
       <c r="F6" t="n">
-        <v>-21011285.44000006</v>
+        <v>-24200463.0400002</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.750940453333338</v>
+        <v>-2.01670525333335</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.750940453333338</v>
+        <v>-2.01670525333335</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4869,22 +4869,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D7" t="n">
-        <v>2116476598.37</v>
+        <v>2196126359.83</v>
       </c>
       <c r="E7" t="n">
-        <v>21478251.46999979</v>
+        <v>24623320.71999979</v>
       </c>
       <c r="F7" t="n">
-        <v>10739125.7349999</v>
+        <v>12311660.3599999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.789854289166649</v>
+        <v>2.051943393333316</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8949271445833246</v>
+        <v>1.025971696666658</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4902,22 +4902,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2094998346.9</v>
+        <v>2171503039.11</v>
       </c>
       <c r="D8" t="n">
-        <v>2147240980.85</v>
+        <v>2226642923.68</v>
       </c>
       <c r="E8" t="n">
-        <v>52242633.94999981</v>
+        <v>55139884.56999969</v>
       </c>
       <c r="F8" t="n">
-        <v>26121316.9749999</v>
+        <v>27569942.28499985</v>
       </c>
       <c r="G8" t="n">
-        <v>4.353552829166651</v>
+        <v>4.594990380833308</v>
       </c>
       <c r="H8" t="n">
-        <v>2.176776414583325</v>
+        <v>2.297495190416654</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5047,19 +5047,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G2" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="J2" t="n">
         <v>-620000000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="L2" t="n">
         <v>0.03432749872940843</v>
@@ -5071,10 +5071,10 @@
         <v>0.02500481880599148</v>
       </c>
       <c r="O2" t="n">
-        <v>-33619463.21620177</v>
+        <v>-32494633.94614996</v>
       </c>
       <c r="P2" t="n">
-        <v>-33619463.21620177</v>
+        <v>-32494633.94614996</v>
       </c>
     </row>
     <row r="3">
@@ -5105,19 +5105,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="H3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="J3" t="n">
         <v>-62000000</v>
       </c>
       <c r="K3" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="L3" t="n">
         <v>0.03782665436246635</v>
@@ -5129,10 +5129,10 @@
         <v>0.0251058158502353</v>
       </c>
       <c r="O3" t="n">
-        <v>20372203.03130213</v>
+        <v>17770533.45230579</v>
       </c>
       <c r="P3" t="n">
-        <v>10186101.51565107</v>
+        <v>8885266.726152895</v>
       </c>
     </row>
     <row r="4">
@@ -5163,19 +5163,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="H4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="L4" t="n">
         <v>0.03830470017405307</v>
@@ -5187,10 +5187,10 @@
         <v>0.02521323244800655</v>
       </c>
       <c r="O4" t="n">
-        <v>17251109.82916852</v>
+        <v>16811911.25825904</v>
       </c>
       <c r="P4" t="n">
-        <v>8625554.914584262</v>
+        <v>8405955.629129518</v>
       </c>
     </row>
     <row r="5">
@@ -5221,19 +5221,19 @@
         <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="H5" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I5" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="J5" t="n">
         <v>-124000000</v>
       </c>
       <c r="K5" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="L5" t="n">
         <v>0.03852218097221538</v>
@@ -5245,10 +5245,10 @@
         <v>0.02532026333962101</v>
       </c>
       <c r="O5" t="n">
-        <v>16614400.89951043</v>
+        <v>16336466.04784997</v>
       </c>
       <c r="P5" t="n">
-        <v>8307200.449755214</v>
+        <v>8168233.023924986</v>
       </c>
     </row>
     <row r="6">
@@ -5279,19 +5279,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="H6" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I6" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="J6" t="n">
         <v>-62000000</v>
       </c>
       <c r="K6" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="L6" t="n">
         <v>0.03873510939427094</v>
@@ -5303,10 +5303,10 @@
         <v>0.02542872476626745</v>
       </c>
       <c r="O6" t="n">
-        <v>-5650065.696432507</v>
+        <v>-5790491.76086683</v>
       </c>
       <c r="P6" t="n">
-        <v>-5650065.696432507</v>
+        <v>-5790491.76086683</v>
       </c>
     </row>
     <row r="7">
@@ -5337,19 +5337,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="H7" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I7" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="J7" t="n">
         <v>-62000000</v>
       </c>
       <c r="K7" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="L7" t="n">
         <v>0.03888939094511485</v>
@@ -5361,10 +5361,10 @@
         <v>0.02553821260711615</v>
       </c>
       <c r="O7" t="n">
-        <v>-4936984.056458791</v>
+        <v>-5105458.722928206</v>
       </c>
       <c r="P7" t="n">
-        <v>-4936984.056458791</v>
+        <v>-5105458.722928206</v>
       </c>
     </row>
     <row r="8">
@@ -5395,19 +5395,19 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="H8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="J8" t="n">
         <v>-31000000</v>
       </c>
       <c r="K8" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="L8" t="n">
         <v>0.03901400018340251</v>
@@ -5419,10 +5419,10 @@
         <v>0.02564775160277089</v>
       </c>
       <c r="O8" t="n">
-        <v>759788.3394733594</v>
+        <v>3940141.833224572</v>
       </c>
       <c r="P8" t="n">
-        <v>379894.1697366797</v>
+        <v>1970070.916612286</v>
       </c>
     </row>
     <row r="9">
@@ -5453,19 +5453,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="H9" t="n">
         <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="J9" t="n">
         <v>-31000000</v>
       </c>
       <c r="K9" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="L9" t="n">
         <v>0.03908855826627113</v>
@@ -5477,10 +5477,10 @@
         <v>0.02575828679253624</v>
       </c>
       <c r="O9" t="n">
-        <v>1273776.841778861</v>
+        <v>-1986148.711206025</v>
       </c>
       <c r="P9" t="n">
-        <v>636888.4208894307</v>
+        <v>-1986148.711206025</v>
       </c>
     </row>
     <row r="10">
@@ -5511,19 +5511,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="H10" t="n">
         <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="J10" t="n">
         <v>-31000000</v>
       </c>
       <c r="K10" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="L10" t="n">
         <v>0.03915884386251234</v>
@@ -5535,10 +5535,10 @@
         <v>0.02586772256944581</v>
       </c>
       <c r="O10" t="n">
-        <v>-161860.997434103</v>
+        <v>-149667.0570893367</v>
       </c>
       <c r="P10" t="n">
-        <v>-161860.997434103</v>
+        <v>-149667.0570893367</v>
       </c>
     </row>
     <row r="11">
@@ -5569,19 +5569,19 @@
         <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="H11" t="n">
         <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="J11" t="n">
         <v>-31000000</v>
       </c>
       <c r="K11" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="L11" t="n">
         <v>0.03922681220647117</v>
@@ -5593,10 +5593,10 @@
         <v>0.02597850453979926</v>
       </c>
       <c r="O11" t="n">
-        <v>-108951.261100436</v>
+        <v>-89137.46036406193</v>
       </c>
       <c r="P11" t="n">
-        <v>-108951.261100436</v>
+        <v>-89137.46036406193</v>
       </c>
     </row>
     <row r="12">
@@ -5627,19 +5627,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="H12" t="n">
         <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="J12" t="n">
         <v>-31000000</v>
       </c>
       <c r="K12" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="L12" t="n">
         <v>0.03929424848359133</v>
@@ -5651,10 +5651,10 @@
         <v>0.02608953222428303</v>
       </c>
       <c r="O12" t="n">
-        <v>449150.7134622567</v>
+        <v>-8536.538861164656</v>
       </c>
       <c r="P12" t="n">
-        <v>224575.3567311283</v>
+        <v>-8536.538861164656</v>
       </c>
     </row>
     <row r="13">
@@ -5685,19 +5685,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G13" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="H13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="L13" t="n">
         <v>0.03936107056455495</v>
@@ -5709,10 +5709,10 @@
         <v>0.02620112954634799</v>
       </c>
       <c r="O13" t="n">
-        <v>79813.76476863457</v>
+        <v>80400.62277743395</v>
       </c>
       <c r="P13" t="n">
-        <v>39906.88238431729</v>
+        <v>40200.31138871697</v>
       </c>
     </row>
     <row r="14">
@@ -5743,19 +5743,19 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="H14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="J14" t="n">
         <v>-62000000</v>
       </c>
       <c r="K14" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="L14" t="n">
         <v>0.03942868733737526</v>
@@ -5767,10 +5767,10 @@
         <v>0.02631330603469872</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5801,19 +5801,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G15" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="J15" t="n">
         <v>-620000000</v>
       </c>
       <c r="K15" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="L15" t="n">
         <v>0.03432749872940843</v>
@@ -5825,10 +5825,10 @@
         <v>-0.02499999878494696</v>
       </c>
       <c r="O15" t="n">
-        <v>18155449.10923949</v>
+        <v>17030836.66542407</v>
       </c>
       <c r="P15" t="n">
-        <v>9077724.554619746</v>
+        <v>8515418.332712036</v>
       </c>
     </row>
     <row r="16">
@@ -5859,19 +5859,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="H16" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I16" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="J16" t="n">
         <v>-62000000</v>
       </c>
       <c r="K16" t="n">
-        <v>947222038.641096</v>
+        <v>834173133.4710958</v>
       </c>
       <c r="L16" t="n">
         <v>0.03782665436246635</v>
@@ -5883,10 +5883,10 @@
         <v>-0.02505175249492542</v>
       </c>
       <c r="O16" t="n">
-        <v>-21752107.73062747</v>
+        <v>-19156040.63783142</v>
       </c>
       <c r="P16" t="n">
-        <v>-21752107.73062747</v>
+        <v>-19156040.63783142</v>
       </c>
     </row>
     <row r="17">
@@ -5917,19 +5917,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="H17" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I17" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="L17" t="n">
         <v>0.03830470017405307</v>
@@ -5941,10 +5941,10 @@
         <v>-0.02510607109988339</v>
       </c>
       <c r="O17" t="n">
-        <v>-17177789.11593881</v>
+        <v>-16740457.22797247</v>
       </c>
       <c r="P17" t="n">
-        <v>-17177789.11593881</v>
+        <v>-16740457.22797247</v>
       </c>
     </row>
     <row r="18">
@@ -5975,19 +5975,19 @@
         <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="H18" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I18" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="J18" t="n">
         <v>-124000000</v>
       </c>
       <c r="K18" t="n">
-        <v>998893528.3787673</v>
+        <v>984257827.4287672</v>
       </c>
       <c r="L18" t="n">
         <v>0.03852218097221538</v>
@@ -5999,10 +5999,10 @@
         <v>-0.02516160099667442</v>
       </c>
       <c r="O18" t="n">
-        <v>-18850320.29942011</v>
+        <v>-18574127.0487122</v>
       </c>
       <c r="P18" t="n">
-        <v>-18850320.29942011</v>
+        <v>-18574127.0487122</v>
       </c>
     </row>
     <row r="19">
@@ -6033,19 +6033,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="H19" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I19" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="J19" t="n">
         <v>-62000000</v>
       </c>
       <c r="K19" t="n">
-        <v>-271288382.4316438</v>
+        <v>-279571892.4616438</v>
       </c>
       <c r="L19" t="n">
         <v>0.03873510939427094</v>
@@ -6057,10 +6057,10 @@
         <v>-0.02521743137943178</v>
       </c>
       <c r="O19" t="n">
-        <v>4560797.445338016</v>
+        <v>4700056.675846255</v>
       </c>
       <c r="P19" t="n">
-        <v>2280398.722669008</v>
+        <v>2350028.337923128</v>
       </c>
     </row>
     <row r="20">
@@ -6091,19 +6091,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="H20" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I20" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="J20" t="n">
         <v>-62000000</v>
       </c>
       <c r="K20" t="n">
-        <v>-269401471.5847945</v>
+        <v>-280710552.5447945</v>
       </c>
       <c r="L20" t="n">
         <v>0.03888939094511485</v>
@@ -6115,10 +6115,10 @@
         <v>-0.02527289166469284</v>
       </c>
       <c r="O20" t="n">
-        <v>3971656.619974947</v>
+        <v>4138380.973767051</v>
       </c>
       <c r="P20" t="n">
-        <v>1985828.309987474</v>
+        <v>2069190.486883525</v>
       </c>
     </row>
     <row r="21">
@@ -6149,19 +6149,19 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="H21" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I21" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="J21" t="n">
         <v>-31000000</v>
       </c>
       <c r="K21" t="n">
-        <v>90247949.00082195</v>
+        <v>338250467.3508219</v>
       </c>
       <c r="L21" t="n">
         <v>0.03901400018340251</v>
@@ -6173,10 +6173,10 @@
         <v>-0.02532890719506886</v>
       </c>
       <c r="O21" t="n">
-        <v>-1142940.962393563</v>
+        <v>-4283757.348108819</v>
       </c>
       <c r="P21" t="n">
-        <v>-1142940.962393563</v>
+        <v>-4283757.348108819</v>
       </c>
     </row>
     <row r="22">
@@ -6207,19 +6207,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="H22" t="n">
         <v>2250000</v>
       </c>
       <c r="I22" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="J22" t="n">
         <v>-31000000</v>
       </c>
       <c r="K22" t="n">
-        <v>149682754.21</v>
+        <v>-154057218.49</v>
       </c>
       <c r="L22" t="n">
         <v>0.03908855826627113</v>
@@ -6231,10 +6231,10 @@
         <v>-0.02538363335203554</v>
       </c>
       <c r="O22" t="n">
-        <v>-1583121.729995623</v>
+        <v>1629388.312243579</v>
       </c>
       <c r="P22" t="n">
-        <v>-1583121.729995623</v>
+        <v>814694.1561217897</v>
       </c>
     </row>
     <row r="23">
@@ -6265,19 +6265,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="H23" t="n">
         <v>2250000</v>
       </c>
       <c r="I23" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="J23" t="n">
         <v>-31000000</v>
       </c>
       <c r="K23" t="n">
-        <v>12228227.91999999</v>
+        <v>13642415.84999999</v>
       </c>
       <c r="L23" t="n">
         <v>0.03915884386251234</v>
@@ -6289,10 +6289,10 @@
         <v>-0.02543993459508764</v>
       </c>
       <c r="O23" t="n">
-        <v>-103695.1061662082</v>
+        <v>-115687.3889809956</v>
       </c>
       <c r="P23" t="n">
-        <v>-103695.1061662082</v>
+        <v>-115687.3889809956</v>
       </c>
     </row>
     <row r="24">
@@ -6323,19 +6323,19 @@
         <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="H24" t="n">
         <v>2250000</v>
       </c>
       <c r="I24" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="J24" t="n">
         <v>-31000000</v>
       </c>
       <c r="K24" t="n">
-        <v>14224398.32</v>
+        <v>17275197.6</v>
       </c>
       <c r="L24" t="n">
         <v>0.03922681220647117</v>
@@ -6347,10 +6347,10 @@
         <v>-0.02549552338669633</v>
       </c>
       <c r="O24" t="n">
-        <v>-90664.62000731099</v>
+        <v>-110110.0511051501</v>
       </c>
       <c r="P24" t="n">
-        <v>-90664.62000731099</v>
+        <v>-110110.0511051501</v>
       </c>
     </row>
     <row r="25">
@@ -6381,19 +6381,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="H25" t="n">
         <v>2250000</v>
       </c>
       <c r="I25" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="J25" t="n">
         <v>-31000000</v>
       </c>
       <c r="K25" t="n">
-        <v>134294465.29</v>
+        <v>29036789.9</v>
       </c>
       <c r="L25" t="n">
         <v>0.03929424848359133</v>
@@ -6405,10 +6405,10 @@
         <v>-0.02555147156878314</v>
       </c>
       <c r="O25" t="n">
-        <v>-571903.5352837283</v>
+        <v>-123655.4519297632</v>
       </c>
       <c r="P25" t="n">
-        <v>-571903.5352837283</v>
+        <v>-123655.4519297632</v>
       </c>
     </row>
     <row r="26">
@@ -6439,19 +6439,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G26" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="H26" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I26" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="L26" t="n">
         <v>0.03936107056455495</v>
@@ -6463,10 +6463,10 @@
         <v>-0.02560744979333988</v>
       </c>
       <c r="O26" t="n">
-        <v>-78005.30013467018</v>
+        <v>-78578.86078859412</v>
       </c>
       <c r="P26" t="n">
-        <v>-78005.30013467018</v>
+        <v>-78578.86078859412</v>
       </c>
     </row>
     <row r="27">
@@ -6497,19 +6497,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="H27" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I27" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="J27" t="n">
         <v>-62000000</v>
       </c>
       <c r="K27" t="n">
-        <v>-10917433.92684932</v>
+        <v>133651477.9931507</v>
       </c>
       <c r="L27" t="n">
         <v>0.03942868733737526</v>
@@ -6521,10 +6521,10 @@
         <v>-0.02566354060598441</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -6555,19 +6555,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G28" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="J28" t="n">
         <v>-620000000</v>
       </c>
       <c r="K28" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="L28" t="n">
         <v>0.03432749872940843</v>
@@ -6579,10 +6579,10 @@
         <v>-0.02264935222023312</v>
       </c>
       <c r="O28" t="n">
-        <v>16448367.26309286</v>
+        <v>15429497.47952432</v>
       </c>
       <c r="P28" t="n">
-        <v>8224183.631546429</v>
+        <v>7714748.739762162</v>
       </c>
     </row>
     <row r="29">
@@ -6613,19 +6613,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="H29" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I29" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="J29" t="n">
         <v>-62000000</v>
       </c>
       <c r="K29" t="n">
-        <v>947222038.641096</v>
+        <v>834173133.4710958</v>
       </c>
       <c r="L29" t="n">
         <v>0.03782665436246635</v>
@@ -6637,10 +6637,10 @@
         <v>-0.01985875398907044</v>
       </c>
       <c r="O29" t="n">
-        <v>-17243095.31853269</v>
+        <v>-15185169.12173664</v>
       </c>
       <c r="P29" t="n">
-        <v>-17243095.31853269</v>
+        <v>-15185169.12173664</v>
       </c>
     </row>
     <row r="30">
@@ -6671,19 +6671,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="H30" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I30" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="L30" t="n">
         <v>0.03830470017405307</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01722276407024426</v>
       </c>
       <c r="O30" t="n">
-        <v>-11783962.85166252</v>
+        <v>-11483953.18878565</v>
       </c>
       <c r="P30" t="n">
-        <v>-11783962.85166252</v>
+        <v>-11483953.18878565</v>
       </c>
     </row>
     <row r="31">
@@ -6729,19 +6729,19 @@
         <v>0.75</v>
       </c>
       <c r="G31" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="H31" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I31" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="J31" t="n">
         <v>-124000000</v>
       </c>
       <c r="K31" t="n">
-        <v>998893528.3787673</v>
+        <v>984257827.4287672</v>
       </c>
       <c r="L31" t="n">
         <v>0.03852218097221538</v>
@@ -6753,10 +6753,10 @@
         <v>-0.01482995615663363</v>
       </c>
       <c r="O31" t="n">
-        <v>-11110160.42325164</v>
+        <v>-10947375.32069406</v>
       </c>
       <c r="P31" t="n">
-        <v>-11110160.42325164</v>
+        <v>-10947375.32069406</v>
       </c>
     </row>
     <row r="32">
@@ -6787,19 +6787,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="H32" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I32" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="J32" t="n">
         <v>-62000000</v>
       </c>
       <c r="K32" t="n">
-        <v>-271288382.4316438</v>
+        <v>-279571892.4616438</v>
       </c>
       <c r="L32" t="n">
         <v>0.03873510939427094</v>
@@ -6811,10 +6811,10 @@
         <v>-0.01260515871784285</v>
       </c>
       <c r="O32" t="n">
-        <v>2279755.412571813</v>
+        <v>2349365.385017809</v>
       </c>
       <c r="P32" t="n">
-        <v>1139877.706285907</v>
+        <v>1174682.692508904</v>
       </c>
     </row>
     <row r="33">
@@ -6845,19 +6845,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="H33" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I33" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="J33" t="n">
         <v>-62000000</v>
       </c>
       <c r="K33" t="n">
-        <v>-269401471.5847945</v>
+        <v>-280710552.5447945</v>
       </c>
       <c r="L33" t="n">
         <v>0.03888939094511485</v>
@@ -6869,10 +6869,10 @@
         <v>-0.01053392699102673</v>
       </c>
       <c r="O33" t="n">
-        <v>1655415.669220475</v>
+        <v>1724907.605235288</v>
       </c>
       <c r="P33" t="n">
-        <v>827707.8346102377</v>
+        <v>862453.8026176442</v>
       </c>
     </row>
     <row r="34">
@@ -6903,19 +6903,19 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="H34" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I34" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="J34" t="n">
         <v>-31000000</v>
       </c>
       <c r="K34" t="n">
-        <v>90247949.00082195</v>
+        <v>338250467.3508219</v>
       </c>
       <c r="L34" t="n">
         <v>0.03901400018340251</v>
@@ -6927,10 +6927,10 @@
         <v>-0.008630921630449429</v>
       </c>
       <c r="O34" t="n">
-        <v>-389461.4875674455</v>
+        <v>-1459706.637583918</v>
       </c>
       <c r="P34" t="n">
-        <v>-389461.4875674455</v>
+        <v>-1459706.637583918</v>
       </c>
     </row>
     <row r="35">
@@ -6961,19 +6961,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="H35" t="n">
         <v>2250000</v>
       </c>
       <c r="I35" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="J35" t="n">
         <v>-31000000</v>
       </c>
       <c r="K35" t="n">
-        <v>149682754.21</v>
+        <v>-154057218.49</v>
       </c>
       <c r="L35" t="n">
         <v>0.03908855826627113</v>
@@ -6985,10 +6985,10 @@
         <v>-0.006850555280960409</v>
       </c>
       <c r="O35" t="n">
-        <v>-427254.1593008393</v>
+        <v>439740.6215403088</v>
       </c>
       <c r="P35" t="n">
-        <v>-427254.1593008393</v>
+        <v>219870.3107701544</v>
       </c>
     </row>
     <row r="36">
@@ -7019,19 +7019,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G36" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="H36" t="n">
         <v>2250000</v>
       </c>
       <c r="I36" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="J36" t="n">
         <v>-31000000</v>
       </c>
       <c r="K36" t="n">
-        <v>12228227.91999999</v>
+        <v>13642415.84999999</v>
       </c>
       <c r="L36" t="n">
         <v>0.03915884386251234</v>
@@ -7043,10 +7043,10 @@
         <v>-0.005233721067838482</v>
       </c>
       <c r="O36" t="n">
-        <v>-21333.04469574491</v>
+        <v>-23800.19975011954</v>
       </c>
       <c r="P36" t="n">
-        <v>-21333.04469574491</v>
+        <v>-23800.19975011954</v>
       </c>
     </row>
     <row r="37">
@@ -7077,19 +7077,19 @@
         <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="H37" t="n">
         <v>2250000</v>
       </c>
       <c r="I37" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="J37" t="n">
         <v>-31000000</v>
       </c>
       <c r="K37" t="n">
-        <v>14224398.32</v>
+        <v>17275197.6</v>
       </c>
       <c r="L37" t="n">
         <v>0.03922681220647117</v>
@@ -7101,10 +7101,10 @@
         <v>-0.003721650822949542</v>
       </c>
       <c r="O37" t="n">
-        <v>-13234.56092839752</v>
+        <v>-16073.06334116399</v>
       </c>
       <c r="P37" t="n">
-        <v>-13234.56092839752</v>
+        <v>-16073.06334116399</v>
       </c>
     </row>
     <row r="38">
@@ -7135,19 +7135,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="H38" t="n">
         <v>2250000</v>
       </c>
       <c r="I38" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="J38" t="n">
         <v>-31000000</v>
       </c>
       <c r="K38" t="n">
-        <v>134294465.29</v>
+        <v>29036789.9</v>
       </c>
       <c r="L38" t="n">
         <v>0.03929424848359133</v>
@@ -7159,10 +7159,10 @@
         <v>-0.002324803196355599</v>
       </c>
       <c r="O38" t="n">
-        <v>-52034.700359843</v>
+        <v>-11250.80366190433</v>
       </c>
       <c r="P38" t="n">
-        <v>-52034.700359843</v>
+        <v>-11250.80366190433</v>
       </c>
     </row>
     <row r="39">
@@ -7193,19 +7193,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G39" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="H39" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I39" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="L39" t="n">
         <v>0.03936107056455495</v>
@@ -7217,10 +7217,10 @@
         <v>-0.001029519969532107</v>
       </c>
       <c r="O39" t="n">
-        <v>-3136.119171026371</v>
+        <v>-3159.178560060345</v>
       </c>
       <c r="P39" t="n">
-        <v>-3136.119171026371</v>
+        <v>-3159.178560060345</v>
       </c>
     </row>
     <row r="40">
@@ -7251,19 +7251,19 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="H40" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I40" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="J40" t="n">
         <v>-62000000</v>
       </c>
       <c r="K40" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="L40" t="n">
         <v>0.03942868733737526</v>
@@ -7275,10 +7275,10 @@
         <v>0.0001712813743293129</v>
       </c>
       <c r="O40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -7309,19 +7309,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G41" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="J41" t="n">
         <v>-620000000</v>
       </c>
       <c r="K41" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="L41" t="n">
         <v>0.03432749872940843</v>
@@ -7333,10 +7333,10 @@
         <v>0.02789279458488503</v>
       </c>
       <c r="O41" t="n">
-        <v>-37502402.5896528</v>
+        <v>-36247659.17335165</v>
       </c>
       <c r="P41" t="n">
-        <v>-37502402.5896528</v>
+        <v>-36247659.17335165</v>
       </c>
     </row>
     <row r="42">
@@ -7367,19 +7367,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G42" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="H42" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I42" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="J42" t="n">
         <v>-62000000</v>
       </c>
       <c r="K42" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="L42" t="n">
         <v>0.03782665436246635</v>
@@ -7391,10 +7391,10 @@
         <v>0.02492545821291703</v>
       </c>
       <c r="O42" t="n">
-        <v>20225851.18886004</v>
+        <v>17642871.74051509</v>
       </c>
       <c r="P42" t="n">
-        <v>10112925.59443002</v>
+        <v>8821435.870257543</v>
       </c>
     </row>
     <row r="43">
@@ -7425,19 +7425,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="H43" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I43" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="L43" t="n">
         <v>0.03830470017405307</v>
@@ -7449,10 +7449,10 @@
         <v>0.02210627144826827</v>
       </c>
       <c r="O43" t="n">
-        <v>15125300.47283325</v>
+        <v>14740223.1984997</v>
       </c>
       <c r="P43" t="n">
-        <v>7562650.236416627</v>
+        <v>7370111.599249849</v>
       </c>
     </row>
     <row r="44">
@@ -7483,19 +7483,19 @@
         <v>0.75</v>
       </c>
       <c r="G44" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="H44" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I44" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="J44" t="n">
         <v>-124000000</v>
       </c>
       <c r="K44" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="L44" t="n">
         <v>0.03852218097221538</v>
@@ -7507,10 +7507,10 @@
         <v>0.01953451299207831</v>
       </c>
       <c r="O44" t="n">
-        <v>12817964.2476002</v>
+        <v>12603538.27983324</v>
       </c>
       <c r="P44" t="n">
-        <v>6408982.1238001</v>
+        <v>6301769.139916618</v>
       </c>
     </row>
     <row r="45">
@@ -7541,19 +7541,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="H45" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I45" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="J45" t="n">
         <v>-62000000</v>
       </c>
       <c r="K45" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="L45" t="n">
         <v>0.03873510939427094</v>
@@ -7565,10 +7565,10 @@
         <v>0.01713582153361681</v>
       </c>
       <c r="O45" t="n">
-        <v>-3807446.827050986</v>
+        <v>-3902076.660081655</v>
       </c>
       <c r="P45" t="n">
-        <v>-3807446.827050986</v>
+        <v>-3902076.660081655</v>
       </c>
     </row>
     <row r="46">
@@ -7599,19 +7599,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="H46" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I46" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="J46" t="n">
         <v>-62000000</v>
       </c>
       <c r="K46" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="L46" t="n">
         <v>0.03888939094511485</v>
@@ -7623,10 +7623,10 @@
         <v>0.01489823429388384</v>
       </c>
       <c r="O46" t="n">
-        <v>-2880089.781921424</v>
+        <v>-2978372.895632596</v>
       </c>
       <c r="P46" t="n">
-        <v>-2880089.781921424</v>
+        <v>-2978372.895632596</v>
       </c>
     </row>
     <row r="47">
@@ -7657,19 +7657,19 @@
         <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="H47" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I47" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="J47" t="n">
         <v>-31000000</v>
       </c>
       <c r="K47" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="L47" t="n">
         <v>0.03901400018340251</v>
@@ -7681,10 +7681,10 @@
         <v>0.01283846298538327</v>
       </c>
       <c r="O47" t="n">
-        <v>380326.3001034642</v>
+        <v>1972311.876162619</v>
       </c>
       <c r="P47" t="n">
-        <v>190163.1500517321</v>
+        <v>986155.9380813093</v>
       </c>
     </row>
     <row r="48">
@@ -7715,19 +7715,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="H48" t="n">
         <v>2250000</v>
       </c>
       <c r="I48" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="J48" t="n">
         <v>-31000000</v>
       </c>
       <c r="K48" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="L48" t="n">
         <v>0.03908855826627113</v>
@@ -7739,10 +7739,10 @@
         <v>0.01091166853486086</v>
       </c>
       <c r="O48" t="n">
-        <v>539594.5311432841</v>
+        <v>-841367.9283942515</v>
       </c>
       <c r="P48" t="n">
-        <v>269797.265571642</v>
+        <v>-841367.9283942515</v>
       </c>
     </row>
     <row r="49">
@@ -7773,19 +7773,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G49" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="H49" t="n">
         <v>2250000</v>
       </c>
       <c r="I49" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="J49" t="n">
         <v>-31000000</v>
       </c>
       <c r="K49" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="L49" t="n">
         <v>0.03915884386251234</v>
@@ -7797,10 +7797,10 @@
         <v>0.009159039096315102</v>
       </c>
       <c r="O49" t="n">
-        <v>-57310.46479594545</v>
+        <v>-52992.93061580981</v>
       </c>
       <c r="P49" t="n">
-        <v>-57310.46479594545</v>
+        <v>-52992.93061580981</v>
       </c>
     </row>
     <row r="50">
@@ -7831,19 +7831,19 @@
         <v>0.25</v>
       </c>
       <c r="G50" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="H50" t="n">
         <v>2250000</v>
       </c>
       <c r="I50" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="J50" t="n">
         <v>-31000000</v>
       </c>
       <c r="K50" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="L50" t="n">
         <v>0.03922681220647117</v>
@@ -7855,10 +7855,10 @@
         <v>0.007522420693245678</v>
       </c>
       <c r="O50" t="n">
-        <v>-31548.28330481974</v>
+        <v>-25810.93439611698</v>
       </c>
       <c r="P50" t="n">
-        <v>-31548.28330481974</v>
+        <v>-25810.93439611698</v>
       </c>
     </row>
     <row r="51">
@@ -7889,19 +7889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="H51" t="n">
         <v>2250000</v>
       </c>
       <c r="I51" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="J51" t="n">
         <v>-31000000</v>
       </c>
       <c r="K51" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="L51" t="n">
         <v>0.03929424848359133</v>
@@ -7913,10 +7913,10 @@
         <v>0.006011768704670392</v>
       </c>
       <c r="O51" t="n">
-        <v>103497.0722993473</v>
+        <v>-1967.060839978806</v>
       </c>
       <c r="P51" t="n">
-        <v>51748.53614967367</v>
+        <v>-1967.060839978806</v>
       </c>
     </row>
     <row r="52">
@@ -7947,19 +7947,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G52" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="H52" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I52" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="L52" t="n">
         <v>0.03936107056455495</v>
@@ -7971,10 +7971,10 @@
         <v>0.004613431737291229</v>
       </c>
       <c r="O52" t="n">
-        <v>14053.41532337252</v>
+        <v>14156.74786704356</v>
       </c>
       <c r="P52" t="n">
-        <v>7026.70766168626</v>
+        <v>7078.373933521779</v>
       </c>
     </row>
     <row r="53">
@@ -8005,19 +8005,19 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="H53" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I53" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="J53" t="n">
         <v>-62000000</v>
       </c>
       <c r="K53" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="L53" t="n">
         <v>0.03942868733737526</v>
@@ -8029,10 +8029,10 @@
         <v>0.003319954993421748</v>
       </c>
       <c r="O53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -8063,19 +8063,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G54" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="J54" t="n">
         <v>-620000000</v>
       </c>
       <c r="K54" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="L54" t="n">
         <v>0.03432749872940843</v>
@@ -8087,10 +8087,10 @@
         <v>0.0349083460781352</v>
       </c>
       <c r="O54" t="n">
-        <v>-46934947.46025104</v>
+        <v>-45364612.96823002</v>
       </c>
       <c r="P54" t="n">
-        <v>-46934947.46025104</v>
+        <v>-45364612.96823002</v>
       </c>
     </row>
     <row r="55">
@@ -8121,19 +8121,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G55" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="H55" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I55" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="J55" t="n">
         <v>-62000000</v>
       </c>
       <c r="K55" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="L55" t="n">
         <v>0.03782665436246635</v>
@@ -8145,10 +8145,10 @@
         <v>0.03231037168362505</v>
       </c>
       <c r="O55" t="n">
-        <v>26218365.33344426</v>
+        <v>22870100.86768048</v>
       </c>
       <c r="P55" t="n">
-        <v>13109182.66672213</v>
+        <v>11435050.43384024</v>
       </c>
     </row>
     <row r="56">
@@ -8179,19 +8179,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="H56" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I56" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="L56" t="n">
         <v>0.03830470017405307</v>
@@ -8203,10 +8203,10 @@
         <v>0.02984617139370105</v>
       </c>
       <c r="O56" t="n">
-        <v>20421006.38046642</v>
+        <v>19901104.94179668</v>
       </c>
       <c r="P56" t="n">
-        <v>10210503.19023321</v>
+        <v>9950552.470898338</v>
       </c>
     </row>
     <row r="57">
@@ -8237,19 +8237,19 @@
         <v>0.75</v>
       </c>
       <c r="G57" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="H57" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I57" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="J57" t="n">
         <v>-124000000</v>
       </c>
       <c r="K57" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="L57" t="n">
         <v>0.03852218097221538</v>
@@ -8261,10 +8261,10 @@
         <v>0.02759968737635887</v>
       </c>
       <c r="O57" t="n">
-        <v>18110090.90314015</v>
+        <v>17807135.32507474</v>
       </c>
       <c r="P57" t="n">
-        <v>9055045.451570075</v>
+        <v>8903567.662537372</v>
       </c>
     </row>
     <row r="58">
@@ -8295,19 +8295,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="H58" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I58" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="J58" t="n">
         <v>-62000000</v>
       </c>
       <c r="K58" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="L58" t="n">
         <v>0.03873510939427094</v>
@@ -8319,10 +8319,10 @@
         <v>0.02550527570343863</v>
       </c>
       <c r="O58" t="n">
-        <v>-5667074.721781447</v>
+        <v>-5807923.526519679</v>
       </c>
       <c r="P58" t="n">
-        <v>-5667074.721781447</v>
+        <v>-5807923.526519679</v>
       </c>
     </row>
     <row r="59">
@@ -8353,19 +8353,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="H59" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I59" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="J59" t="n">
         <v>-62000000</v>
       </c>
       <c r="K59" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="L59" t="n">
         <v>0.03888939094511485</v>
@@ -8377,10 +8377,10 @@
         <v>0.02355207664351209</v>
       </c>
       <c r="O59" t="n">
-        <v>-4553029.167480368</v>
+        <v>-4708401.366710636</v>
       </c>
       <c r="P59" t="n">
-        <v>-4553029.167480368</v>
+        <v>-4708401.366710636</v>
       </c>
     </row>
     <row r="60">
@@ -8411,19 +8411,19 @@
         <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="H60" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I60" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="J60" t="n">
         <v>-31000000</v>
       </c>
       <c r="K60" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="L60" t="n">
         <v>0.03901400018340251</v>
@@ -8435,10 +8435,10 @@
         <v>0.02175522406292973</v>
       </c>
       <c r="O60" t="n">
-        <v>644476.2028909577</v>
+        <v>3342151.380328503</v>
       </c>
       <c r="P60" t="n">
-        <v>322238.1014454789</v>
+        <v>1671075.690164251</v>
       </c>
     </row>
     <row r="61">
@@ -8469,19 +8469,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="H61" t="n">
         <v>2250000</v>
       </c>
       <c r="I61" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="J61" t="n">
         <v>-31000000</v>
       </c>
       <c r="K61" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="L61" t="n">
         <v>0.03908855826627113</v>
@@ -8493,10 +8493,10 @@
         <v>0.02007474611606698</v>
       </c>
       <c r="O61" t="n">
-        <v>992719.2329672207</v>
+        <v>-1547906.949221786</v>
       </c>
       <c r="P61" t="n">
-        <v>496359.6164836104</v>
+        <v>-1547906.949221786</v>
       </c>
     </row>
     <row r="62">
@@ -8527,19 +8527,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="H62" t="n">
         <v>2250000</v>
       </c>
       <c r="I62" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="J62" t="n">
         <v>-31000000</v>
       </c>
       <c r="K62" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="L62" t="n">
         <v>0.03915884386251234</v>
@@ -8551,10 +8551,10 @@
         <v>0.01854770837490727</v>
       </c>
       <c r="O62" t="n">
-        <v>-116057.7847400222</v>
+        <v>-107314.4696357043</v>
       </c>
       <c r="P62" t="n">
-        <v>-116057.7847400222</v>
+        <v>-107314.4696357043</v>
       </c>
     </row>
     <row r="63">
@@ -8585,19 +8585,19 @@
         <v>0.25</v>
       </c>
       <c r="G63" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="H63" t="n">
         <v>2250000</v>
       </c>
       <c r="I63" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="J63" t="n">
         <v>-31000000</v>
       </c>
       <c r="K63" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="L63" t="n">
         <v>0.03922681220647117</v>
@@ -8609,10 +8609,10 @@
         <v>0.01712251280817986</v>
       </c>
       <c r="O63" t="n">
-        <v>-71810.11365768088</v>
+        <v>-58750.7762209344</v>
       </c>
       <c r="P63" t="n">
-        <v>-71810.11365768088</v>
+        <v>-58750.7762209344</v>
       </c>
     </row>
     <row r="64">
@@ -8643,19 +8643,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="H64" t="n">
         <v>2250000</v>
       </c>
       <c r="I64" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="J64" t="n">
         <v>-31000000</v>
       </c>
       <c r="K64" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="L64" t="n">
         <v>0.03929424848359133</v>
@@ -8667,10 +8667,10 @@
         <v>0.01580817291864865</v>
       </c>
       <c r="O64" t="n">
-        <v>272149.4614739451</v>
+        <v>-5172.460789406253</v>
       </c>
       <c r="P64" t="n">
-        <v>136074.7307369725</v>
+        <v>-5172.460789406253</v>
       </c>
     </row>
     <row r="65">
@@ -8701,19 +8701,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G65" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="H65" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I65" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="L65" t="n">
         <v>0.03936107056455495</v>
@@ -8725,10 +8725,10 @@
         <v>0.01459272426401294</v>
       </c>
       <c r="O65" t="n">
-        <v>44452.29201593011</v>
+        <v>44779.14269957671</v>
       </c>
       <c r="P65" t="n">
-        <v>22226.14600796506</v>
+        <v>22389.57134978836</v>
       </c>
     </row>
     <row r="66">
@@ -8759,19 +8759,19 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="H66" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I66" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="J66" t="n">
         <v>-62000000</v>
       </c>
       <c r="K66" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="L66" t="n">
         <v>0.03942868733737526</v>
@@ -8783,10 +8783,10 @@
         <v>0.01346967956071188</v>
       </c>
       <c r="O66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -8817,19 +8817,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G67" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="J67" t="n">
         <v>-620000000</v>
       </c>
       <c r="K67" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="L67" t="n">
         <v>0.03432749872940843</v>
@@ -8841,10 +8841,10 @@
         <v>-0.03432359322008915</v>
       </c>
       <c r="O67" t="n">
-        <v>24926411.20961912</v>
+        <v>23382381.53250516</v>
       </c>
       <c r="P67" t="n">
-        <v>12463205.60480956</v>
+        <v>11691190.76625258</v>
       </c>
     </row>
     <row r="68">
@@ -8875,19 +8875,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G68" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="H68" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I68" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="J68" t="n">
         <v>-62000000</v>
       </c>
       <c r="K68" t="n">
-        <v>947222038.641096</v>
+        <v>834173133.4710958</v>
       </c>
       <c r="L68" t="n">
         <v>0.03782665436246635</v>
@@ -8899,10 +8899,10 @@
         <v>-0.03222210497938605</v>
       </c>
       <c r="O68" t="n">
-        <v>-27978030.63722467</v>
+        <v>-24638913.08788164</v>
       </c>
       <c r="P68" t="n">
-        <v>-27978030.63722467</v>
+        <v>-24638913.08788164</v>
       </c>
     </row>
     <row r="69">
@@ -8933,19 +8933,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="H69" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I69" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="L69" t="n">
         <v>0.03830470017405307</v>
@@ -8957,10 +8957,10 @@
         <v>-0.02969704733354739</v>
       </c>
       <c r="O69" t="n">
-        <v>-20318974.41986052</v>
+        <v>-19801670.62805112</v>
       </c>
       <c r="P69" t="n">
-        <v>-20318974.41986052</v>
+        <v>-19801670.62805112</v>
       </c>
     </row>
     <row r="70">
@@ -8991,19 +8991,19 @@
         <v>0.75</v>
       </c>
       <c r="G70" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="H70" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I70" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="J70" t="n">
         <v>-124000000</v>
       </c>
       <c r="K70" t="n">
-        <v>998893528.3787673</v>
+        <v>984257827.4287672</v>
       </c>
       <c r="L70" t="n">
         <v>0.03852218097221538</v>
@@ -9015,10 +9015,10 @@
         <v>-0.0274114503343057</v>
       </c>
       <c r="O70" t="n">
-        <v>-20535840.25681047</v>
+        <v>-20234950.91453646</v>
       </c>
       <c r="P70" t="n">
-        <v>-20535840.25681047</v>
+        <v>-20234950.91453646</v>
       </c>
     </row>
     <row r="71">
@@ -9049,19 +9049,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="H71" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I71" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="J71" t="n">
         <v>-62000000</v>
       </c>
       <c r="K71" t="n">
-        <v>-271288382.4316438</v>
+        <v>-279571892.4616438</v>
       </c>
       <c r="L71" t="n">
         <v>0.03873510939427094</v>
@@ -9073,10 +9073,10 @@
         <v>-0.0252927177134521</v>
       </c>
       <c r="O71" t="n">
-        <v>4574413.650521738</v>
+        <v>4714088.637765296</v>
       </c>
       <c r="P71" t="n">
-        <v>2287206.825260869</v>
+        <v>2357044.318882648</v>
       </c>
     </row>
     <row r="72">
@@ -9107,19 +9107,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G72" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="H72" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I72" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="J72" t="n">
         <v>-62000000</v>
       </c>
       <c r="K72" t="n">
-        <v>-269401471.5847945</v>
+        <v>-280710552.5447945</v>
       </c>
       <c r="L72" t="n">
         <v>0.03888939094511485</v>
@@ -9131,10 +9131,10 @@
         <v>-0.02332613375362271</v>
       </c>
       <c r="O72" t="n">
-        <v>3665721.943105661</v>
+        <v>3819603.605249374</v>
       </c>
       <c r="P72" t="n">
-        <v>1832860.971552831</v>
+        <v>1909801.802624687</v>
       </c>
     </row>
     <row r="73">
@@ -9165,19 +9165,19 @@
         <v>0.5</v>
       </c>
       <c r="G73" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="H73" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I73" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="J73" t="n">
         <v>-31000000</v>
       </c>
       <c r="K73" t="n">
-        <v>90247949.00082195</v>
+        <v>338250467.3508219</v>
       </c>
       <c r="L73" t="n">
         <v>0.03901400018340251</v>
@@ -9189,10 +9189,10 @@
         <v>-0.02152530442995682</v>
       </c>
       <c r="O73" t="n">
-        <v>-971307.2882109547</v>
+        <v>-3640472.141650804</v>
       </c>
       <c r="P73" t="n">
-        <v>-971307.2882109547</v>
+        <v>-3640472.141650804</v>
       </c>
     </row>
     <row r="74">
@@ -9223,19 +9223,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G74" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="H74" t="n">
         <v>2250000</v>
       </c>
       <c r="I74" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="J74" t="n">
         <v>-31000000</v>
       </c>
       <c r="K74" t="n">
-        <v>149682754.21</v>
+        <v>-154057218.49</v>
       </c>
       <c r="L74" t="n">
         <v>0.03908855826627113</v>
@@ -9247,10 +9247,10 @@
         <v>-0.01984578814143261</v>
       </c>
       <c r="O74" t="n">
-        <v>-1237738.428532413</v>
+        <v>1273911.216587889</v>
       </c>
       <c r="P74" t="n">
-        <v>-1237738.428532413</v>
+        <v>636955.6082939446</v>
       </c>
     </row>
     <row r="75">
@@ -9281,19 +9281,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G75" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="H75" t="n">
         <v>2250000</v>
       </c>
       <c r="I75" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="J75" t="n">
         <v>-31000000</v>
       </c>
       <c r="K75" t="n">
-        <v>12228227.91999999</v>
+        <v>13642415.84999999</v>
       </c>
       <c r="L75" t="n">
         <v>0.03915884386251234</v>
@@ -9305,10 +9305,10 @@
         <v>-0.01832662273584051</v>
       </c>
       <c r="O75" t="n">
-        <v>-74700.70660590389</v>
+        <v>-83339.80282946698</v>
       </c>
       <c r="P75" t="n">
-        <v>-74700.70660590389</v>
+        <v>-83339.80282946698</v>
       </c>
     </row>
     <row r="76">
@@ -9339,19 +9339,19 @@
         <v>0.25</v>
       </c>
       <c r="G76" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="H76" t="n">
         <v>2250000</v>
       </c>
       <c r="I76" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="J76" t="n">
         <v>-31000000</v>
       </c>
       <c r="K76" t="n">
-        <v>14224398.32</v>
+        <v>17275197.6</v>
       </c>
       <c r="L76" t="n">
         <v>0.03922681220647117</v>
@@ -9363,10 +9363,10 @@
         <v>-0.01691110693903308</v>
       </c>
       <c r="O76" t="n">
-        <v>-60137.58028323063</v>
+        <v>-73035.67850163192</v>
       </c>
       <c r="P76" t="n">
-        <v>-60137.58028323063</v>
+        <v>-73035.67850163192</v>
       </c>
     </row>
     <row r="77">
@@ -9397,19 +9397,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="H77" t="n">
         <v>2250000</v>
       </c>
       <c r="I77" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="J77" t="n">
         <v>-31000000</v>
       </c>
       <c r="K77" t="n">
-        <v>134294465.29</v>
+        <v>29036789.9</v>
       </c>
       <c r="L77" t="n">
         <v>0.03929424848359133</v>
@@ -9421,10 +9421,10 @@
         <v>-0.01560891224971384</v>
       </c>
       <c r="O77" t="n">
-        <v>-349365.0873889751</v>
+        <v>-75538.78426041281</v>
       </c>
       <c r="P77" t="n">
-        <v>-349365.0873889751</v>
+        <v>-75538.78426041281</v>
       </c>
     </row>
     <row r="78">
@@ -9455,19 +9455,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G78" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="H78" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I78" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="L78" t="n">
         <v>0.03936107056455495</v>
@@ -9479,10 +9479,10 @@
         <v>-0.01440665719067059</v>
       </c>
       <c r="O78" t="n">
-        <v>-43885.49532128132</v>
+        <v>-44208.17843833612</v>
       </c>
       <c r="P78" t="n">
-        <v>-43885.49532128132</v>
+        <v>-44208.17843833612</v>
       </c>
     </row>
     <row r="79">
@@ -9513,19 +9513,19 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="H79" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I79" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="J79" t="n">
         <v>-62000000</v>
       </c>
       <c r="K79" t="n">
-        <v>-10917433.92684932</v>
+        <v>133651477.9931507</v>
       </c>
       <c r="L79" t="n">
         <v>0.03942868733737526</v>
@@ -9537,10 +9537,10 @@
         <v>-0.01329726695768341</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="80">
@@ -9571,19 +9571,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G80" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>-1348213104.06</v>
+        <v>-1303105020.33</v>
       </c>
       <c r="J80" t="n">
         <v>-620000000</v>
       </c>
       <c r="K80" t="n">
-        <v>-728213104.0599999</v>
+        <v>-683105020.3299999</v>
       </c>
       <c r="L80" t="n">
         <v>0.03432749872940843</v>
@@ -9595,10 +9595,10 @@
         <v>-0.01000145066733071</v>
       </c>
       <c r="O80" t="n">
-        <v>7263233.497380241</v>
+        <v>6813323.240446202</v>
       </c>
       <c r="P80" t="n">
-        <v>3631616.74869012</v>
+        <v>3406661.620223101</v>
       </c>
     </row>
     <row r="81">
@@ -9629,19 +9629,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>974764849.6000001</v>
+        <v>861715944.4299999</v>
       </c>
       <c r="H81" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I81" t="n">
-        <v>885222038.641096</v>
+        <v>772173133.4710958</v>
       </c>
       <c r="J81" t="n">
         <v>-62000000</v>
       </c>
       <c r="K81" t="n">
-        <v>947222038.641096</v>
+        <v>834173133.4710958</v>
       </c>
       <c r="L81" t="n">
         <v>0.03782665436246635</v>
@@ -9653,10 +9653,10 @@
         <v>-0.01002646052209499</v>
       </c>
       <c r="O81" t="n">
-        <v>-8705844.011418846</v>
+        <v>-7666820.325395201</v>
       </c>
       <c r="P81" t="n">
-        <v>-8705844.011418846</v>
+        <v>-7666820.325395201</v>
       </c>
     </row>
     <row r="82">
@@ -9687,19 +9687,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>871985042.7</v>
+        <v>851081801.2700001</v>
       </c>
       <c r="H82" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I82" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>821050289.2753425</v>
+        <v>800147047.8453425</v>
       </c>
       <c r="L82" t="n">
         <v>0.03830470017405307</v>
@@ -9711,10 +9711,10 @@
         <v>-0.01005429630576771</v>
       </c>
       <c r="O82" t="n">
-        <v>-6879235.741925485</v>
+        <v>-6704096.256018637</v>
       </c>
       <c r="P82" t="n">
-        <v>-6879235.741925485</v>
+        <v>-6704096.256018637</v>
       </c>
     </row>
     <row r="83">
@@ -9745,19 +9745,19 @@
         <v>0.75</v>
       </c>
       <c r="G83" t="n">
-        <v>1005206416.05</v>
+        <v>990570715.1000001</v>
       </c>
       <c r="H83" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I83" t="n">
-        <v>874893528.3787673</v>
+        <v>860257827.4287672</v>
       </c>
       <c r="J83" t="n">
         <v>-124000000</v>
       </c>
       <c r="K83" t="n">
-        <v>998893528.3787673</v>
+        <v>984257827.4287672</v>
       </c>
       <c r="L83" t="n">
         <v>0.03852218097221538</v>
@@ -9769,10 +9769,10 @@
         <v>-0.01008322673507944</v>
       </c>
       <c r="O83" t="n">
-        <v>-7554052.448134966</v>
+        <v>-7443371.129805716</v>
       </c>
       <c r="P83" t="n">
-        <v>-7554052.448134966</v>
+        <v>-7443371.129805716</v>
       </c>
     </row>
     <row r="84">
@@ -9803,19 +9803,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G84" t="n">
-        <v>-243337598.87</v>
+        <v>-251621108.9</v>
       </c>
       <c r="H84" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I84" t="n">
-        <v>-333288382.4316438</v>
+        <v>-341571892.4616438</v>
       </c>
       <c r="J84" t="n">
         <v>-62000000</v>
       </c>
       <c r="K84" t="n">
-        <v>-271288382.4316438</v>
+        <v>-279571892.4616438</v>
       </c>
       <c r="L84" t="n">
         <v>0.03873510939427094</v>
@@ -9827,10 +9827,10 @@
         <v>-0.0101121147124088</v>
       </c>
       <c r="O84" t="n">
-        <v>1828866.162195075</v>
+        <v>1884708.697958241</v>
       </c>
       <c r="P84" t="n">
-        <v>914433.0810975374</v>
+        <v>942354.3489791203</v>
       </c>
     </row>
     <row r="85">
@@ -9861,19 +9861,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G85" t="n">
-        <v>-241428019.53</v>
+        <v>-252737100.49</v>
       </c>
       <c r="H85" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I85" t="n">
-        <v>-331401471.5847945</v>
+        <v>-342710552.5447945</v>
       </c>
       <c r="J85" t="n">
         <v>-62000000</v>
       </c>
       <c r="K85" t="n">
-        <v>-269401471.5847945</v>
+        <v>-280710552.5447945</v>
       </c>
       <c r="L85" t="n">
         <v>0.03888939094511485</v>
@@ -9885,10 +9885,10 @@
         <v>-0.0101405708492285</v>
       </c>
       <c r="O85" t="n">
-        <v>1593599.413870349</v>
+        <v>1660496.393620498</v>
       </c>
       <c r="P85" t="n">
-        <v>796799.7069351746</v>
+        <v>830248.196810249</v>
       </c>
     </row>
     <row r="86">
@@ -9919,19 +9919,19 @@
         <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>149216557.22</v>
+        <v>397219075.5699999</v>
       </c>
       <c r="H86" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I86" t="n">
-        <v>59247949.00082195</v>
+        <v>307250467.3508219</v>
       </c>
       <c r="J86" t="n">
         <v>-31000000</v>
       </c>
       <c r="K86" t="n">
-        <v>90247949.00082195</v>
+        <v>338250467.3508219</v>
       </c>
       <c r="L86" t="n">
         <v>0.03901400018340251</v>
@@ -9943,10 +9943,10 @@
         <v>-0.01016949446707605</v>
       </c>
       <c r="O86" t="n">
-        <v>-458888.00901441</v>
+        <v>-1719918.128105035</v>
       </c>
       <c r="P86" t="n">
-        <v>-458888.00901441</v>
+        <v>-1719918.128105035</v>
       </c>
     </row>
     <row r="87">
@@ -9977,19 +9977,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>116432754.21</v>
+        <v>-187307218.49</v>
       </c>
       <c r="H87" t="n">
         <v>2250000</v>
       </c>
       <c r="I87" t="n">
-        <v>118682754.21</v>
+        <v>-185057218.49</v>
       </c>
       <c r="J87" t="n">
         <v>-31000000</v>
       </c>
       <c r="K87" t="n">
-        <v>149682754.21</v>
+        <v>-154057218.49</v>
       </c>
       <c r="L87" t="n">
         <v>0.03908855826627113</v>
@@ -10001,10 +10001,10 @@
         <v>-0.01019737062440143</v>
       </c>
       <c r="O87" t="n">
-        <v>-635987.7169835642</v>
+        <v>654574.397627883</v>
       </c>
       <c r="P87" t="n">
-        <v>-635987.7169835642</v>
+        <v>327287.1988139415</v>
       </c>
     </row>
     <row r="88">
@@ -10035,19 +10035,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>-21021772.08000001</v>
+        <v>-19607584.15000001</v>
       </c>
       <c r="H88" t="n">
         <v>2250000</v>
       </c>
       <c r="I88" t="n">
-        <v>-18771772.08000001</v>
+        <v>-17357584.15000001</v>
       </c>
       <c r="J88" t="n">
         <v>-31000000</v>
       </c>
       <c r="K88" t="n">
-        <v>12228227.91999999</v>
+        <v>13642415.84999999</v>
       </c>
       <c r="L88" t="n">
         <v>0.03915884386251234</v>
@@ -10059,10 +10059,10 @@
         <v>-0.0102268186216663</v>
       </c>
       <c r="O88" t="n">
-        <v>-41685.28966741191</v>
+        <v>-46506.17081976515</v>
       </c>
       <c r="P88" t="n">
-        <v>-41685.28966741191</v>
+        <v>-46506.17081976515</v>
       </c>
     </row>
     <row r="89">
@@ -10093,19 +10093,19 @@
         <v>0.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-19025601.68</v>
+        <v>-15974802.4</v>
       </c>
       <c r="H89" t="n">
         <v>2250000</v>
       </c>
       <c r="I89" t="n">
-        <v>-16775601.68</v>
+        <v>-13724802.4</v>
       </c>
       <c r="J89" t="n">
         <v>-31000000</v>
       </c>
       <c r="K89" t="n">
-        <v>14224398.32</v>
+        <v>17275197.6</v>
       </c>
       <c r="L89" t="n">
         <v>0.03922681220647117</v>
@@ -10117,10 +10117,10 @@
         <v>-0.01025547675463123</v>
       </c>
       <c r="O89" t="n">
-        <v>-36469.49657984389</v>
+        <v>-44291.34685461532</v>
       </c>
       <c r="P89" t="n">
-        <v>-36469.49657984389</v>
+        <v>-44291.34685461532</v>
       </c>
     </row>
     <row r="90">
@@ -10151,19 +10151,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>101044465.29</v>
+        <v>-4213210.100000001</v>
       </c>
       <c r="H90" t="n">
         <v>2250000</v>
       </c>
       <c r="I90" t="n">
-        <v>103294465.29</v>
+        <v>-1963210.100000001</v>
       </c>
       <c r="J90" t="n">
         <v>-31000000</v>
       </c>
       <c r="K90" t="n">
-        <v>134294465.29</v>
+        <v>29036789.9</v>
       </c>
       <c r="L90" t="n">
         <v>0.03929424848359133</v>
@@ -10175,10 +10175,10 @@
         <v>-0.01028445871969606</v>
       </c>
       <c r="O90" t="n">
-        <v>-230190.9807597766</v>
+        <v>-49771.27784650621</v>
       </c>
       <c r="P90" t="n">
-        <v>-230190.9807597766</v>
+        <v>-49771.27784650621</v>
       </c>
     </row>
     <row r="91">
@@ -10209,19 +10209,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G91" t="n">
-        <v>34292018.08</v>
+        <v>34560796.42</v>
       </c>
       <c r="H91" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I91" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>36554346.84712329</v>
+        <v>36823125.18712329</v>
       </c>
       <c r="L91" t="n">
         <v>0.03936107056455495</v>
@@ -10233,10 +10233,10 @@
         <v>-0.01031343600303951</v>
       </c>
       <c r="O91" t="n">
-        <v>-31416.7430700596</v>
+        <v>-31647.74542077571</v>
       </c>
       <c r="P91" t="n">
-        <v>-31416.7430700596</v>
+        <v>-31647.74542077571</v>
       </c>
     </row>
     <row r="92">
@@ -10267,19 +10267,19 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>-76962502.42</v>
+        <v>67606409.5</v>
       </c>
       <c r="H92" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I92" t="n">
-        <v>-72917433.92684932</v>
+        <v>71651477.99315068</v>
       </c>
       <c r="J92" t="n">
         <v>-62000000</v>
       </c>
       <c r="K92" t="n">
-        <v>-10917433.92684932</v>
+        <v>133651477.9931507</v>
       </c>
       <c r="L92" t="n">
         <v>0.03942868733737526</v>
@@ -10291,10 +10291,10 @@
         <v>-0.01034243719640493</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -10370,22 +10370,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D2" t="n">
-        <v>567239502.7</v>
+        <v>570524821.17</v>
       </c>
       <c r="E2" t="n">
-        <v>38693708.36000007</v>
+        <v>33204891.25999999</v>
       </c>
       <c r="F2" t="n">
-        <v>19346854.18000004</v>
+        <v>16602445.63</v>
       </c>
       <c r="G2" t="n">
-        <v>3.224475696666672</v>
+        <v>2.767074271666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1.612237848333336</v>
+        <v>1.383537135833333</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -10403,22 +10403,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D3" t="n">
-        <v>486337695.77</v>
+        <v>500370371.04</v>
       </c>
       <c r="E3" t="n">
-        <v>-42208098.56999999</v>
+        <v>-36949558.86999995</v>
       </c>
       <c r="F3" t="n">
-        <v>-42208098.56999999</v>
+        <v>-36949558.86999995</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.5173415475</v>
+        <v>-3.079129905833329</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.5173415475</v>
+        <v>-3.079129905833329</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -10436,22 +10436,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D4" t="n">
-        <v>552265384.9</v>
+        <v>561357106.7</v>
       </c>
       <c r="E4" t="n">
-        <v>23719590.56</v>
+        <v>24037176.79000008</v>
       </c>
       <c r="F4" t="n">
-        <v>11859795.28</v>
+        <v>12018588.39500004</v>
       </c>
       <c r="G4" t="n">
-        <v>1.976632546666667</v>
+        <v>2.00309806583334</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9883162733333334</v>
+        <v>1.00154903291667</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -10469,22 +10469,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D5" t="n">
-        <v>504658759.42</v>
+        <v>512211372.01</v>
       </c>
       <c r="E5" t="n">
-        <v>-23887034.91999996</v>
+        <v>-25108557.89999998</v>
       </c>
       <c r="F5" t="n">
-        <v>-23887034.91999996</v>
+        <v>-25108557.89999998</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.99058624333333</v>
+        <v>-2.092379824999998</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.99058624333333</v>
+        <v>-2.092379824999998</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -10502,22 +10502,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D6" t="n">
-        <v>523259508.19</v>
+        <v>528761317.8</v>
       </c>
       <c r="E6" t="n">
-        <v>-5286286.149999976</v>
+        <v>-8558612.109999955</v>
       </c>
       <c r="F6" t="n">
-        <v>-5286286.149999976</v>
+        <v>-8558612.109999955</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4405238458333314</v>
+        <v>-0.7132176758333296</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4405238458333314</v>
+        <v>-0.7132176758333296</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -10535,22 +10535,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D7" t="n">
-        <v>530093342.62</v>
+        <v>542004735.38</v>
       </c>
       <c r="E7" t="n">
-        <v>1547548.280000031</v>
+        <v>4684805.470000029</v>
       </c>
       <c r="F7" t="n">
-        <v>773774.1400000155</v>
+        <v>2342402.735000014</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1289623566666692</v>
+        <v>0.3904004558333357</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06448117833333462</v>
+        <v>0.1952002279166679</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -10568,22 +10568,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>528545794.34</v>
+        <v>537319929.91</v>
       </c>
       <c r="D8" t="n">
-        <v>510628634.11</v>
+        <v>521475205.63</v>
       </c>
       <c r="E8" t="n">
-        <v>-17917160.22999996</v>
+        <v>-15844724.27999997</v>
       </c>
       <c r="F8" t="n">
-        <v>-17917160.22999996</v>
+        <v>-15844724.27999997</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.49309668583333</v>
+        <v>-1.320393689999998</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.49309668583333</v>
+        <v>-1.320393689999998</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>

--- a/irrbb_calc/output/eba_sot_results.xlsx
+++ b/irrbb_calc/output/eba_sot_results.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1341385513.46</v>
+        <v>-1336496145.66</v>
       </c>
       <c r="E2" t="n">
         <v>0.999906031812547</v>
@@ -495,10 +495,10 @@
         <v>1.270756758997571e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>-17045.74707650722</v>
+        <v>-16983.61510471647</v>
       </c>
       <c r="I2" t="n">
-        <v>-17045.74707650722</v>
+        <v>-16983.61510471647</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-275079901.81</v>
+        <v>-294615437.6</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983821828874917</v>
@@ -530,10 +530,10 @@
         <v>-0.001074720528931317</v>
       </c>
       <c r="H3" t="n">
-        <v>295634.0175716178</v>
+        <v>316629.2589288033</v>
       </c>
       <c r="I3" t="n">
-        <v>147817.0087858089</v>
+        <v>158314.6294644016</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-460380476.87</v>
+        <v>-481529446.14</v>
       </c>
       <c r="E4" t="n">
         <v>0.9936563817038003</v>
@@ -565,10 +565,10 @@
         <v>-0.004131807575030844</v>
       </c>
       <c r="H4" t="n">
-        <v>1902203.541727778</v>
+        <v>1989587.013161659</v>
       </c>
       <c r="I4" t="n">
-        <v>951101.770863889</v>
+        <v>994793.5065808293</v>
       </c>
     </row>
     <row r="5">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-774901251.0700001</v>
+        <v>-787008130.14</v>
       </c>
       <c r="E5" t="n">
         <v>0.9856536327098718</v>
@@ -600,10 +600,10 @@
         <v>-0.009198654711137122</v>
       </c>
       <c r="H5" t="n">
-        <v>7128049.043821106</v>
+        <v>7239416.044015528</v>
       </c>
       <c r="I5" t="n">
-        <v>3564024.521910553</v>
+        <v>3619708.022007764</v>
       </c>
     </row>
     <row r="6">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14337145.59999999</v>
+        <v>134038813.24</v>
       </c>
       <c r="E6" t="n">
         <v>0.9761318955535195</v>
@@ -635,10 +635,10 @@
         <v>-0.01513456126685975</v>
       </c>
       <c r="H6" t="n">
-        <v>-216986.4084750885</v>
+        <v>-2028618.631117951</v>
       </c>
       <c r="I6" t="n">
-        <v>-216986.4084750885</v>
+        <v>-2028618.631117951</v>
       </c>
     </row>
     <row r="7">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>505596029.58</v>
+        <v>327140775.91</v>
       </c>
       <c r="E7" t="n">
         <v>0.9667342819189046</v>
@@ -670,10 +670,10 @@
         <v>-0.02091896253201642</v>
       </c>
       <c r="H7" t="n">
-        <v>-10576544.39912028</v>
+        <v>-6843445.633956069</v>
       </c>
       <c r="I7" t="n">
-        <v>-10576544.39912028</v>
+        <v>-6843445.633956069</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>526743176.9999999</v>
+        <v>597747588.01</v>
       </c>
       <c r="E8" t="n">
         <v>0.9524015829683793</v>
@@ -705,10 +705,10 @@
         <v>-0.02930239133147783</v>
       </c>
       <c r="H8" t="n">
-        <v>-15434834.70363989</v>
+        <v>-17515433.74131601</v>
       </c>
       <c r="I8" t="n">
-        <v>-15434834.70363989</v>
+        <v>-17515433.74131601</v>
       </c>
     </row>
     <row r="9">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>380413008.79</v>
+        <v>285154483.07</v>
       </c>
       <c r="E9" t="n">
         <v>0.9333610479054046</v>
@@ -740,10 +740,10 @@
         <v>-0.03995420556806362</v>
       </c>
       <c r="H9" t="n">
-        <v>-15199099.55396125</v>
+        <v>-11393120.8352337</v>
       </c>
       <c r="I9" t="n">
-        <v>-15199099.55396125</v>
+        <v>-11393120.8352337</v>
       </c>
     </row>
     <row r="10">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>963113319.4399999</v>
+        <v>850770561.15</v>
       </c>
       <c r="E10" t="n">
         <v>0.9066754799235061</v>
@@ -775,10 +775,10 @@
         <v>-0.05493320652757383</v>
       </c>
       <c r="H10" t="n">
-        <v>-52906902.88625471</v>
+        <v>-46735554.94323283</v>
       </c>
       <c r="I10" t="n">
-        <v>-52906902.88625471</v>
+        <v>-46735554.94323283</v>
       </c>
     </row>
     <row r="11">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1410720811.72</v>
+        <v>1364232580.07</v>
       </c>
       <c r="E11" t="n">
         <v>0.8730418834956067</v>
@@ -810,10 +810,10 @@
         <v>-0.07314463828611695</v>
       </c>
       <c r="H11" t="n">
-        <v>-103186663.4959567</v>
+        <v>-99786298.60735622</v>
       </c>
       <c r="I11" t="n">
-        <v>-103186663.4959567</v>
+        <v>-99786298.60735622</v>
       </c>
     </row>
     <row r="12">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>805426893.5699999</v>
+        <v>831336595.33</v>
       </c>
       <c r="E12" t="n">
         <v>0.839886760163754</v>
@@ -845,10 +845,10 @@
         <v>-0.0893662269184845</v>
       </c>
       <c r="H12" t="n">
-        <v>-71977962.53702669</v>
+        <v>-74293414.8239011</v>
       </c>
       <c r="I12" t="n">
-        <v>-71977962.53702669</v>
+        <v>-74293414.8239011</v>
       </c>
     </row>
     <row r="13">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>167532998.8</v>
+        <v>163716720.8</v>
       </c>
       <c r="E13" t="n">
         <v>0.8060794216350962</v>
@@ -880,10 +880,10 @@
         <v>-0.1035535335270944</v>
       </c>
       <c r="H13" t="n">
-        <v>-17348634.00813047</v>
+        <v>-16953444.93630875</v>
       </c>
       <c r="I13" t="n">
-        <v>-17348634.00813047</v>
+        <v>-16953444.93630875</v>
       </c>
     </row>
     <row r="14">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>301626600.17</v>
+        <v>298627003.45</v>
       </c>
       <c r="E14" t="n">
         <v>0.7725125366488534</v>
@@ -915,10 +915,10 @@
         <v>-0.1158645673464029</v>
       </c>
       <c r="H14" t="n">
-        <v>-34947835.52886352</v>
+        <v>-34600288.55268703</v>
       </c>
       <c r="I14" t="n">
-        <v>-34947835.52886352</v>
+        <v>-34600288.55268703</v>
       </c>
     </row>
     <row r="15">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>294575354.51</v>
+        <v>293231811.97</v>
       </c>
       <c r="E15" t="n">
         <v>0.7390723504327896</v>
@@ -950,10 +950,10 @@
         <v>-0.1263599384343468</v>
       </c>
       <c r="H15" t="n">
-        <v>-37222523.66015948</v>
+        <v>-37052753.70752116</v>
       </c>
       <c r="I15" t="n">
-        <v>-37222523.66015948</v>
+        <v>-37052753.70752116</v>
       </c>
     </row>
     <row r="16">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>241238577.56</v>
+        <v>241079539.25</v>
       </c>
       <c r="E16" t="n">
         <v>0.7058360643204235</v>
@@ -985,10 +985,10 @@
         <v>-0.135125484853127</v>
       </c>
       <c r="H16" t="n">
-        <v>-32597479.75807369</v>
+        <v>-32575989.62932472</v>
       </c>
       <c r="I16" t="n">
-        <v>-32597479.75807369</v>
+        <v>-32575989.62932472</v>
       </c>
     </row>
     <row r="17">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>151684434.17</v>
+        <v>152684438.78</v>
       </c>
       <c r="E17" t="n">
         <v>0.6740936305925465</v>
@@ -1020,10 +1020,10 @@
         <v>-0.142505629537688</v>
       </c>
       <c r="H17" t="n">
-        <v>-21615885.78246384</v>
+        <v>-21758392.06895248</v>
       </c>
       <c r="I17" t="n">
-        <v>-21615885.78246384</v>
+        <v>-21758392.06895248</v>
       </c>
     </row>
     <row r="18">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12178049.77</v>
+        <v>12791711.15</v>
       </c>
       <c r="E18" t="n">
         <v>0.5835756277426192</v>
@@ -1055,10 +1055,10 @@
         <v>-0.1566226182330579</v>
       </c>
       <c r="H18" t="n">
-        <v>-1907358.039949888</v>
+        <v>-2003471.291994</v>
       </c>
       <c r="I18" t="n">
-        <v>-1907358.039949888</v>
+        <v>-2003471.291994</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1341385513.46</v>
+        <v>-1336496145.66</v>
       </c>
       <c r="E19" t="n">
         <v>0.999906031812547</v>
@@ -1090,10 +1090,10 @@
         <v>8.119444430232381e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-108913.051360572</v>
+        <v>-108516.0618590613</v>
       </c>
       <c r="I19" t="n">
-        <v>-108913.051360572</v>
+        <v>-108516.0618590613</v>
       </c>
     </row>
     <row r="20">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-275079901.81</v>
+        <v>-294615437.6</v>
       </c>
       <c r="E20" t="n">
         <v>0.9983821828874917</v>
@@ -1125,10 +1125,10 @@
         <v>0.001073618328581993</v>
       </c>
       <c r="H20" t="n">
-        <v>-295330.824407751</v>
+        <v>-316304.5336905645</v>
       </c>
       <c r="I20" t="n">
-        <v>-295330.824407751</v>
+        <v>-316304.5336905645</v>
       </c>
     </row>
     <row r="21">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-460380476.87</v>
+        <v>-481529446.14</v>
       </c>
       <c r="E21" t="n">
         <v>0.9936563817038003</v>
@@ -1160,10 +1160,10 @@
         <v>0.004148675157226389</v>
       </c>
       <c r="H21" t="n">
-        <v>-1909969.047262607</v>
+        <v>-1997709.250674</v>
       </c>
       <c r="I21" t="n">
-        <v>-1909969.047262607</v>
+        <v>-1997709.250674</v>
       </c>
     </row>
     <row r="22">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-774901251.0700001</v>
+        <v>-787008130.14</v>
       </c>
       <c r="E22" t="n">
         <v>0.9856536327098718</v>
@@ -1195,10 +1195,10 @@
         <v>0.009282592027197278</v>
       </c>
       <c r="H22" t="n">
-        <v>-7193092.175047579</v>
+        <v>-7305475.394177002</v>
       </c>
       <c r="I22" t="n">
-        <v>-7193092.175047579</v>
+        <v>-7305475.394177002</v>
       </c>
     </row>
     <row r="23">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14337145.59999999</v>
+        <v>134038813.24</v>
       </c>
       <c r="E23" t="n">
         <v>0.9761318955535195</v>
@@ -1230,10 +1230,10 @@
         <v>0.01537076312862229</v>
       </c>
       <c r="H23" t="n">
-        <v>220372.8689581691</v>
+        <v>2060278.848353681</v>
       </c>
       <c r="I23" t="n">
-        <v>110186.4344790845</v>
+        <v>1030139.42417684</v>
       </c>
     </row>
     <row r="24">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>505596029.58</v>
+        <v>327140775.91</v>
       </c>
       <c r="E24" t="n">
         <v>0.9667342819189046</v>
@@ -1265,10 +1265,10 @@
         <v>0.02137897737503558</v>
       </c>
       <c r="H24" t="n">
-        <v>10809126.07729864</v>
+        <v>6993935.246631475</v>
       </c>
       <c r="I24" t="n">
-        <v>5404563.03864932</v>
+        <v>3496967.623315738</v>
       </c>
     </row>
     <row r="25">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>526743176.9999999</v>
+        <v>597747588.01</v>
       </c>
       <c r="E25" t="n">
         <v>0.9524015829683793</v>
@@ -1300,10 +1300,10 @@
         <v>0.03023239035728253</v>
       </c>
       <c r="H25" t="n">
-        <v>15924705.34509917</v>
+        <v>18071338.41584242</v>
       </c>
       <c r="I25" t="n">
-        <v>7962352.672549583</v>
+        <v>9035669.207921209</v>
       </c>
     </row>
     <row r="26">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>380413008.79</v>
+        <v>285154483.07</v>
       </c>
       <c r="E26" t="n">
         <v>0.9333610479054046</v>
@@ -1335,10 +1335,10 @@
         <v>0.04174093883572272</v>
       </c>
       <c r="H26" t="n">
-        <v>15878796.13221664</v>
+        <v>11902615.836557</v>
       </c>
       <c r="I26" t="n">
-        <v>7939398.06610832</v>
+        <v>5951307.9182785</v>
       </c>
     </row>
     <row r="27">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>963113319.4399999</v>
+        <v>850770561.15</v>
       </c>
       <c r="E27" t="n">
         <v>0.9066754799235061</v>
@@ -1370,10 +1370,10 @@
         <v>0.05847495853512397</v>
       </c>
       <c r="H27" t="n">
-        <v>56318011.4188796</v>
+        <v>49748773.2861504</v>
       </c>
       <c r="I27" t="n">
-        <v>28159005.7094398</v>
+        <v>24874386.6430752</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1410720811.72</v>
+        <v>1364232580.07</v>
       </c>
       <c r="E28" t="n">
         <v>0.8730418834956067</v>
@@ -1405,10 +1405,10 @@
         <v>0.07983268361646123</v>
       </c>
       <c r="H28" t="n">
-        <v>112621628.2332001</v>
+        <v>108910347.9439969</v>
       </c>
       <c r="I28" t="n">
-        <v>56310814.11660007</v>
+        <v>54455173.97199846</v>
       </c>
     </row>
     <row r="29">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>805426893.5699999</v>
+        <v>831336595.33</v>
       </c>
       <c r="E29" t="n">
         <v>0.839886760163754</v>
@@ -1440,10 +1440,10 @@
         <v>0.1000071588498553</v>
       </c>
       <c r="H29" t="n">
-        <v>80548455.28720051</v>
+        <v>83139610.94686522</v>
       </c>
       <c r="I29" t="n">
-        <v>40274227.64360026</v>
+        <v>41569805.47343261</v>
       </c>
     </row>
     <row r="30">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>167532998.8</v>
+        <v>163716720.8</v>
       </c>
       <c r="E30" t="n">
         <v>0.8060794216350962</v>
@@ -1475,10 +1475,10 @@
         <v>0.1188174585554111</v>
       </c>
       <c r="H30" t="n">
-        <v>19905845.14158275</v>
+        <v>19452404.68848182</v>
       </c>
       <c r="I30" t="n">
-        <v>9952922.570791373</v>
+        <v>9726202.344240909</v>
       </c>
     </row>
     <row r="31">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>301626600.17</v>
+        <v>298627003.45</v>
       </c>
       <c r="E31" t="n">
         <v>0.7725125366488534</v>
@@ -1510,10 +1510,10 @@
         <v>0.1363083780988569</v>
       </c>
       <c r="H31" t="n">
-        <v>41114232.66064509</v>
+        <v>40705362.49679124</v>
       </c>
       <c r="I31" t="n">
-        <v>20557116.33032255</v>
+        <v>20352681.24839562</v>
       </c>
     </row>
     <row r="32">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>294575354.51</v>
+        <v>293231811.97</v>
       </c>
       <c r="E32" t="n">
         <v>0.7390723504327896</v>
@@ -1545,10 +1545,10 @@
         <v>0.1524189448946068</v>
       </c>
       <c r="H32" t="n">
-        <v>44898864.72636896</v>
+        <v>44694083.39000115</v>
       </c>
       <c r="I32" t="n">
-        <v>22449432.36318448</v>
+        <v>22347041.69500057</v>
       </c>
     </row>
     <row r="33">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>241238577.56</v>
+        <v>241079539.25</v>
       </c>
       <c r="E33" t="n">
         <v>0.7058360643204235</v>
@@ -1580,10 +1580,10 @@
         <v>0.1671173700222426</v>
       </c>
       <c r="H33" t="n">
-        <v>40315156.62973399</v>
+        <v>40288578.565634</v>
       </c>
       <c r="I33" t="n">
-        <v>20157578.31486699</v>
+        <v>20144289.282817</v>
       </c>
     </row>
     <row r="34">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>151684434.17</v>
+        <v>152684438.78</v>
       </c>
       <c r="E34" t="n">
         <v>0.6740936305925465</v>
@@ -1615,10 +1615,10 @@
         <v>0.1807074230390667</v>
       </c>
       <c r="H34" t="n">
-        <v>27410503.21399966</v>
+        <v>27591211.47009994</v>
       </c>
       <c r="I34" t="n">
-        <v>13705251.60699983</v>
+        <v>13795605.73504997</v>
       </c>
     </row>
     <row r="35">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12178049.77</v>
+        <v>12791711.15</v>
       </c>
       <c r="E35" t="n">
         <v>0.5835756277426192</v>
@@ -1650,10 +1650,10 @@
         <v>0.2140775985160066</v>
       </c>
       <c r="H35" t="n">
-        <v>2607047.649370006</v>
+        <v>2738418.803902425</v>
       </c>
       <c r="I35" t="n">
-        <v>1303523.824685003</v>
+        <v>1369209.401951213</v>
       </c>
     </row>
     <row r="36">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-1341385513.46</v>
+        <v>-1336496145.66</v>
       </c>
       <c r="E36" t="n">
         <v>0.999906031812547</v>
@@ -1685,10 +1685,10 @@
         <v>7.797724224745117e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>-104597.5431302921</v>
+        <v>-104216.2837129146</v>
       </c>
       <c r="I36" t="n">
-        <v>-104597.5431302921</v>
+        <v>-104216.2837129146</v>
       </c>
     </row>
     <row r="37">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-275079901.81</v>
+        <v>-294615437.6</v>
       </c>
       <c r="E37" t="n">
         <v>0.9983821828874917</v>
@@ -1720,10 +1720,10 @@
         <v>0.000857634379940464</v>
       </c>
       <c r="H37" t="n">
-        <v>-235917.9810229031</v>
+        <v>-252672.3281469644</v>
       </c>
       <c r="I37" t="n">
-        <v>-235917.9810229031</v>
+        <v>-252672.3281469644</v>
       </c>
     </row>
     <row r="38">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-460380476.87</v>
+        <v>-481529446.14</v>
       </c>
       <c r="E38" t="n">
         <v>0.9936563817038003</v>
@@ -1755,10 +1755,10 @@
         <v>0.002842264830571484</v>
       </c>
       <c r="H38" t="n">
-        <v>-1308523.238089329</v>
+        <v>-1368634.209648287</v>
       </c>
       <c r="I38" t="n">
-        <v>-1308523.238089329</v>
+        <v>-1368634.209648287</v>
       </c>
     </row>
     <row r="39">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-774901251.0700001</v>
+        <v>-787008130.14</v>
       </c>
       <c r="E39" t="n">
         <v>0.9856536327098718</v>
@@ -1790,10 +1790,10 @@
         <v>0.004190624857375314</v>
       </c>
       <c r="H39" t="n">
-        <v>-3247320.444745171</v>
+        <v>-3298055.83312115</v>
       </c>
       <c r="I39" t="n">
-        <v>-3247320.444745171</v>
+        <v>-3298055.83312115</v>
       </c>
     </row>
     <row r="40">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14337145.59999999</v>
+        <v>134038813.24</v>
       </c>
       <c r="E40" t="n">
         <v>0.9761318955535195</v>
@@ -1825,10 +1825,10 @@
         <v>0.003588231255082563</v>
       </c>
       <c r="H40" t="n">
-        <v>51444.99395058941</v>
+        <v>480962.2590619425</v>
       </c>
       <c r="I40" t="n">
-        <v>25722.4969752947</v>
+        <v>240481.1295309713</v>
       </c>
     </row>
     <row r="41">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>505596029.58</v>
+        <v>327140775.91</v>
       </c>
       <c r="E41" t="n">
         <v>0.9667342819189046</v>
@@ -1860,10 +1860,10 @@
         <v>0.001347768023809648</v>
       </c>
       <c r="H41" t="n">
-        <v>681426.1616330409</v>
+        <v>440909.8770557756</v>
       </c>
       <c r="I41" t="n">
-        <v>340713.0808165204</v>
+        <v>220454.9385278878</v>
       </c>
     </row>
     <row r="42">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>526743176.9999999</v>
+        <v>597747588.01</v>
       </c>
       <c r="E42" t="n">
         <v>0.9524015829683793</v>
@@ -1895,10 +1895,10 @@
         <v>-0.003700723745374557</v>
       </c>
       <c r="H42" t="n">
-        <v>-1949330.982837933</v>
+        <v>-2212098.692688975</v>
       </c>
       <c r="I42" t="n">
-        <v>-1949330.982837933</v>
+        <v>-2212098.692688975</v>
       </c>
     </row>
     <row r="43">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>380413008.79</v>
+        <v>285154483.07</v>
       </c>
       <c r="E43" t="n">
         <v>0.9333610479054046</v>
@@ -1930,10 +1930,10 @@
         <v>-0.01168774742577749</v>
       </c>
       <c r="H43" t="n">
-        <v>-4446171.164217594</v>
+        <v>-3332813.575450305</v>
       </c>
       <c r="I43" t="n">
-        <v>-4446171.164217594</v>
+        <v>-3332813.575450305</v>
       </c>
     </row>
     <row r="44">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>963113319.4399999</v>
+        <v>850770561.15</v>
       </c>
       <c r="E44" t="n">
         <v>0.9066754799235061</v>
@@ -1965,10 +1965,10 @@
         <v>-0.02354447052112385</v>
       </c>
       <c r="H44" t="n">
-        <v>-22675993.15805682</v>
+        <v>-20030942.39723617</v>
       </c>
       <c r="I44" t="n">
-        <v>-22675993.15805682</v>
+        <v>-20030942.39723617</v>
       </c>
     </row>
     <row r="45">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1410720811.72</v>
+        <v>1364232580.07</v>
       </c>
       <c r="E45" t="n">
         <v>0.8730418834956067</v>
@@ -2000,10 +2000,10 @@
         <v>-0.03709517753986769</v>
       </c>
       <c r="H45" t="n">
-        <v>-52330938.96993966</v>
+        <v>-50606449.76336841</v>
       </c>
       <c r="I45" t="n">
-        <v>-52330938.96993966</v>
+        <v>-50606449.76336841</v>
       </c>
     </row>
     <row r="46">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>805426893.5699999</v>
+        <v>831336595.33</v>
       </c>
       <c r="E46" t="n">
         <v>0.839886760163754</v>
@@ -2035,10 +2035,10 @@
         <v>-0.04807062925974992</v>
       </c>
       <c r="H46" t="n">
-        <v>-38717377.59663552</v>
+        <v>-39962873.26417118</v>
       </c>
       <c r="I46" t="n">
-        <v>-38717377.59663552</v>
+        <v>-39962873.26417118</v>
       </c>
     </row>
     <row r="47">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>167532998.8</v>
+        <v>163716720.8</v>
       </c>
       <c r="E47" t="n">
         <v>0.8060794216350962</v>
@@ -2070,10 +2070,10 @@
         <v>-0.05707337113962196</v>
       </c>
       <c r="H47" t="n">
-        <v>-9561673.018646242</v>
+        <v>-9343865.167980267</v>
       </c>
       <c r="I47" t="n">
-        <v>-9561673.018646242</v>
+        <v>-9343865.167980267</v>
       </c>
     </row>
     <row r="48">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>301626600.17</v>
+        <v>298627003.45</v>
       </c>
       <c r="E48" t="n">
         <v>0.7725125366488534</v>
@@ -2105,10 +2105,10 @@
         <v>-0.06464828621749663</v>
       </c>
       <c r="H48" t="n">
-        <v>-19499642.77860058</v>
+        <v>-19305723.99130895</v>
       </c>
       <c r="I48" t="n">
-        <v>-19499642.77860058</v>
+        <v>-19305723.99130895</v>
       </c>
     </row>
     <row r="49">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>294575354.51</v>
+        <v>293231811.97</v>
       </c>
       <c r="E49" t="n">
         <v>0.7390723504327896</v>
@@ -2140,10 +2140,10 @@
         <v>-0.07106709005817402</v>
       </c>
       <c r="H49" t="n">
-        <v>-20934613.24788071</v>
+        <v>-20839131.58919354</v>
       </c>
       <c r="I49" t="n">
-        <v>-20934613.24788071</v>
+        <v>-20839131.58919354</v>
       </c>
     </row>
     <row r="50">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>241238577.56</v>
+        <v>241079539.25</v>
       </c>
       <c r="E50" t="n">
         <v>0.7058360643204235</v>
@@ -2175,10 +2175,10 @@
         <v>-0.07648141160373034</v>
       </c>
       <c r="H50" t="n">
-        <v>-18450266.94506479</v>
+        <v>-18438103.47061691</v>
       </c>
       <c r="I50" t="n">
-        <v>-18450266.94506479</v>
+        <v>-18438103.47061691</v>
       </c>
     </row>
     <row r="51">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>151684434.17</v>
+        <v>152684438.78</v>
       </c>
       <c r="E51" t="n">
         <v>0.6740936305925465</v>
@@ -2210,10 +2210,10 @@
         <v>-0.08112320091848635</v>
       </c>
       <c r="H51" t="n">
-        <v>-12305126.82937982</v>
+        <v>-12386250.40427627</v>
       </c>
       <c r="I51" t="n">
-        <v>-12305126.82937982</v>
+        <v>-12386250.40427627</v>
       </c>
     </row>
     <row r="52">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12178049.77</v>
+        <v>12791711.15</v>
       </c>
       <c r="E52" t="n">
         <v>0.5835756277426192</v>
@@ -2245,10 +2245,10 @@
         <v>-0.09061680299551267</v>
       </c>
       <c r="H52" t="n">
-        <v>-1103535.936877638</v>
+        <v>-1159143.969255053</v>
       </c>
       <c r="I52" t="n">
-        <v>-1103535.936877638</v>
+        <v>-1159143.969255053</v>
       </c>
     </row>
     <row r="53">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1341385513.46</v>
+        <v>-1336496145.66</v>
       </c>
       <c r="E53" t="n">
         <v>0.999906031812547</v>
@@ -2280,10 +2280,10 @@
         <v>8.749858685930256e-06</v>
       </c>
       <c r="H53" t="n">
-        <v>-11736.933686129</v>
+        <v>-11694.15240881546</v>
       </c>
       <c r="I53" t="n">
-        <v>-11736.933686129</v>
+        <v>-11694.15240881546</v>
       </c>
     </row>
     <row r="54">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-275079901.81</v>
+        <v>-294615437.6</v>
       </c>
       <c r="E54" t="n">
         <v>0.9983821828874917</v>
@@ -2315,10 +2315,10 @@
         <v>-0.00107465764159409</v>
       </c>
       <c r="H54" t="n">
-        <v>295616.7185290685</v>
+        <v>316610.7313484268</v>
       </c>
       <c r="I54" t="n">
-        <v>147808.3592645342</v>
+        <v>158305.3656742134</v>
       </c>
     </row>
     <row r="55">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-460380476.87</v>
+        <v>-481529446.14</v>
       </c>
       <c r="E55" t="n">
         <v>0.9936563817038003</v>
@@ -2350,10 +2350,10 @@
         <v>-0.003624512892459575</v>
       </c>
       <c r="H55" t="n">
-        <v>1668654.973852002</v>
+        <v>1745309.685633348</v>
       </c>
       <c r="I55" t="n">
-        <v>834327.486926001</v>
+        <v>872654.8428166742</v>
       </c>
     </row>
     <row r="56">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-774901251.0700001</v>
+        <v>-787008130.14</v>
       </c>
       <c r="E56" t="n">
         <v>0.9856536327098718</v>
@@ -2385,10 +2385,10 @@
         <v>-0.00575832701755552</v>
       </c>
       <c r="H56" t="n">
-        <v>4462134.809973955</v>
+        <v>4531850.178821012</v>
       </c>
       <c r="I56" t="n">
-        <v>2231067.404986978</v>
+        <v>2265925.089410506</v>
       </c>
     </row>
     <row r="57">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14337145.59999999</v>
+        <v>134038813.24</v>
       </c>
       <c r="E57" t="n">
         <v>0.9761318955535195</v>
@@ -2420,10 +2420,10 @@
         <v>-0.005916553585663675</v>
       </c>
       <c r="H57" t="n">
-        <v>-84826.49020786211</v>
+        <v>-793047.8210932257</v>
       </c>
       <c r="I57" t="n">
-        <v>-84826.49020786211</v>
+        <v>-793047.8210932257</v>
       </c>
     </row>
     <row r="58">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>505596029.58</v>
+        <v>327140775.91</v>
       </c>
       <c r="E58" t="n">
         <v>0.9667342819189046</v>
@@ -2455,10 +2455,10 @@
         <v>-0.004299740059850787</v>
       </c>
       <c r="H58" t="n">
-        <v>-2173931.502486629</v>
+        <v>-1406620.299390896</v>
       </c>
       <c r="I58" t="n">
-        <v>-2173931.502486629</v>
+        <v>-1406620.299390896</v>
       </c>
     </row>
     <row r="59">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>526743176.9999999</v>
+        <v>597747588.01</v>
       </c>
       <c r="E59" t="n">
         <v>0.9524015829683793</v>
@@ -2490,10 +2490,10 @@
         <v>5.935525280276188e-06</v>
       </c>
       <c r="H59" t="n">
-        <v>3126.497443296495</v>
+        <v>3547.94591985747</v>
       </c>
       <c r="I59" t="n">
-        <v>1563.248721648247</v>
+        <v>1773.972959928735</v>
       </c>
     </row>
     <row r="60">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>380413008.79</v>
+        <v>285154483.07</v>
       </c>
       <c r="E60" t="n">
         <v>0.9333610479054046</v>
@@ -2525,10 +2525,10 @@
         <v>0.007262963541339373</v>
       </c>
       <c r="H60" t="n">
-        <v>2762925.813492985</v>
+        <v>2071066.614186886</v>
       </c>
       <c r="I60" t="n">
-        <v>1381462.906746492</v>
+        <v>1035533.307093443</v>
       </c>
     </row>
     <row r="61">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>963113319.4399999</v>
+        <v>850770561.15</v>
       </c>
       <c r="E61" t="n">
         <v>0.9066754799235061</v>
@@ -2560,10 +2560,10 @@
         <v>0.01838001221226671</v>
       </c>
       <c r="H61" t="n">
-        <v>17702034.57310392</v>
+        <v>15637173.303774</v>
       </c>
       <c r="I61" t="n">
-        <v>8851017.286551962</v>
+        <v>7818586.651886999</v>
       </c>
     </row>
     <row r="62">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1410720811.72</v>
+        <v>1364232580.07</v>
       </c>
       <c r="E62" t="n">
         <v>0.8730418834956067</v>
@@ -2595,10 +2595,10 @@
         <v>0.03130191235040702</v>
       </c>
       <c r="H62" t="n">
-        <v>44158259.19935449</v>
+        <v>42703088.64692077</v>
       </c>
       <c r="I62" t="n">
-        <v>22079129.59967725</v>
+        <v>21351544.32346039</v>
       </c>
     </row>
     <row r="63">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>805426893.5699999</v>
+        <v>831336595.33</v>
       </c>
       <c r="E63" t="n">
         <v>0.839886760163754</v>
@@ -2630,10 +2630,10 @@
         <v>0.04188199495808165</v>
       </c>
       <c r="H63" t="n">
-        <v>33732885.0956021</v>
+        <v>34818035.09407982</v>
       </c>
       <c r="I63" t="n">
-        <v>16866442.54780105</v>
+        <v>17409017.54703991</v>
       </c>
     </row>
     <row r="64">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>167532998.8</v>
+        <v>163716720.8</v>
       </c>
       <c r="E64" t="n">
         <v>0.8060794216350962</v>
@@ -2665,10 +2665,10 @@
         <v>0.05069529339115386</v>
       </c>
       <c r="H64" t="n">
-        <v>8493134.526865829</v>
+        <v>8299667.193993622</v>
       </c>
       <c r="I64" t="n">
-        <v>4246567.263432914</v>
+        <v>4149833.596996811</v>
       </c>
     </row>
     <row r="65">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>301626600.17</v>
+        <v>298627003.45</v>
       </c>
       <c r="E65" t="n">
         <v>0.7725125366488534</v>
@@ -2700,10 +2700,10 @@
         <v>0.05828777906690807</v>
       </c>
       <c r="H65" t="n">
-        <v>17581144.63141158</v>
+        <v>17406304.80050639</v>
       </c>
       <c r="I65" t="n">
-        <v>8790572.315705789</v>
+        <v>8703152.400253197</v>
       </c>
     </row>
     <row r="66">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>294575354.51</v>
+        <v>293231811.97</v>
       </c>
       <c r="E66" t="n">
         <v>0.7390723504327896</v>
@@ -2735,10 +2735,10 @@
         <v>0.06493454530509235</v>
       </c>
       <c r="H66" t="n">
-        <v>19128116.70319324</v>
+        <v>19040874.37926029</v>
       </c>
       <c r="I66" t="n">
-        <v>9564058.351596618</v>
+        <v>9520437.189630143</v>
       </c>
     </row>
     <row r="67">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>241238577.56</v>
+        <v>241079539.25</v>
       </c>
       <c r="E67" t="n">
         <v>0.7058360643204235</v>
@@ -2770,10 +2770,10 @@
         <v>0.0707747284866409</v>
       </c>
       <c r="H67" t="n">
-        <v>17073594.82731246</v>
+        <v>17062338.93410324</v>
       </c>
       <c r="I67" t="n">
-        <v>8536797.413656231</v>
+        <v>8531169.46705162</v>
       </c>
     </row>
     <row r="68">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>151684434.17</v>
+        <v>152684438.78</v>
       </c>
       <c r="E68" t="n">
         <v>0.6740936305925465</v>
@@ -2805,10 +2805,10 @@
         <v>0.07601335275394061</v>
       </c>
       <c r="H68" t="n">
-        <v>11530042.40184609</v>
+        <v>11606056.10502159</v>
       </c>
       <c r="I68" t="n">
-        <v>5765021.200923046</v>
+        <v>5803028.052510795</v>
       </c>
     </row>
     <row r="69">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12178049.77</v>
+        <v>12791711.15</v>
       </c>
       <c r="E69" t="n">
         <v>0.5835756277426192</v>
@@ -2840,10 +2840,10 @@
         <v>0.08811450570325163</v>
       </c>
       <c r="H69" t="n">
-        <v>1073062.835913147</v>
+        <v>1127135.305081022</v>
       </c>
       <c r="I69" t="n">
-        <v>536531.4179565737</v>
+        <v>563567.6525405112</v>
       </c>
     </row>
     <row r="70">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-1341385513.46</v>
+        <v>-1336496145.66</v>
       </c>
       <c r="E70" t="n">
         <v>0.999906031812547</v>
@@ -2875,10 +2875,10 @@
         <v>-8.56716656616463e-07</v>
       </c>
       <c r="H70" t="n">
-        <v>1149.187312325209</v>
+        <v>1144.998509490624</v>
       </c>
       <c r="I70" t="n">
-        <v>574.5936561626044</v>
+        <v>572.4992547453122</v>
       </c>
     </row>
     <row r="71">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-275079901.81</v>
+        <v>-294615437.6</v>
       </c>
       <c r="E71" t="n">
         <v>0.9983821828874917</v>
@@ -2910,10 +2910,10 @@
         <v>-0.001389003495161578</v>
       </c>
       <c r="H71" t="n">
-        <v>382086.9450627937</v>
+        <v>409221.8725549578</v>
       </c>
       <c r="I71" t="n">
-        <v>191043.4725313969</v>
+        <v>204610.9362774789</v>
       </c>
     </row>
     <row r="72">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-460380476.87</v>
+        <v>-481529446.14</v>
       </c>
       <c r="E72" t="n">
         <v>0.9936563817038003</v>
@@ -2945,10 +2945,10 @@
         <v>-0.004887294219023786</v>
       </c>
       <c r="H72" t="n">
-        <v>2250014.843158165</v>
+        <v>2353376.078409747</v>
       </c>
       <c r="I72" t="n">
-        <v>1125007.421579082</v>
+        <v>1176688.039204874</v>
       </c>
     </row>
     <row r="73">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-774901251.0700001</v>
+        <v>-787008130.14</v>
       </c>
       <c r="E73" t="n">
         <v>0.9856536327098718</v>
@@ -2980,10 +2980,10 @@
         <v>-0.008818310314522182</v>
       </c>
       <c r="H73" t="n">
-        <v>6833319.695046725</v>
+        <v>6940081.911626377</v>
       </c>
       <c r="I73" t="n">
-        <v>3416659.847523362</v>
+        <v>3470040.955813189</v>
       </c>
     </row>
     <row r="74">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14337145.59999999</v>
+        <v>134038813.24</v>
       </c>
       <c r="E74" t="n">
         <v>0.9761318955535195</v>
@@ -3015,10 +3015,10 @@
         <v>-0.01134588039219331</v>
       </c>
       <c r="H74" t="n">
-        <v>-162667.5391430604</v>
+        <v>-1520788.342932577</v>
       </c>
       <c r="I74" t="n">
-        <v>-162667.5391430604</v>
+        <v>-1520788.342932577</v>
       </c>
     </row>
     <row r="75">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>505596029.58</v>
+        <v>327140775.91</v>
       </c>
       <c r="E75" t="n">
         <v>0.9667342819189046</v>
@@ -3050,10 +3050,10 @@
         <v>-0.01225043827690986</v>
       </c>
       <c r="H75" t="n">
-        <v>-6193772.953420481</v>
+        <v>-4007617.883145855</v>
       </c>
       <c r="I75" t="n">
-        <v>-6193772.953420481</v>
+        <v>-4007617.883145855</v>
       </c>
     </row>
     <row r="76">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>526743176.9999999</v>
+        <v>597747588.01</v>
       </c>
       <c r="E76" t="n">
         <v>0.9524015829683793</v>
@@ -3085,10 +3085,10 @@
         <v>-0.01186315201310806</v>
       </c>
       <c r="H76" t="n">
-        <v>-6248834.380618484</v>
+        <v>-7091170.502031318</v>
       </c>
       <c r="I76" t="n">
-        <v>-6248834.380618484</v>
+        <v>-7091170.502031318</v>
       </c>
     </row>
     <row r="77">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>380413008.79</v>
+        <v>285154483.07</v>
       </c>
       <c r="E77" t="n">
         <v>0.9333610479054046</v>
@@ -3120,10 +3120,10 @@
         <v>-0.009881694503488636</v>
       </c>
       <c r="H77" t="n">
-        <v>-3759125.138015717</v>
+        <v>-2817809.487997962</v>
       </c>
       <c r="I77" t="n">
-        <v>-3759125.138015717</v>
+        <v>-2817809.487997962</v>
       </c>
     </row>
     <row r="78">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>963113319.4399999</v>
+        <v>850770561.15</v>
       </c>
       <c r="E78" t="n">
         <v>0.9066754799235061</v>
@@ -3155,10 +3155,10 @@
         <v>-0.006489882432710758</v>
       </c>
       <c r="H78" t="n">
-        <v>-6250492.212543401</v>
+        <v>-5521400.919074859</v>
       </c>
       <c r="I78" t="n">
-        <v>-6250492.212543401</v>
+        <v>-5521400.919074859</v>
       </c>
     </row>
     <row r="79">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1410720811.72</v>
+        <v>1364232580.07</v>
       </c>
       <c r="E79" t="n">
         <v>0.8730418834956067</v>
@@ -3190,10 +3190,10 @@
         <v>-0.003224039784762822</v>
       </c>
       <c r="H79" t="n">
-        <v>-4548220.022178182</v>
+        <v>-4398340.113815312</v>
       </c>
       <c r="I79" t="n">
-        <v>-4548220.022178182</v>
+        <v>-4398340.113815312</v>
       </c>
     </row>
     <row r="80">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>805426893.5699999</v>
+        <v>831336595.33</v>
       </c>
       <c r="E80" t="n">
         <v>0.839886760163754</v>
@@ -3225,10 +3225,10 @@
         <v>-0.001468318235875343</v>
       </c>
       <c r="H80" t="n">
-        <v>-1182622.99549326</v>
+        <v>-1220666.68307356</v>
       </c>
       <c r="I80" t="n">
-        <v>-1182622.99549326</v>
+        <v>-1220666.68307356</v>
       </c>
     </row>
     <row r="81">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>167532998.8</v>
+        <v>163716720.8</v>
       </c>
       <c r="E81" t="n">
         <v>0.8060794216350962</v>
@@ -3260,10 +3260,10 @@
         <v>-0.000633919618590939</v>
       </c>
       <c r="H81" t="n">
-        <v>-106202.4547006923</v>
+        <v>-103783.2412064953</v>
       </c>
       <c r="I81" t="n">
-        <v>-106202.4547006923</v>
+        <v>-103783.2412064953</v>
       </c>
     </row>
     <row r="82">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>301626600.17</v>
+        <v>298627003.45</v>
       </c>
       <c r="E82" t="n">
         <v>0.7725125366488534</v>
@@ -3295,10 +3295,10 @@
         <v>-0.0002643337202767881</v>
       </c>
       <c r="H82" t="n">
-        <v>-79730.0813573754</v>
+        <v>-78937.18679704775</v>
       </c>
       <c r="I82" t="n">
-        <v>-79730.0813573754</v>
+        <v>-78937.18679704775</v>
       </c>
     </row>
     <row r="83">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>294575354.51</v>
+        <v>293231811.97</v>
       </c>
       <c r="E83" t="n">
         <v>0.7390723504327896</v>
@@ -3330,10 +3330,10 @@
         <v>-0.0001074027017012869</v>
       </c>
       <c r="H83" t="n">
-        <v>-31638.18892898835</v>
+        <v>-31493.88883034175</v>
       </c>
       <c r="I83" t="n">
-        <v>-31638.18892898835</v>
+        <v>-31493.88883034175</v>
       </c>
     </row>
     <row r="84">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>241238577.56</v>
+        <v>241079539.25</v>
       </c>
       <c r="E84" t="n">
         <v>0.7058360643204235</v>
@@ -3365,10 +3365,10 @@
         <v>-4.329964913651896e-05</v>
       </c>
       <c r="H84" t="n">
-        <v>-10445.54576654092</v>
+        <v>-10438.65946351865</v>
       </c>
       <c r="I84" t="n">
-        <v>-10445.54576654092</v>
+        <v>-10438.65946351865</v>
       </c>
     </row>
     <row r="85">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>151684434.17</v>
+        <v>152684438.78</v>
       </c>
       <c r="E85" t="n">
         <v>0.6740936305925465</v>
@@ -3400,10 +3400,10 @@
         <v>-1.696070784418247e-05</v>
       </c>
       <c r="H85" t="n">
-        <v>-2572.675372467498</v>
+        <v>-2589.636158500543</v>
       </c>
       <c r="I85" t="n">
-        <v>-2572.675372467498</v>
+        <v>-2589.636158500543</v>
       </c>
     </row>
     <row r="86">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12178049.77</v>
+        <v>12791711.15</v>
       </c>
       <c r="E86" t="n">
         <v>0.5835756277426192</v>
@@ -3435,10 +3435,10 @@
         <v>-1.008678731428958e-06</v>
       </c>
       <c r="H86" t="n">
-        <v>-12.28373979328231</v>
+        <v>-12.90272697558766</v>
       </c>
       <c r="I86" t="n">
-        <v>-12.28373979328231</v>
+        <v>-12.90272697558766</v>
       </c>
     </row>
     <row r="87">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-1341385513.46</v>
+        <v>-1336496145.66</v>
       </c>
       <c r="E87" t="n">
         <v>0.999906031812547</v>
@@ -3470,10 +3470,10 @@
         <v>9.39681874529974e-05</v>
       </c>
       <c r="H87" t="n">
-        <v>-126047.5653755445</v>
+        <v>-125588.1203455874</v>
       </c>
       <c r="I87" t="n">
-        <v>-126047.5653755445</v>
+        <v>-125588.1203455874</v>
       </c>
     </row>
     <row r="88">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-275079901.81</v>
+        <v>-294615437.6</v>
       </c>
       <c r="E88" t="n">
         <v>0.9983821828874917</v>
@@ -3505,10 +3505,10 @@
         <v>0.001387899570778783</v>
       </c>
       <c r="H88" t="n">
-        <v>-381783.2776519689</v>
+        <v>-408896.6393898434</v>
       </c>
       <c r="I88" t="n">
-        <v>-381783.2776519689</v>
+        <v>-408896.6393898434</v>
       </c>
     </row>
     <row r="89">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-460380476.87</v>
+        <v>-481529446.14</v>
       </c>
       <c r="E89" t="n">
         <v>0.9936563817038003</v>
@@ -3540,10 +3540,10 @@
         <v>0.004911064643535079</v>
       </c>
       <c r="H89" t="n">
-        <v>-2260958.282530076</v>
+        <v>-2364822.237759183</v>
       </c>
       <c r="I89" t="n">
-        <v>-2260958.282530076</v>
+        <v>-2364822.237759183</v>
       </c>
     </row>
     <row r="90">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-774901251.0700001</v>
+        <v>-787008130.14</v>
       </c>
       <c r="E90" t="n">
         <v>0.9856536327098718</v>
@@ -3575,10 +3575,10 @@
         <v>0.008895199983645741</v>
       </c>
       <c r="H90" t="n">
-        <v>-6892901.595844928</v>
+        <v>-7000594.706350393</v>
       </c>
       <c r="I90" t="n">
-        <v>-6892901.595844928</v>
+        <v>-7000594.706350393</v>
       </c>
     </row>
     <row r="91">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>14337145.59999999</v>
+        <v>134038813.24</v>
       </c>
       <c r="E91" t="n">
         <v>0.9761318955535195</v>
@@ -3610,10 +3610,10 @@
         <v>0.01147716903300178</v>
       </c>
       <c r="H91" t="n">
-        <v>164549.8435019575</v>
+        <v>1538386.116538437</v>
       </c>
       <c r="I91" t="n">
-        <v>82274.92175097877</v>
+        <v>769193.0582692183</v>
       </c>
     </row>
     <row r="92">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>505596029.58</v>
+        <v>327140775.91</v>
       </c>
       <c r="E92" t="n">
         <v>0.9667342819189046</v>
@@ -3645,10 +3645,10 @@
         <v>0.01240503278375416</v>
       </c>
       <c r="H92" t="n">
-        <v>6271935.322275835</v>
+        <v>4058192.050066322</v>
       </c>
       <c r="I92" t="n">
-        <v>3135967.661137918</v>
+        <v>2029096.025033161</v>
       </c>
     </row>
     <row r="93">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>526743176.9999999</v>
+        <v>597747588.01</v>
       </c>
       <c r="E93" t="n">
         <v>0.9524015829683793</v>
@@ -3680,10 +3680,10 @@
         <v>0.01201262797217995</v>
       </c>
       <c r="H93" t="n">
-        <v>6327569.822185132</v>
+        <v>7180519.39603202</v>
       </c>
       <c r="I93" t="n">
-        <v>3163784.911092566</v>
+        <v>3590259.69801601</v>
       </c>
     </row>
     <row r="94">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>380413008.79</v>
+        <v>285154483.07</v>
       </c>
       <c r="E94" t="n">
         <v>0.9333610479054046</v>
@@ -3715,10 +3715,10 @@
         <v>0.009987366679108822</v>
       </c>
       <c r="H94" t="n">
-        <v>3799324.208288778</v>
+        <v>2847942.382611819</v>
       </c>
       <c r="I94" t="n">
-        <v>1899662.104144389</v>
+        <v>1423971.191305909</v>
       </c>
     </row>
     <row r="95">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>963113319.4399999</v>
+        <v>850770561.15</v>
       </c>
       <c r="E95" t="n">
         <v>0.9066754799235061</v>
@@ -3750,10 +3750,10 @@
         <v>0.006535572677782708</v>
       </c>
       <c r="H95" t="n">
-        <v>6294497.096140673</v>
+        <v>5560272.834513803</v>
       </c>
       <c r="I95" t="n">
-        <v>3147248.548070337</v>
+        <v>2780136.417256902</v>
       </c>
     </row>
     <row r="96">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1410720811.72</v>
+        <v>1364232580.07</v>
       </c>
       <c r="E96" t="n">
         <v>0.8730418834956067</v>
@@ -3785,10 +3785,10 @@
         <v>0.003235551599104936</v>
       </c>
       <c r="H96" t="n">
-        <v>4564459.978251259</v>
+        <v>4414044.905996541</v>
       </c>
       <c r="I96" t="n">
-        <v>2282229.989125629</v>
+        <v>2207022.45299827</v>
       </c>
     </row>
     <row r="97">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>805426893.5699999</v>
+        <v>831336595.33</v>
       </c>
       <c r="E97" t="n">
         <v>0.839886760163754</v>
@@ -3820,10 +3820,10 @@
         <v>0.001470791926687531</v>
       </c>
       <c r="H97" t="n">
-        <v>1184615.372599773</v>
+        <v>1222723.152771263</v>
       </c>
       <c r="I97" t="n">
-        <v>592307.6862998867</v>
+        <v>611361.5763856317</v>
       </c>
     </row>
     <row r="98">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>167532998.8</v>
+        <v>163716720.8</v>
       </c>
       <c r="E98" t="n">
         <v>0.8060794216350962</v>
@@ -3855,10 +3855,10 @@
         <v>0.000634385103338575</v>
       </c>
       <c r="H98" t="n">
-        <v>106280.4387563594</v>
+        <v>103859.4488429606</v>
       </c>
       <c r="I98" t="n">
-        <v>53140.21937817969</v>
+        <v>51929.72442148032</v>
       </c>
     </row>
     <row r="99">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>301626600.17</v>
+        <v>298627003.45</v>
       </c>
       <c r="E99" t="n">
         <v>0.7725125366488534</v>
@@ -3890,10 +3890,10 @@
         <v>0.0002641556154886482</v>
       </c>
       <c r="H99" t="n">
-        <v>79676.36021565476</v>
+        <v>78883.99989786542</v>
       </c>
       <c r="I99" t="n">
-        <v>39838.18010782738</v>
+        <v>39441.99994893271</v>
       </c>
     </row>
     <row r="100">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>294575354.51</v>
+        <v>293231811.97</v>
       </c>
       <c r="E100" t="n">
         <v>0.7390723504327896</v>
@@ -3925,10 +3925,10 @@
         <v>0.0001072133542818765</v>
       </c>
       <c r="H100" t="n">
-        <v>31582.41184579</v>
+        <v>31438.36614345621</v>
       </c>
       <c r="I100" t="n">
-        <v>15791.205922895</v>
+        <v>15719.1830717281</v>
       </c>
     </row>
     <row r="101">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>241238577.56</v>
+        <v>241079539.25</v>
       </c>
       <c r="E101" t="n">
         <v>0.7058360643204235</v>
@@ -3960,10 +3960,10 @@
         <v>4.218442338066453e-05</v>
       </c>
       <c r="H101" t="n">
-        <v>10176.51029154032</v>
+        <v>10169.80135213753</v>
       </c>
       <c r="I101" t="n">
-        <v>5088.255145770158</v>
+        <v>5084.900676068765</v>
       </c>
     </row>
     <row r="102">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>151684434.17</v>
+        <v>152684438.78</v>
       </c>
       <c r="E102" t="n">
         <v>0.6740936305925465</v>
@@ -3995,10 +3995,10 @@
         <v>1.659944883869446e-05</v>
       </c>
       <c r="H102" t="n">
-        <v>2517.878004631233</v>
+        <v>2534.477529993387</v>
       </c>
       <c r="I102" t="n">
-        <v>1258.939002315617</v>
+        <v>1267.238764996694</v>
       </c>
     </row>
     <row r="103">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12178049.77</v>
+        <v>12791711.15</v>
       </c>
       <c r="E103" t="n">
         <v>0.5835756277426192</v>
@@ -4030,10 +4030,10 @@
         <v>8.933136881328352e-07</v>
       </c>
       <c r="H103" t="n">
-        <v>10.87881855430392</v>
+        <v>11.42701066493641</v>
       </c>
       <c r="I103" t="n">
-        <v>5.439409277151962</v>
+        <v>5.713505332468205</v>
       </c>
     </row>
     <row r="104">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-1341385513.46</v>
+        <v>-1336496145.66</v>
       </c>
       <c r="E104" t="n">
         <v>0.999906031812547</v>
@@ -4065,10 +4065,10 @@
         <v>6.06503826584559e-05</v>
       </c>
       <c r="H104" t="n">
-        <v>-81355.54468385836</v>
+        <v>-81059.00265583041</v>
       </c>
       <c r="I104" t="n">
-        <v>-81355.54468385836</v>
+        <v>-81059.00265583041</v>
       </c>
     </row>
     <row r="105">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-275079901.81</v>
+        <v>-294615437.6</v>
       </c>
       <c r="E105" t="n">
         <v>0.9983821828874917</v>
@@ -4100,10 +4100,10 @@
         <v>0.0004286357166750632</v>
       </c>
       <c r="H105" t="n">
-        <v>-117909.0708552354</v>
+        <v>-126282.6992392133</v>
       </c>
       <c r="I105" t="n">
-        <v>-117909.0708552354</v>
+        <v>-126282.6992392133</v>
       </c>
     </row>
     <row r="106">
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-460380476.87</v>
+        <v>-481529446.14</v>
       </c>
       <c r="E106" t="n">
         <v>0.9936563817038003</v>
@@ -4135,10 +4135,10 @@
         <v>0.001657282796573178</v>
       </c>
       <c r="H106" t="n">
-        <v>-762980.6441948072</v>
+        <v>-798030.4671312328</v>
       </c>
       <c r="I106" t="n">
-        <v>-762980.6441948072</v>
+        <v>-798030.4671312328</v>
       </c>
     </row>
     <row r="107">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-774901251.0700001</v>
+        <v>-787008130.14</v>
       </c>
       <c r="E107" t="n">
         <v>0.9856536327098718</v>
@@ -4170,10 +4170,10 @@
         <v>0.003701791136432875</v>
       </c>
       <c r="H107" t="n">
-        <v>-2868522.582821672</v>
+        <v>-2913339.720452862</v>
       </c>
       <c r="I107" t="n">
-        <v>-2868522.582821672</v>
+        <v>-2913339.720452862</v>
       </c>
     </row>
     <row r="108">
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>14337145.59999999</v>
+        <v>134038813.24</v>
       </c>
       <c r="E108" t="n">
         <v>0.9761318955535195</v>
@@ -4205,10 +4205,10 @@
         <v>0.00611886473883394</v>
       </c>
       <c r="H108" t="n">
-        <v>87727.05466736809</v>
+        <v>820165.3679693838</v>
       </c>
       <c r="I108" t="n">
-        <v>43863.52733368405</v>
+        <v>410082.6839846919</v>
       </c>
     </row>
     <row r="109">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>505596029.58</v>
+        <v>327140775.91</v>
       </c>
       <c r="E109" t="n">
         <v>0.9667342819189046</v>
@@ -4240,10 +4240,10 @@
         <v>0.008494727267819302</v>
       </c>
       <c r="H109" t="n">
-        <v>4294900.3789744</v>
+        <v>2778971.669538241</v>
       </c>
       <c r="I109" t="n">
-        <v>2147450.1894872</v>
+        <v>1389485.83476912</v>
       </c>
     </row>
     <row r="110">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>526743176.9999999</v>
+        <v>597747588.01</v>
       </c>
       <c r="E110" t="n">
         <v>0.9524015829683793</v>
@@ -4275,10 +4275,10 @@
         <v>0.01197966122818617</v>
       </c>
       <c r="H110" t="n">
-        <v>6310204.814718503</v>
+        <v>7160813.604325196</v>
       </c>
       <c r="I110" t="n">
-        <v>3155102.407359251</v>
+        <v>3580406.802162598</v>
       </c>
     </row>
     <row r="111">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>380413008.79</v>
+        <v>285154483.07</v>
       </c>
       <c r="E111" t="n">
         <v>0.9333610479054046</v>
@@ -4310,10 +4310,10 @@
         <v>0.01647754477361008</v>
       </c>
       <c r="H111" t="n">
-        <v>6268272.384800948</v>
+        <v>4698645.762181561</v>
       </c>
       <c r="I111" t="n">
-        <v>3134136.192400474</v>
+        <v>2349322.881090781</v>
       </c>
     </row>
     <row r="112">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>963113319.4399999</v>
+        <v>850770561.15</v>
       </c>
       <c r="E112" t="n">
         <v>0.9066754799235061</v>
@@ -4345,10 +4345,10 @@
         <v>0.02295203256100853</v>
       </c>
       <c r="H112" t="n">
-        <v>22105408.26772789</v>
+        <v>19526913.6214623</v>
       </c>
       <c r="I112" t="n">
-        <v>11052704.13386394</v>
+        <v>9763456.810731148</v>
       </c>
     </row>
     <row r="113">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1410720811.72</v>
+        <v>1364232580.07</v>
       </c>
       <c r="E113" t="n">
         <v>0.8730418834956067</v>
@@ -4380,10 +4380,10 @@
         <v>0.03109727088065561</v>
       </c>
       <c r="H113" t="n">
-        <v>43869567.21903521</v>
+        <v>42423910.08665249</v>
       </c>
       <c r="I113" t="n">
-        <v>21934783.6095176</v>
+        <v>21211955.04332624</v>
       </c>
     </row>
     <row r="114">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>805426893.5699999</v>
+        <v>831336595.33</v>
       </c>
       <c r="E114" t="n">
         <v>0.839886760163754</v>
@@ -4415,10 +4415,10 @@
         <v>0.0386581374619398</v>
       </c>
       <c r="H114" t="n">
-        <v>31136303.56717221</v>
+        <v>32137924.37940816</v>
       </c>
       <c r="I114" t="n">
-        <v>15568151.78358611</v>
+        <v>16068962.18970408</v>
       </c>
     </row>
     <row r="115">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>167532998.8</v>
+        <v>163716720.8</v>
       </c>
       <c r="E115" t="n">
         <v>0.8060794216350962</v>
@@ -4450,10 +4450,10 @@
         <v>0.04557620122769612</v>
       </c>
       <c r="H115" t="n">
-        <v>7635517.665588174</v>
+        <v>7461586.211519344</v>
       </c>
       <c r="I115" t="n">
-        <v>3817758.832794087</v>
+        <v>3730793.105759672</v>
       </c>
     </row>
     <row r="116">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>301626600.17</v>
+        <v>298627003.45</v>
       </c>
       <c r="E116" t="n">
         <v>0.7725125366488534</v>
@@ -4485,10 +4485,10 @@
         <v>0.05188104408575822</v>
       </c>
       <c r="H116" t="n">
-        <v>15648702.94085714</v>
+        <v>15493080.73118732</v>
       </c>
       <c r="I116" t="n">
-        <v>7824351.470428569</v>
+        <v>7746540.365593661</v>
       </c>
     </row>
     <row r="117">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>294575354.51</v>
+        <v>293231811.97</v>
       </c>
       <c r="E117" t="n">
         <v>0.7390723504327896</v>
@@ -4520,10 +4520,10 @@
         <v>0.05756191118833565</v>
       </c>
       <c r="H117" t="n">
-        <v>16956320.39457711</v>
+        <v>16878983.51821188</v>
       </c>
       <c r="I117" t="n">
-        <v>8478160.197288554</v>
+        <v>8439491.759105939</v>
       </c>
     </row>
     <row r="118">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>241238577.56</v>
+        <v>241079539.25</v>
       </c>
       <c r="E118" t="n">
         <v>0.7058360643204235</v>
@@ -4555,10 +4555,10 @@
         <v>0.06261909581715475</v>
       </c>
       <c r="H118" t="n">
-        <v>15106141.60302376</v>
+        <v>15096182.76785127</v>
       </c>
       <c r="I118" t="n">
-        <v>7553070.801511878</v>
+        <v>7548091.383925634</v>
       </c>
     </row>
     <row r="119">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>151684434.17</v>
+        <v>152684438.78</v>
       </c>
       <c r="E119" t="n">
         <v>0.6740936305925465</v>
@@ -4590,10 +4590,10 @@
         <v>0.06717920059908133</v>
       </c>
       <c r="H119" t="n">
-        <v>10190039.03086458</v>
+        <v>10257218.54115977</v>
       </c>
       <c r="I119" t="n">
-        <v>5095019.515432288</v>
+        <v>5128609.270579887</v>
       </c>
     </row>
     <row r="120">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12178049.77</v>
+        <v>12791711.15</v>
       </c>
       <c r="E120" t="n">
         <v>0.5835756277426192</v>
@@ -4625,10 +4625,10 @@
         <v>0.07770212208989746</v>
       </c>
       <c r="H120" t="n">
-        <v>946260.3100453877</v>
+        <v>993943.1015160027</v>
       </c>
       <c r="I120" t="n">
-        <v>473130.1550226939</v>
+        <v>496971.5507580013</v>
       </c>
     </row>
   </sheetData>
@@ -4704,22 +4704,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D2" t="n">
-        <v>2041758857.86</v>
+        <v>1794233839.47</v>
       </c>
       <c r="E2" t="n">
-        <v>-129744181.2500002</v>
+        <v>-122122222.0699999</v>
       </c>
       <c r="F2" t="n">
-        <v>-129744181.2500002</v>
+        <v>-122122222.0699999</v>
       </c>
       <c r="G2" t="n">
-        <v>-10.81201510416669</v>
+        <v>-10.17685183916666</v>
       </c>
       <c r="H2" t="n">
-        <v>-10.81201510416669</v>
+        <v>-10.17685183916666</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4737,22 +4737,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D3" t="n">
-        <v>2312912010.57</v>
+        <v>2049892910.4</v>
       </c>
       <c r="E3" t="n">
-        <v>141408971.46</v>
+        <v>133536848.8600001</v>
       </c>
       <c r="F3" t="n">
-        <v>70704485.73000002</v>
+        <v>66768424.43000007</v>
       </c>
       <c r="G3" t="n">
-        <v>11.784080955</v>
+        <v>11.12807073833334</v>
       </c>
       <c r="H3" t="n">
-        <v>5.892040477500002</v>
+        <v>5.564035369166672</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4770,22 +4770,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D4" t="n">
-        <v>2125095296.74</v>
+        <v>1870259103.15</v>
       </c>
       <c r="E4" t="n">
-        <v>-46407742.37000012</v>
+        <v>-46096958.38999987</v>
       </c>
       <c r="F4" t="n">
-        <v>-46407742.37000012</v>
+        <v>-46096958.38999987</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.867311864166677</v>
+        <v>-3.841413199166656</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.867311864166677</v>
+        <v>-3.841413199166656</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4803,22 +4803,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D5" t="n">
-        <v>2206059950.06</v>
+        <v>1951602159.12</v>
       </c>
       <c r="E5" t="n">
-        <v>34556910.94999981</v>
+        <v>35246097.57999992</v>
       </c>
       <c r="F5" t="n">
-        <v>17278455.4749999</v>
+        <v>17623048.78999996</v>
       </c>
       <c r="G5" t="n">
-        <v>2.879742579166651</v>
+        <v>2.937174798333327</v>
       </c>
       <c r="H5" t="n">
-        <v>1.439871289583325</v>
+        <v>1.468587399166663</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4836,22 +4836,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D6" t="n">
-        <v>2147302576.07</v>
+        <v>1895858582.06</v>
       </c>
       <c r="E6" t="n">
-        <v>-24200463.0400002</v>
+        <v>-20497479.48000002</v>
       </c>
       <c r="F6" t="n">
-        <v>-24200463.0400002</v>
+        <v>-20497479.48000002</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.01670525333335</v>
+        <v>-1.708123290000002</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.01670525333335</v>
+        <v>-1.708123290000002</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4869,22 +4869,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D7" t="n">
-        <v>2196126359.83</v>
+        <v>1937223352.26</v>
       </c>
       <c r="E7" t="n">
-        <v>24623320.71999979</v>
+        <v>20867290.72000003</v>
       </c>
       <c r="F7" t="n">
-        <v>12311660.3599999</v>
+        <v>10433645.36000001</v>
       </c>
       <c r="G7" t="n">
-        <v>2.051943393333316</v>
+        <v>1.738940893333336</v>
       </c>
       <c r="H7" t="n">
-        <v>1.025971696666658</v>
+        <v>0.8694704466666678</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4902,22 +4902,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2171503039.11</v>
+        <v>1916356061.54</v>
       </c>
       <c r="D8" t="n">
-        <v>2226642923.68</v>
+        <v>1968379211.04</v>
       </c>
       <c r="E8" t="n">
-        <v>55139884.56999969</v>
+        <v>52023149.5</v>
       </c>
       <c r="F8" t="n">
-        <v>27569942.28499985</v>
+        <v>26011574.75</v>
       </c>
       <c r="G8" t="n">
-        <v>4.594990380833308</v>
+        <v>4.335262458333333</v>
       </c>
       <c r="H8" t="n">
-        <v>2.297495190416654</v>
+        <v>2.167631229166667</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5047,19 +5047,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G2" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="J2" t="n">
         <v>-620000000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="L2" t="n">
         <v>0.03432749872940843</v>
@@ -5071,10 +5071,10 @@
         <v>0.02500481880599148</v>
       </c>
       <c r="O2" t="n">
-        <v>-32494633.94614996</v>
+        <v>-32631303.37430746</v>
       </c>
       <c r="P2" t="n">
-        <v>-32494633.94614996</v>
+        <v>-32631303.37430746</v>
       </c>
     </row>
     <row r="3">
@@ -5105,19 +5105,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="H3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="J3" t="n">
         <v>-62000000</v>
       </c>
       <c r="K3" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="L3" t="n">
         <v>0.03782665436246635</v>
@@ -5129,10 +5129,10 @@
         <v>0.0251058158502353</v>
       </c>
       <c r="O3" t="n">
-        <v>17770533.45230579</v>
+        <v>17714781.8447465</v>
       </c>
       <c r="P3" t="n">
-        <v>8885266.726152895</v>
+        <v>8857390.922373248</v>
       </c>
     </row>
     <row r="4">
@@ -5163,19 +5163,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="H4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="L4" t="n">
         <v>0.03830470017405307</v>
@@ -5187,10 +5187,10 @@
         <v>0.02521323244800655</v>
       </c>
       <c r="O4" t="n">
-        <v>16811911.25825904</v>
+        <v>16199877.06434811</v>
       </c>
       <c r="P4" t="n">
-        <v>8405955.629129518</v>
+        <v>8099938.532174057</v>
       </c>
     </row>
     <row r="5">
@@ -5221,19 +5221,19 @@
         <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="H5" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I5" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="J5" t="n">
         <v>-124000000</v>
       </c>
       <c r="K5" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="L5" t="n">
         <v>0.03852218097221538</v>
@@ -5245,10 +5245,10 @@
         <v>0.02532026333962101</v>
       </c>
       <c r="O5" t="n">
-        <v>16336466.04784997</v>
+        <v>21234360.61087049</v>
       </c>
       <c r="P5" t="n">
-        <v>8168233.023924986</v>
+        <v>10617180.30543524</v>
       </c>
     </row>
     <row r="6">
@@ -5279,19 +5279,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="H6" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I6" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="J6" t="n">
         <v>-62000000</v>
       </c>
       <c r="K6" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="L6" t="n">
         <v>0.03873510939427094</v>
@@ -5303,10 +5303,10 @@
         <v>0.02542872476626745</v>
       </c>
       <c r="O6" t="n">
-        <v>-5790491.76086683</v>
+        <v>-5671815.360242249</v>
       </c>
       <c r="P6" t="n">
-        <v>-5790491.76086683</v>
+        <v>-5671815.360242249</v>
       </c>
     </row>
     <row r="7">
@@ -5337,19 +5337,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="H7" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I7" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="J7" t="n">
         <v>-62000000</v>
       </c>
       <c r="K7" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="L7" t="n">
         <v>0.03888939094511485</v>
@@ -5361,10 +5361,10 @@
         <v>0.02553821260711615</v>
       </c>
       <c r="O7" t="n">
-        <v>-5105458.722928206</v>
+        <v>-5086871.529461038</v>
       </c>
       <c r="P7" t="n">
-        <v>-5105458.722928206</v>
+        <v>-5086871.529461038</v>
       </c>
     </row>
     <row r="8">
@@ -5395,19 +5395,19 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="H8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="J8" t="n">
         <v>-31000000</v>
       </c>
       <c r="K8" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="L8" t="n">
         <v>0.03901400018340251</v>
@@ -5419,10 +5419,10 @@
         <v>0.02564775160277089</v>
       </c>
       <c r="O8" t="n">
-        <v>3940141.833224572</v>
+        <v>667437.9128207581</v>
       </c>
       <c r="P8" t="n">
-        <v>1970070.916612286</v>
+        <v>333718.956410379</v>
       </c>
     </row>
     <row r="9">
@@ -5453,19 +5453,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="H9" t="n">
         <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="J9" t="n">
         <v>-31000000</v>
       </c>
       <c r="K9" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="L9" t="n">
         <v>0.03908855826627113</v>
@@ -5477,10 +5477,10 @@
         <v>0.02575828679253624</v>
       </c>
       <c r="O9" t="n">
-        <v>-1986148.711206025</v>
+        <v>-526190.7388415849</v>
       </c>
       <c r="P9" t="n">
-        <v>-1986148.711206025</v>
+        <v>-526190.7388415849</v>
       </c>
     </row>
     <row r="10">
@@ -5511,19 +5511,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="H10" t="n">
         <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="J10" t="n">
         <v>-31000000</v>
       </c>
       <c r="K10" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="L10" t="n">
         <v>0.03915884386251234</v>
@@ -5535,10 +5535,10 @@
         <v>0.02586772256944581</v>
       </c>
       <c r="O10" t="n">
-        <v>-149667.0570893367</v>
+        <v>-155238.837347826</v>
       </c>
       <c r="P10" t="n">
-        <v>-149667.0570893367</v>
+        <v>-155238.837347826</v>
       </c>
     </row>
     <row r="11">
@@ -5569,19 +5569,19 @@
         <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="H11" t="n">
         <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="J11" t="n">
         <v>-31000000</v>
       </c>
       <c r="K11" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="L11" t="n">
         <v>0.03922681220647117</v>
@@ -5593,10 +5593,10 @@
         <v>0.02597850453979926</v>
       </c>
       <c r="O11" t="n">
-        <v>-89137.46036406193</v>
+        <v>-123518.1300839188</v>
       </c>
       <c r="P11" t="n">
-        <v>-89137.46036406193</v>
+        <v>-123518.1300839188</v>
       </c>
     </row>
     <row r="12">
@@ -5627,19 +5627,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="H12" t="n">
         <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="J12" t="n">
         <v>-31000000</v>
       </c>
       <c r="K12" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="L12" t="n">
         <v>0.03929424848359133</v>
@@ -5651,10 +5651,10 @@
         <v>0.02608953222428303</v>
       </c>
       <c r="O12" t="n">
-        <v>-8536.538861164656</v>
+        <v>-73224.96182435016</v>
       </c>
       <c r="P12" t="n">
-        <v>-8536.538861164656</v>
+        <v>-73224.96182435016</v>
       </c>
     </row>
     <row r="13">
@@ -5685,19 +5685,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G13" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="H13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="L13" t="n">
         <v>0.03936107056455495</v>
@@ -5709,10 +5709,10 @@
         <v>0.02620112954634799</v>
       </c>
       <c r="O13" t="n">
-        <v>80400.62277743395</v>
+        <v>82865.02185148366</v>
       </c>
       <c r="P13" t="n">
-        <v>40200.31138871697</v>
+        <v>41432.51092574183</v>
       </c>
     </row>
     <row r="14">
@@ -5743,19 +5743,19 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="H14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="J14" t="n">
         <v>-62000000</v>
       </c>
       <c r="K14" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="L14" t="n">
         <v>0.03942868733737526</v>
@@ -5767,10 +5767,10 @@
         <v>0.02631330603469872</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -5801,19 +5801,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G15" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="J15" t="n">
         <v>-620000000</v>
       </c>
       <c r="K15" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="L15" t="n">
         <v>0.03432749872940843</v>
@@ -5825,10 +5825,10 @@
         <v>-0.02499999878494696</v>
       </c>
       <c r="O15" t="n">
-        <v>17030836.66542407</v>
+        <v>17167479.74867882</v>
       </c>
       <c r="P15" t="n">
-        <v>8515418.332712036</v>
+        <v>8583739.874339411</v>
       </c>
     </row>
     <row r="16">
@@ -5859,19 +5859,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="H16" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I16" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="J16" t="n">
         <v>-62000000</v>
       </c>
       <c r="K16" t="n">
-        <v>834173133.4710958</v>
+        <v>831750589.7910959</v>
       </c>
       <c r="L16" t="n">
         <v>0.03782665436246635</v>
@@ -5883,10 +5883,10 @@
         <v>-0.02505175249492542</v>
       </c>
       <c r="O16" t="n">
-        <v>-19156040.63783142</v>
+        <v>-19100409.08687521</v>
       </c>
       <c r="P16" t="n">
-        <v>-19156040.63783142</v>
+        <v>-19100409.08687521</v>
       </c>
     </row>
     <row r="17">
@@ -5917,19 +5917,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="H17" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I17" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="L17" t="n">
         <v>0.03830470017405307</v>
@@ -5941,10 +5941,10 @@
         <v>-0.02510607109988339</v>
       </c>
       <c r="O17" t="n">
-        <v>-16740457.22797247</v>
+        <v>-16131024.30343279</v>
       </c>
       <c r="P17" t="n">
-        <v>-16740457.22797247</v>
+        <v>-16131024.30343279</v>
       </c>
     </row>
     <row r="18">
@@ -5975,19 +5975,19 @@
         <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="H18" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I18" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="J18" t="n">
         <v>-124000000</v>
       </c>
       <c r="K18" t="n">
-        <v>984257827.4287672</v>
+        <v>1242174816.538767</v>
       </c>
       <c r="L18" t="n">
         <v>0.03852218097221538</v>
@@ -5999,10 +5999,10 @@
         <v>-0.02516160099667442</v>
       </c>
       <c r="O18" t="n">
-        <v>-18574127.0487122</v>
+        <v>-23441330.32639927</v>
       </c>
       <c r="P18" t="n">
-        <v>-18574127.0487122</v>
+        <v>-23441330.32639927</v>
       </c>
     </row>
     <row r="19">
@@ -6033,19 +6033,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="H19" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I19" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="J19" t="n">
         <v>-62000000</v>
       </c>
       <c r="K19" t="n">
-        <v>-279571892.4616438</v>
+        <v>-272571360.4816439</v>
       </c>
       <c r="L19" t="n">
         <v>0.03873510939427094</v>
@@ -6057,10 +6057,10 @@
         <v>-0.02521743137943178</v>
       </c>
       <c r="O19" t="n">
-        <v>4700056.675846255</v>
+        <v>4582366.385962811</v>
       </c>
       <c r="P19" t="n">
-        <v>2350028.337923128</v>
+        <v>2291183.192981406</v>
       </c>
     </row>
     <row r="20">
@@ -6091,19 +6091,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="H20" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I20" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="J20" t="n">
         <v>-62000000</v>
       </c>
       <c r="K20" t="n">
-        <v>-280710552.5447945</v>
+        <v>-279462863.0247945</v>
       </c>
       <c r="L20" t="n">
         <v>0.03888939094511485</v>
@@ -6115,10 +6115,10 @@
         <v>-0.02527289166469284</v>
       </c>
       <c r="O20" t="n">
-        <v>4138380.973767051</v>
+        <v>4119986.885892807</v>
       </c>
       <c r="P20" t="n">
-        <v>2069190.486883525</v>
+        <v>2059993.442946403</v>
       </c>
     </row>
     <row r="21">
@@ -6149,19 +6149,19 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="H21" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I21" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="J21" t="n">
         <v>-31000000</v>
       </c>
       <c r="K21" t="n">
-        <v>338250467.3508219</v>
+        <v>83046504.75082195</v>
       </c>
       <c r="L21" t="n">
         <v>0.03901400018340251</v>
@@ -6173,10 +6173,10 @@
         <v>-0.02532890719506886</v>
       </c>
       <c r="O21" t="n">
-        <v>-4283757.348108819</v>
+        <v>-1051738.605854207</v>
       </c>
       <c r="P21" t="n">
-        <v>-4283757.348108819</v>
+        <v>-1051738.605854207</v>
       </c>
     </row>
     <row r="22">
@@ -6207,19 +6207,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="H22" t="n">
         <v>2250000</v>
       </c>
       <c r="I22" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="J22" t="n">
         <v>-31000000</v>
       </c>
       <c r="K22" t="n">
-        <v>-154057218.49</v>
+        <v>-18027242.50999999</v>
       </c>
       <c r="L22" t="n">
         <v>0.03908855826627113</v>
@@ -6231,10 +6231,10 @@
         <v>-0.02538363335203554</v>
       </c>
       <c r="O22" t="n">
-        <v>1629388.312243579</v>
+        <v>190665.3809258619</v>
       </c>
       <c r="P22" t="n">
-        <v>814694.1561217897</v>
+        <v>95332.69046293097</v>
       </c>
     </row>
     <row r="23">
@@ -6265,19 +6265,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="H23" t="n">
         <v>2250000</v>
       </c>
       <c r="I23" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="J23" t="n">
         <v>-31000000</v>
       </c>
       <c r="K23" t="n">
-        <v>13642415.84999999</v>
+        <v>12996230.59999999</v>
       </c>
       <c r="L23" t="n">
         <v>0.03915884386251234</v>
@@ -6289,10 +6289,10 @@
         <v>-0.02543993459508764</v>
       </c>
       <c r="O23" t="n">
-        <v>-115687.3889809956</v>
+        <v>-110207.7521488922</v>
       </c>
       <c r="P23" t="n">
-        <v>-115687.3889809956</v>
+        <v>-110207.7521488922</v>
       </c>
     </row>
     <row r="24">
@@ -6323,19 +6323,19 @@
         <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="H24" t="n">
         <v>2250000</v>
       </c>
       <c r="I24" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="J24" t="n">
         <v>-31000000</v>
       </c>
       <c r="K24" t="n">
-        <v>17275197.6</v>
+        <v>11981487.23</v>
       </c>
       <c r="L24" t="n">
         <v>0.03922681220647117</v>
@@ -6347,10 +6347,10 @@
         <v>-0.02549552338669633</v>
       </c>
       <c r="O24" t="n">
-        <v>-110110.0511051501</v>
+        <v>-76368.57196996707</v>
       </c>
       <c r="P24" t="n">
-        <v>-110110.0511051501</v>
+        <v>-76368.57196996707</v>
       </c>
     </row>
     <row r="25">
@@ -6381,19 +6381,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="H25" t="n">
         <v>2250000</v>
       </c>
       <c r="I25" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="J25" t="n">
         <v>-31000000</v>
       </c>
       <c r="K25" t="n">
-        <v>29036789.9</v>
+        <v>14159921.49</v>
       </c>
       <c r="L25" t="n">
         <v>0.03929424848359133</v>
@@ -6405,10 +6405,10 @@
         <v>-0.02555147156878314</v>
       </c>
       <c r="O25" t="n">
-        <v>-123655.4519297632</v>
+        <v>-60301.13856132274</v>
       </c>
       <c r="P25" t="n">
-        <v>-123655.4519297632</v>
+        <v>-60301.13856132274</v>
       </c>
     </row>
     <row r="26">
@@ -6439,19 +6439,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G26" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="H26" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I26" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="L26" t="n">
         <v>0.03936107056455495</v>
@@ -6463,10 +6463,10 @@
         <v>-0.02560744979333988</v>
       </c>
       <c r="O26" t="n">
-        <v>-78578.86078859412</v>
+        <v>-80987.4201389782</v>
       </c>
       <c r="P26" t="n">
-        <v>-78578.86078859412</v>
+        <v>-80987.4201389782</v>
       </c>
     </row>
     <row r="27">
@@ -6497,19 +6497,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="H27" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I27" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="J27" t="n">
         <v>-62000000</v>
       </c>
       <c r="K27" t="n">
-        <v>133651477.9931507</v>
+        <v>-13511470.05684932</v>
       </c>
       <c r="L27" t="n">
         <v>0.03942868733737526</v>
@@ -6521,10 +6521,10 @@
         <v>-0.02566354060598441</v>
       </c>
       <c r="O27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -6555,19 +6555,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G28" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="J28" t="n">
         <v>-620000000</v>
       </c>
       <c r="K28" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="L28" t="n">
         <v>0.03432749872940843</v>
@@ -6579,10 +6579,10 @@
         <v>-0.02264935222023312</v>
       </c>
       <c r="O28" t="n">
-        <v>15429497.47952432</v>
+        <v>15553292.57838485</v>
       </c>
       <c r="P28" t="n">
-        <v>7714748.739762162</v>
+        <v>7776646.289192423</v>
       </c>
     </row>
     <row r="29">
@@ -6613,19 +6613,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="H29" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I29" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="J29" t="n">
         <v>-62000000</v>
       </c>
       <c r="K29" t="n">
-        <v>834173133.4710958</v>
+        <v>831750589.7910959</v>
       </c>
       <c r="L29" t="n">
         <v>0.03782665436246635</v>
@@ -6637,10 +6637,10 @@
         <v>-0.01985875398907044</v>
       </c>
       <c r="O29" t="n">
-        <v>-15185169.12173664</v>
+        <v>-15141069.48101515</v>
       </c>
       <c r="P29" t="n">
-        <v>-15185169.12173664</v>
+        <v>-15141069.48101515</v>
       </c>
     </row>
     <row r="30">
@@ -6671,19 +6671,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="H30" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I30" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="L30" t="n">
         <v>0.03830470017405307</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01722276407024426</v>
       </c>
       <c r="O30" t="n">
-        <v>-11483953.18878565</v>
+        <v>-11065882.21964725</v>
       </c>
       <c r="P30" t="n">
-        <v>-11483953.18878565</v>
+        <v>-11065882.21964725</v>
       </c>
     </row>
     <row r="31">
@@ -6729,19 +6729,19 @@
         <v>0.75</v>
       </c>
       <c r="G31" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="H31" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I31" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="J31" t="n">
         <v>-124000000</v>
       </c>
       <c r="K31" t="n">
-        <v>984257827.4287672</v>
+        <v>1242174816.538767</v>
       </c>
       <c r="L31" t="n">
         <v>0.03852218097221538</v>
@@ -6753,10 +6753,10 @@
         <v>-0.01482995615663363</v>
       </c>
       <c r="O31" t="n">
-        <v>-10947375.32069406</v>
+        <v>-13816048.55110825</v>
       </c>
       <c r="P31" t="n">
-        <v>-10947375.32069406</v>
+        <v>-13816048.55110825</v>
       </c>
     </row>
     <row r="32">
@@ -6787,19 +6787,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="H32" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I32" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="J32" t="n">
         <v>-62000000</v>
       </c>
       <c r="K32" t="n">
-        <v>-279571892.4616438</v>
+        <v>-272571360.4816439</v>
       </c>
       <c r="L32" t="n">
         <v>0.03873510939427094</v>
@@ -6811,10 +6811,10 @@
         <v>-0.01260515871784285</v>
       </c>
       <c r="O32" t="n">
-        <v>2349365.385017809</v>
+        <v>2290536.840539652</v>
       </c>
       <c r="P32" t="n">
-        <v>1174682.692508904</v>
+        <v>1145268.420269826</v>
       </c>
     </row>
     <row r="33">
@@ -6845,19 +6845,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="H33" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I33" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="J33" t="n">
         <v>-62000000</v>
       </c>
       <c r="K33" t="n">
-        <v>-280710552.5447945</v>
+        <v>-279462863.0247945</v>
       </c>
       <c r="L33" t="n">
         <v>0.03888939094511485</v>
@@ -6869,10 +6869,10 @@
         <v>-0.01053392699102673</v>
       </c>
       <c r="O33" t="n">
-        <v>1724907.605235288</v>
+        <v>1717240.814220452</v>
       </c>
       <c r="P33" t="n">
-        <v>862453.8026176442</v>
+        <v>858620.4071102258</v>
       </c>
     </row>
     <row r="34">
@@ -6903,19 +6903,19 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="H34" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I34" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="J34" t="n">
         <v>-31000000</v>
       </c>
       <c r="K34" t="n">
-        <v>338250467.3508219</v>
+        <v>83046504.75082195</v>
       </c>
       <c r="L34" t="n">
         <v>0.03901400018340251</v>
@@ -6927,10 +6927,10 @@
         <v>-0.008630921630449429</v>
       </c>
       <c r="O34" t="n">
-        <v>-1459706.637583918</v>
+        <v>-358383.9370935452</v>
       </c>
       <c r="P34" t="n">
-        <v>-1459706.637583918</v>
+        <v>-358383.9370935452</v>
       </c>
     </row>
     <row r="35">
@@ -6961,19 +6961,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="H35" t="n">
         <v>2250000</v>
       </c>
       <c r="I35" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="J35" t="n">
         <v>-31000000</v>
       </c>
       <c r="K35" t="n">
-        <v>-154057218.49</v>
+        <v>-18027242.50999999</v>
       </c>
       <c r="L35" t="n">
         <v>0.03908855826627113</v>
@@ -6985,10 +6985,10 @@
         <v>-0.006850555280960409</v>
       </c>
       <c r="O35" t="n">
-        <v>439740.6215403088</v>
+        <v>51456.925574181</v>
       </c>
       <c r="P35" t="n">
-        <v>219870.3107701544</v>
+        <v>25728.4627870905</v>
       </c>
     </row>
     <row r="36">
@@ -7019,19 +7019,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G36" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="H36" t="n">
         <v>2250000</v>
       </c>
       <c r="I36" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="J36" t="n">
         <v>-31000000</v>
       </c>
       <c r="K36" t="n">
-        <v>13642415.84999999</v>
+        <v>12996230.59999999</v>
       </c>
       <c r="L36" t="n">
         <v>0.03915884386251234</v>
@@ -7043,10 +7043,10 @@
         <v>-0.005233721067838482</v>
       </c>
       <c r="O36" t="n">
-        <v>-23800.19975011954</v>
+        <v>-22672.88196456904</v>
       </c>
       <c r="P36" t="n">
-        <v>-23800.19975011954</v>
+        <v>-22672.88196456904</v>
       </c>
     </row>
     <row r="37">
@@ -7077,19 +7077,19 @@
         <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="H37" t="n">
         <v>2250000</v>
       </c>
       <c r="I37" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="J37" t="n">
         <v>-31000000</v>
       </c>
       <c r="K37" t="n">
-        <v>17275197.6</v>
+        <v>11981487.23</v>
       </c>
       <c r="L37" t="n">
         <v>0.03922681220647117</v>
@@ -7101,10 +7101,10 @@
         <v>-0.003721650822949542</v>
       </c>
       <c r="O37" t="n">
-        <v>-16073.06334116399</v>
+        <v>-11147.72795242223</v>
       </c>
       <c r="P37" t="n">
-        <v>-16073.06334116399</v>
+        <v>-11147.72795242223</v>
       </c>
     </row>
     <row r="38">
@@ -7135,19 +7135,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="H38" t="n">
         <v>2250000</v>
       </c>
       <c r="I38" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="J38" t="n">
         <v>-31000000</v>
       </c>
       <c r="K38" t="n">
-        <v>29036789.9</v>
+        <v>14159921.49</v>
       </c>
       <c r="L38" t="n">
         <v>0.03929424848359133</v>
@@ -7159,10 +7159,10 @@
         <v>-0.002324803196355599</v>
       </c>
       <c r="O38" t="n">
-        <v>-11250.80366190433</v>
+        <v>-5486.505123349388</v>
       </c>
       <c r="P38" t="n">
-        <v>-11250.80366190433</v>
+        <v>-5486.505123349388</v>
       </c>
     </row>
     <row r="39">
@@ -7193,19 +7193,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G39" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="H39" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I39" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="L39" t="n">
         <v>0.03936107056455495</v>
@@ -7217,10 +7217,10 @@
         <v>-0.001029519969532107</v>
       </c>
       <c r="O39" t="n">
-        <v>-3159.178560060345</v>
+        <v>-3256.01209752836</v>
       </c>
       <c r="P39" t="n">
-        <v>-3159.178560060345</v>
+        <v>-3256.01209752836</v>
       </c>
     </row>
     <row r="40">
@@ -7251,19 +7251,19 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="H40" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I40" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="J40" t="n">
         <v>-62000000</v>
       </c>
       <c r="K40" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="L40" t="n">
         <v>0.03942868733737526</v>
@@ -7275,10 +7275,10 @@
         <v>0.0001712813743293129</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="41">
@@ -7309,19 +7309,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G41" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="J41" t="n">
         <v>-620000000</v>
       </c>
       <c r="K41" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="L41" t="n">
         <v>0.03432749872940843</v>
@@ -7333,10 +7333,10 @@
         <v>0.02789279458488503</v>
       </c>
       <c r="O41" t="n">
-        <v>-36247659.17335165</v>
+        <v>-36400113.47886805</v>
       </c>
       <c r="P41" t="n">
-        <v>-36247659.17335165</v>
+        <v>-36400113.47886805</v>
       </c>
     </row>
     <row r="42">
@@ -7367,19 +7367,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G42" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="H42" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I42" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="J42" t="n">
         <v>-62000000</v>
       </c>
       <c r="K42" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="L42" t="n">
         <v>0.03782665436246635</v>
@@ -7391,10 +7391,10 @@
         <v>0.02492545821291703</v>
       </c>
       <c r="O42" t="n">
-        <v>17642871.74051509</v>
+        <v>17587520.64685568</v>
       </c>
       <c r="P42" t="n">
-        <v>8821435.870257543</v>
+        <v>8793760.323427841</v>
       </c>
     </row>
     <row r="43">
@@ -7425,19 +7425,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="H43" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I43" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="L43" t="n">
         <v>0.03830470017405307</v>
@@ -7449,10 +7449,10 @@
         <v>0.02210627144826827</v>
       </c>
       <c r="O43" t="n">
-        <v>14740223.1984997</v>
+        <v>14203608.38506325</v>
       </c>
       <c r="P43" t="n">
-        <v>7370111.599249849</v>
+        <v>7101804.192531625</v>
       </c>
     </row>
     <row r="44">
@@ -7483,19 +7483,19 @@
         <v>0.75</v>
       </c>
       <c r="G44" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="H44" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I44" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="J44" t="n">
         <v>-124000000</v>
       </c>
       <c r="K44" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="L44" t="n">
         <v>0.03852218097221538</v>
@@ -7507,10 +7507,10 @@
         <v>0.01953451299207831</v>
       </c>
       <c r="O44" t="n">
-        <v>12603538.27983324</v>
+        <v>16382250.36081849</v>
       </c>
       <c r="P44" t="n">
-        <v>6301769.139916618</v>
+        <v>8191125.180409247</v>
       </c>
     </row>
     <row r="45">
@@ -7541,19 +7541,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="H45" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I45" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="J45" t="n">
         <v>-62000000</v>
       </c>
       <c r="K45" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="L45" t="n">
         <v>0.03873510939427094</v>
@@ -7565,10 +7565,10 @@
         <v>0.01713582153361681</v>
       </c>
       <c r="O45" t="n">
-        <v>-3902076.660081655</v>
+        <v>-3822103.415648551</v>
       </c>
       <c r="P45" t="n">
-        <v>-3902076.660081655</v>
+        <v>-3822103.415648551</v>
       </c>
     </row>
     <row r="46">
@@ -7599,19 +7599,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="H46" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I46" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="J46" t="n">
         <v>-62000000</v>
       </c>
       <c r="K46" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="L46" t="n">
         <v>0.03888939094511485</v>
@@ -7623,10 +7623,10 @@
         <v>0.01489823429388384</v>
       </c>
       <c r="O46" t="n">
-        <v>-2978372.895632596</v>
+        <v>-2967529.679335522</v>
       </c>
       <c r="P46" t="n">
-        <v>-2978372.895632596</v>
+        <v>-2967529.679335522</v>
       </c>
     </row>
     <row r="47">
@@ -7657,19 +7657,19 @@
         <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="H47" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I47" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="J47" t="n">
         <v>-31000000</v>
       </c>
       <c r="K47" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="L47" t="n">
         <v>0.03901400018340251</v>
@@ -7681,10 +7681,10 @@
         <v>0.01283846298538327</v>
       </c>
       <c r="O47" t="n">
-        <v>1972311.876162619</v>
+        <v>334098.562381001</v>
       </c>
       <c r="P47" t="n">
-        <v>986155.9380813093</v>
+        <v>167049.2811905005</v>
       </c>
     </row>
     <row r="48">
@@ -7715,19 +7715,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="H48" t="n">
         <v>2250000</v>
       </c>
       <c r="I48" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="J48" t="n">
         <v>-31000000</v>
       </c>
       <c r="K48" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="L48" t="n">
         <v>0.03908855826627113</v>
@@ -7739,10 +7739,10 @@
         <v>0.01091166853486086</v>
       </c>
       <c r="O48" t="n">
-        <v>-841367.9283942515</v>
+        <v>-222903.7581030664</v>
       </c>
       <c r="P48" t="n">
-        <v>-841367.9283942515</v>
+        <v>-222903.7581030664</v>
       </c>
     </row>
     <row r="49">
@@ -7773,19 +7773,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G49" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="H49" t="n">
         <v>2250000</v>
       </c>
       <c r="I49" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="J49" t="n">
         <v>-31000000</v>
       </c>
       <c r="K49" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="L49" t="n">
         <v>0.03915884386251234</v>
@@ -7797,10 +7797,10 @@
         <v>0.009159039096315102</v>
       </c>
       <c r="O49" t="n">
-        <v>-52992.93061580981</v>
+        <v>-54965.74260521386</v>
       </c>
       <c r="P49" t="n">
-        <v>-52992.93061580981</v>
+        <v>-54965.74260521386</v>
       </c>
     </row>
     <row r="50">
@@ -7831,19 +7831,19 @@
         <v>0.25</v>
       </c>
       <c r="G50" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="H50" t="n">
         <v>2250000</v>
       </c>
       <c r="I50" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="J50" t="n">
         <v>-31000000</v>
       </c>
       <c r="K50" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="L50" t="n">
         <v>0.03922681220647117</v>
@@ -7855,10 +7855,10 @@
         <v>0.007522420693245678</v>
       </c>
       <c r="O50" t="n">
-        <v>-25810.93439611698</v>
+        <v>-35766.3135039513</v>
       </c>
       <c r="P50" t="n">
-        <v>-25810.93439611698</v>
+        <v>-35766.3135039513</v>
       </c>
     </row>
     <row r="51">
@@ -7889,19 +7889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="H51" t="n">
         <v>2250000</v>
       </c>
       <c r="I51" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="J51" t="n">
         <v>-31000000</v>
       </c>
       <c r="K51" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="L51" t="n">
         <v>0.03929424848359133</v>
@@ -7913,10 +7913,10 @@
         <v>0.006011768704670392</v>
       </c>
       <c r="O51" t="n">
-        <v>-1967.060839978806</v>
+        <v>-16873.10949510173</v>
       </c>
       <c r="P51" t="n">
-        <v>-1967.060839978806</v>
+        <v>-16873.10949510173</v>
       </c>
     </row>
     <row r="52">
@@ -7947,19 +7947,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G52" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="H52" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I52" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="L52" t="n">
         <v>0.03936107056455495</v>
@@ -7971,10 +7971,10 @@
         <v>0.004613431737291229</v>
       </c>
       <c r="O52" t="n">
-        <v>14156.74786704356</v>
+        <v>14590.67331600027</v>
       </c>
       <c r="P52" t="n">
-        <v>7078.373933521779</v>
+        <v>7295.336658000136</v>
       </c>
     </row>
     <row r="53">
@@ -8005,19 +8005,19 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="H53" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I53" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="J53" t="n">
         <v>-62000000</v>
       </c>
       <c r="K53" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="L53" t="n">
         <v>0.03942868733737526</v>
@@ -8029,10 +8029,10 @@
         <v>0.003319954993421748</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="54">
@@ -8063,19 +8063,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G54" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="J54" t="n">
         <v>-620000000</v>
       </c>
       <c r="K54" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="L54" t="n">
         <v>0.03432749872940843</v>
@@ -8087,10 +8087,10 @@
         <v>0.0349083460781352</v>
       </c>
       <c r="O54" t="n">
-        <v>-45364612.96823002</v>
+        <v>-45555412.33908088</v>
       </c>
       <c r="P54" t="n">
-        <v>-45364612.96823002</v>
+        <v>-45555412.33908088</v>
       </c>
     </row>
     <row r="55">
@@ -8121,19 +8121,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G55" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="H55" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I55" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="J55" t="n">
         <v>-62000000</v>
       </c>
       <c r="K55" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="L55" t="n">
         <v>0.03782665436246635</v>
@@ -8145,10 +8145,10 @@
         <v>0.03231037168362505</v>
       </c>
       <c r="O55" t="n">
-        <v>22870100.86768048</v>
+        <v>22798350.35485325</v>
       </c>
       <c r="P55" t="n">
-        <v>11435050.43384024</v>
+        <v>11399175.17742662</v>
       </c>
     </row>
     <row r="56">
@@ -8179,19 +8179,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="H56" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I56" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="L56" t="n">
         <v>0.03830470017405307</v>
@@ -8203,10 +8203,10 @@
         <v>0.02984617139370105</v>
       </c>
       <c r="O56" t="n">
-        <v>19901104.94179668</v>
+        <v>19176609.28310079</v>
       </c>
       <c r="P56" t="n">
-        <v>9950552.470898338</v>
+        <v>9588304.641550394</v>
       </c>
     </row>
     <row r="57">
@@ -8237,19 +8237,19 @@
         <v>0.75</v>
       </c>
       <c r="G57" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="H57" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I57" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="J57" t="n">
         <v>-124000000</v>
       </c>
       <c r="K57" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="L57" t="n">
         <v>0.03852218097221538</v>
@@ -8261,10 +8261,10 @@
         <v>0.02759968737635887</v>
       </c>
       <c r="O57" t="n">
-        <v>17807135.32507474</v>
+        <v>23145956.52644055</v>
       </c>
       <c r="P57" t="n">
-        <v>8903567.662537372</v>
+        <v>11572978.26322027</v>
       </c>
     </row>
     <row r="58">
@@ -8295,19 +8295,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="H58" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I58" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="J58" t="n">
         <v>-62000000</v>
       </c>
       <c r="K58" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="L58" t="n">
         <v>0.03873510939427094</v>
@@ -8319,10 +8319,10 @@
         <v>0.02550527570343863</v>
       </c>
       <c r="O58" t="n">
-        <v>-5807923.526519679</v>
+        <v>-5688889.861039254</v>
       </c>
       <c r="P58" t="n">
-        <v>-5807923.526519679</v>
+        <v>-5688889.861039254</v>
       </c>
     </row>
     <row r="59">
@@ -8353,19 +8353,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="H59" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I59" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="J59" t="n">
         <v>-62000000</v>
       </c>
       <c r="K59" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="L59" t="n">
         <v>0.03888939094511485</v>
@@ -8377,10 +8377,10 @@
         <v>0.02355207664351209</v>
       </c>
       <c r="O59" t="n">
-        <v>-4708401.366710636</v>
+        <v>-4691259.720509267</v>
       </c>
       <c r="P59" t="n">
-        <v>-4708401.366710636</v>
+        <v>-4691259.720509267</v>
       </c>
     </row>
     <row r="60">
@@ -8411,19 +8411,19 @@
         <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="H60" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I60" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="J60" t="n">
         <v>-31000000</v>
       </c>
       <c r="K60" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="L60" t="n">
         <v>0.03901400018340251</v>
@@ -8435,10 +8435,10 @@
         <v>0.02175522406292973</v>
       </c>
       <c r="O60" t="n">
-        <v>3342151.380328503</v>
+        <v>566141.6862732342</v>
       </c>
       <c r="P60" t="n">
-        <v>1671075.690164251</v>
+        <v>283070.8431366171</v>
       </c>
     </row>
     <row r="61">
@@ -8469,19 +8469,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="H61" t="n">
         <v>2250000</v>
       </c>
       <c r="I61" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="J61" t="n">
         <v>-31000000</v>
       </c>
       <c r="K61" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="L61" t="n">
         <v>0.03908855826627113</v>
@@ -8493,10 +8493,10 @@
         <v>0.02007474611606698</v>
       </c>
       <c r="O61" t="n">
-        <v>-1547906.949221786</v>
+        <v>-410087.2692329567</v>
       </c>
       <c r="P61" t="n">
-        <v>-1547906.949221786</v>
+        <v>-410087.2692329567</v>
       </c>
     </row>
     <row r="62">
@@ -8527,19 +8527,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="H62" t="n">
         <v>2250000</v>
       </c>
       <c r="I62" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="J62" t="n">
         <v>-31000000</v>
       </c>
       <c r="K62" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="L62" t="n">
         <v>0.03915884386251234</v>
@@ -8551,10 +8551,10 @@
         <v>0.01854770837490727</v>
       </c>
       <c r="O62" t="n">
-        <v>-107314.4696357043</v>
+        <v>-111309.5548267598</v>
       </c>
       <c r="P62" t="n">
-        <v>-107314.4696357043</v>
+        <v>-111309.5548267598</v>
       </c>
     </row>
     <row r="63">
@@ -8585,19 +8585,19 @@
         <v>0.25</v>
       </c>
       <c r="G63" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="H63" t="n">
         <v>2250000</v>
       </c>
       <c r="I63" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="J63" t="n">
         <v>-31000000</v>
       </c>
       <c r="K63" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="L63" t="n">
         <v>0.03922681220647117</v>
@@ -8609,10 +8609,10 @@
         <v>0.01712251280817986</v>
       </c>
       <c r="O63" t="n">
-        <v>-58750.7762209344</v>
+        <v>-81411.18212421431</v>
       </c>
       <c r="P63" t="n">
-        <v>-58750.7762209344</v>
+        <v>-81411.18212421431</v>
       </c>
     </row>
     <row r="64">
@@ -8643,19 +8643,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="H64" t="n">
         <v>2250000</v>
       </c>
       <c r="I64" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="J64" t="n">
         <v>-31000000</v>
       </c>
       <c r="K64" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="L64" t="n">
         <v>0.03929424848359133</v>
@@ -8667,10 +8667,10 @@
         <v>0.01580817291864865</v>
       </c>
       <c r="O64" t="n">
-        <v>-5172.460789406253</v>
+        <v>-44368.47884161649</v>
       </c>
       <c r="P64" t="n">
-        <v>-5172.460789406253</v>
+        <v>-44368.47884161649</v>
       </c>
     </row>
     <row r="65">
@@ -8701,19 +8701,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G65" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="H65" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I65" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="L65" t="n">
         <v>0.03936107056455495</v>
@@ -8725,10 +8725,10 @@
         <v>0.01459272426401294</v>
       </c>
       <c r="O65" t="n">
-        <v>44779.14269957671</v>
+        <v>46151.69024950127</v>
       </c>
       <c r="P65" t="n">
-        <v>22389.57134978836</v>
+        <v>23075.84512475063</v>
       </c>
     </row>
     <row r="66">
@@ -8759,19 +8759,19 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="H66" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I66" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="J66" t="n">
         <v>-62000000</v>
       </c>
       <c r="K66" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="L66" t="n">
         <v>0.03942868733737526</v>
@@ -8783,10 +8783,10 @@
         <v>0.01346967956071188</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="67">
@@ -8817,19 +8817,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G67" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="J67" t="n">
         <v>-620000000</v>
       </c>
       <c r="K67" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="L67" t="n">
         <v>0.03432749872940843</v>
@@ -8841,10 +8841,10 @@
         <v>-0.03432359322008915</v>
       </c>
       <c r="O67" t="n">
-        <v>23382381.53250516</v>
+        <v>23569984.80586207</v>
       </c>
       <c r="P67" t="n">
-        <v>11691190.76625258</v>
+        <v>11784992.40293104</v>
       </c>
     </row>
     <row r="68">
@@ -8875,19 +8875,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G68" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="H68" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I68" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="J68" t="n">
         <v>-62000000</v>
       </c>
       <c r="K68" t="n">
-        <v>834173133.4710958</v>
+        <v>831750589.7910959</v>
       </c>
       <c r="L68" t="n">
         <v>0.03782665436246635</v>
@@ -8899,10 +8899,10 @@
         <v>-0.03222210497938605</v>
       </c>
       <c r="O68" t="n">
-        <v>-24638913.08788164</v>
+        <v>-24567358.5858387</v>
       </c>
       <c r="P68" t="n">
-        <v>-24638913.08788164</v>
+        <v>-24567358.5858387</v>
       </c>
     </row>
     <row r="69">
@@ -8933,19 +8933,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="H69" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I69" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="L69" t="n">
         <v>0.03830470017405307</v>
@@ -8957,10 +8957,10 @@
         <v>-0.02969704733354739</v>
       </c>
       <c r="O69" t="n">
-        <v>-19801670.62805112</v>
+        <v>-19080794.85522814</v>
       </c>
       <c r="P69" t="n">
-        <v>-19801670.62805112</v>
+        <v>-19080794.85522814</v>
       </c>
     </row>
     <row r="70">
@@ -8991,19 +8991,19 @@
         <v>0.75</v>
       </c>
       <c r="G70" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="H70" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I70" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="J70" t="n">
         <v>-124000000</v>
       </c>
       <c r="K70" t="n">
-        <v>984257827.4287672</v>
+        <v>1242174816.538767</v>
       </c>
       <c r="L70" t="n">
         <v>0.03852218097221538</v>
@@ -9015,10 +9015,10 @@
         <v>-0.0274114503343057</v>
       </c>
       <c r="O70" t="n">
-        <v>-20234950.91453646</v>
+        <v>-25537359.96755828</v>
       </c>
       <c r="P70" t="n">
-        <v>-20234950.91453646</v>
+        <v>-25537359.96755828</v>
       </c>
     </row>
     <row r="71">
@@ -9049,19 +9049,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="H71" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I71" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="J71" t="n">
         <v>-62000000</v>
       </c>
       <c r="K71" t="n">
-        <v>-279571892.4616438</v>
+        <v>-272571360.4816439</v>
       </c>
       <c r="L71" t="n">
         <v>0.03873510939427094</v>
@@ -9073,10 +9073,10 @@
         <v>-0.0252927177134521</v>
       </c>
       <c r="O71" t="n">
-        <v>4714088.637765296</v>
+        <v>4596046.984955874</v>
       </c>
       <c r="P71" t="n">
-        <v>2357044.318882648</v>
+        <v>2298023.492477937</v>
       </c>
     </row>
     <row r="72">
@@ -9107,19 +9107,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G72" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="H72" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I72" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="J72" t="n">
         <v>-62000000</v>
       </c>
       <c r="K72" t="n">
-        <v>-280710552.5447945</v>
+        <v>-279462863.0247945</v>
       </c>
       <c r="L72" t="n">
         <v>0.03888939094511485</v>
@@ -9131,10 +9131,10 @@
         <v>-0.02332613375362271</v>
       </c>
       <c r="O72" t="n">
-        <v>3819603.605249374</v>
+        <v>3802626.404550575</v>
       </c>
       <c r="P72" t="n">
-        <v>1909801.802624687</v>
+        <v>1901313.202275287</v>
       </c>
     </row>
     <row r="73">
@@ -9165,19 +9165,19 @@
         <v>0.5</v>
       </c>
       <c r="G73" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="H73" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I73" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="J73" t="n">
         <v>-31000000</v>
       </c>
       <c r="K73" t="n">
-        <v>338250467.3508219</v>
+        <v>83046504.75082195</v>
       </c>
       <c r="L73" t="n">
         <v>0.03901400018340251</v>
@@ -9189,10 +9189,10 @@
         <v>-0.02152530442995682</v>
       </c>
       <c r="O73" t="n">
-        <v>-3640472.141650804</v>
+        <v>-893800.6483026487</v>
       </c>
       <c r="P73" t="n">
-        <v>-3640472.141650804</v>
+        <v>-893800.6483026487</v>
       </c>
     </row>
     <row r="74">
@@ -9223,19 +9223,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G74" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="H74" t="n">
         <v>2250000</v>
       </c>
       <c r="I74" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="J74" t="n">
         <v>-31000000</v>
       </c>
       <c r="K74" t="n">
-        <v>-154057218.49</v>
+        <v>-18027242.50999999</v>
       </c>
       <c r="L74" t="n">
         <v>0.03908855826627113</v>
@@ -9247,10 +9247,10 @@
         <v>-0.01984578814143261</v>
       </c>
       <c r="O74" t="n">
-        <v>1273911.216587889</v>
+        <v>149068.6815115365</v>
       </c>
       <c r="P74" t="n">
-        <v>636955.6082939446</v>
+        <v>74534.34075576825</v>
       </c>
     </row>
     <row r="75">
@@ -9281,19 +9281,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G75" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="H75" t="n">
         <v>2250000</v>
       </c>
       <c r="I75" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="J75" t="n">
         <v>-31000000</v>
       </c>
       <c r="K75" t="n">
-        <v>13642415.84999999</v>
+        <v>12996230.59999999</v>
       </c>
       <c r="L75" t="n">
         <v>0.03915884386251234</v>
@@ -9305,10 +9305,10 @@
         <v>-0.01832662273584051</v>
       </c>
       <c r="O75" t="n">
-        <v>-83339.80282946698</v>
+        <v>-79392.33839806204</v>
       </c>
       <c r="P75" t="n">
-        <v>-83339.80282946698</v>
+        <v>-79392.33839806204</v>
       </c>
     </row>
     <row r="76">
@@ -9339,19 +9339,19 @@
         <v>0.25</v>
       </c>
       <c r="G76" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="H76" t="n">
         <v>2250000</v>
       </c>
       <c r="I76" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="J76" t="n">
         <v>-31000000</v>
       </c>
       <c r="K76" t="n">
-        <v>17275197.6</v>
+        <v>11981487.23</v>
       </c>
       <c r="L76" t="n">
         <v>0.03922681220647117</v>
@@ -9363,10 +9363,10 @@
         <v>-0.01691110693903308</v>
       </c>
       <c r="O76" t="n">
-        <v>-73035.67850163192</v>
+        <v>-50655.0529587973</v>
       </c>
       <c r="P76" t="n">
-        <v>-73035.67850163192</v>
+        <v>-50655.0529587973</v>
       </c>
     </row>
     <row r="77">
@@ -9397,19 +9397,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="H77" t="n">
         <v>2250000</v>
       </c>
       <c r="I77" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="J77" t="n">
         <v>-31000000</v>
       </c>
       <c r="K77" t="n">
-        <v>29036789.9</v>
+        <v>14159921.49</v>
       </c>
       <c r="L77" t="n">
         <v>0.03929424848359133</v>
@@ -9421,10 +9421,10 @@
         <v>-0.01560891224971384</v>
       </c>
       <c r="O77" t="n">
-        <v>-75538.78426041281</v>
+        <v>-36836.82866670786</v>
       </c>
       <c r="P77" t="n">
-        <v>-75538.78426041281</v>
+        <v>-36836.82866670786</v>
       </c>
     </row>
     <row r="78">
@@ -9455,19 +9455,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G78" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="H78" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I78" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="L78" t="n">
         <v>0.03936107056455495</v>
@@ -9479,10 +9479,10 @@
         <v>-0.01440665719067059</v>
       </c>
       <c r="O78" t="n">
-        <v>-44208.17843833612</v>
+        <v>-45563.22508157478</v>
       </c>
       <c r="P78" t="n">
-        <v>-44208.17843833612</v>
+        <v>-45563.22508157478</v>
       </c>
     </row>
     <row r="79">
@@ -9513,19 +9513,19 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="H79" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I79" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="J79" t="n">
         <v>-62000000</v>
       </c>
       <c r="K79" t="n">
-        <v>133651477.9931507</v>
+        <v>-13511470.05684932</v>
       </c>
       <c r="L79" t="n">
         <v>0.03942868733737526</v>
@@ -9537,10 +9537,10 @@
         <v>-0.01329726695768341</v>
       </c>
       <c r="O79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -9571,19 +9571,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G80" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>-1303105020.33</v>
+        <v>-1308585759.65</v>
       </c>
       <c r="J80" t="n">
         <v>-620000000</v>
       </c>
       <c r="K80" t="n">
-        <v>-683105020.3299999</v>
+        <v>-688585759.6500001</v>
       </c>
       <c r="L80" t="n">
         <v>0.03432749872940843</v>
@@ -9595,10 +9595,10 @@
         <v>-0.01000145066733071</v>
       </c>
       <c r="O80" t="n">
-        <v>6813323.240446202</v>
+        <v>6867988.405351218</v>
       </c>
       <c r="P80" t="n">
-        <v>3406661.620223101</v>
+        <v>3433994.202675609</v>
       </c>
     </row>
     <row r="81">
@@ -9629,19 +9629,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>861715944.4299999</v>
+        <v>859293400.75</v>
       </c>
       <c r="H81" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I81" t="n">
-        <v>772173133.4710958</v>
+        <v>769750589.7910959</v>
       </c>
       <c r="J81" t="n">
         <v>-62000000</v>
       </c>
       <c r="K81" t="n">
-        <v>834173133.4710958</v>
+        <v>831750589.7910959</v>
       </c>
       <c r="L81" t="n">
         <v>0.03782665436246635</v>
@@ -9653,10 +9653,10 @@
         <v>-0.01002646052209499</v>
       </c>
       <c r="O81" t="n">
-        <v>-7666820.325395201</v>
+        <v>-7644554.915038845</v>
       </c>
       <c r="P81" t="n">
-        <v>-7666820.325395201</v>
+        <v>-7644554.915038845</v>
       </c>
     </row>
     <row r="82">
@@ -9687,19 +9687,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>851081801.2700001</v>
+        <v>821952611.5000001</v>
       </c>
       <c r="H82" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I82" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>800147047.8453425</v>
+        <v>771017858.0753425</v>
       </c>
       <c r="L82" t="n">
         <v>0.03830470017405307</v>
@@ -9711,10 +9711,10 @@
         <v>-0.01005429630576771</v>
       </c>
       <c r="O82" t="n">
-        <v>-6704096.256018637</v>
+        <v>-6460035.001773206</v>
       </c>
       <c r="P82" t="n">
-        <v>-6704096.256018637</v>
+        <v>-6460035.001773206</v>
       </c>
     </row>
     <row r="83">
@@ -9745,19 +9745,19 @@
         <v>0.75</v>
       </c>
       <c r="G83" t="n">
-        <v>990570715.1000001</v>
+        <v>1248487704.21</v>
       </c>
       <c r="H83" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I83" t="n">
-        <v>860257827.4287672</v>
+        <v>1118174816.538767</v>
       </c>
       <c r="J83" t="n">
         <v>-124000000</v>
       </c>
       <c r="K83" t="n">
-        <v>984257827.4287672</v>
+        <v>1242174816.538767</v>
       </c>
       <c r="L83" t="n">
         <v>0.03852218097221538</v>
@@ -9769,10 +9769,10 @@
         <v>-0.01008322673507944</v>
       </c>
       <c r="O83" t="n">
-        <v>-7443371.129805716</v>
+        <v>-9393847.739824571</v>
       </c>
       <c r="P83" t="n">
-        <v>-7443371.129805716</v>
+        <v>-9393847.739824571</v>
       </c>
     </row>
     <row r="84">
@@ -9803,19 +9803,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G84" t="n">
-        <v>-251621108.9</v>
+        <v>-244620576.92</v>
       </c>
       <c r="H84" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I84" t="n">
-        <v>-341571892.4616438</v>
+        <v>-334571360.4816439</v>
       </c>
       <c r="J84" t="n">
         <v>-62000000</v>
       </c>
       <c r="K84" t="n">
-        <v>-279571892.4616438</v>
+        <v>-272571360.4816439</v>
       </c>
       <c r="L84" t="n">
         <v>0.03873510939427094</v>
@@ -9827,10 +9827,10 @@
         <v>-0.0101121147124088</v>
       </c>
       <c r="O84" t="n">
-        <v>1884708.697958241</v>
+        <v>1837515.243005143</v>
       </c>
       <c r="P84" t="n">
-        <v>942354.3489791203</v>
+        <v>918757.6215025715</v>
       </c>
     </row>
     <row r="85">
@@ -9861,19 +9861,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G85" t="n">
-        <v>-252737100.49</v>
+        <v>-251489410.97</v>
       </c>
       <c r="H85" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I85" t="n">
-        <v>-342710552.5447945</v>
+        <v>-341462863.0247945</v>
       </c>
       <c r="J85" t="n">
         <v>-62000000</v>
       </c>
       <c r="K85" t="n">
-        <v>-280710552.5447945</v>
+        <v>-279462863.0247945</v>
       </c>
       <c r="L85" t="n">
         <v>0.03888939094511485</v>
@@ -9885,10 +9885,10 @@
         <v>-0.0101405708492285</v>
       </c>
       <c r="O85" t="n">
-        <v>1660496.393620498</v>
+        <v>1653115.894634848</v>
       </c>
       <c r="P85" t="n">
-        <v>830248.196810249</v>
+        <v>826557.9473174242</v>
       </c>
     </row>
     <row r="86">
@@ -9919,19 +9919,19 @@
         <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>397219075.5699999</v>
+        <v>142015112.97</v>
       </c>
       <c r="H86" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I86" t="n">
-        <v>307250467.3508219</v>
+        <v>52046504.75082195</v>
       </c>
       <c r="J86" t="n">
         <v>-31000000</v>
       </c>
       <c r="K86" t="n">
-        <v>338250467.3508219</v>
+        <v>83046504.75082195</v>
       </c>
       <c r="L86" t="n">
         <v>0.03901400018340251</v>
@@ -9943,10 +9943,10 @@
         <v>-0.01016949446707605</v>
       </c>
       <c r="O86" t="n">
-        <v>-1719918.128105035</v>
+        <v>-422270.4852867442</v>
       </c>
       <c r="P86" t="n">
-        <v>-1719918.128105035</v>
+        <v>-422270.4852867442</v>
       </c>
     </row>
     <row r="87">
@@ -9977,19 +9977,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>-187307218.49</v>
+        <v>-51277242.50999999</v>
       </c>
       <c r="H87" t="n">
         <v>2250000</v>
       </c>
       <c r="I87" t="n">
-        <v>-185057218.49</v>
+        <v>-49027242.50999999</v>
       </c>
       <c r="J87" t="n">
         <v>-31000000</v>
       </c>
       <c r="K87" t="n">
-        <v>-154057218.49</v>
+        <v>-18027242.50999999</v>
       </c>
       <c r="L87" t="n">
         <v>0.03908855826627113</v>
@@ -10001,10 +10001,10 @@
         <v>-0.01019737062440143</v>
       </c>
       <c r="O87" t="n">
-        <v>654574.397627883</v>
+        <v>76596.03050434779</v>
       </c>
       <c r="P87" t="n">
-        <v>327287.1988139415</v>
+        <v>38298.01525217389</v>
       </c>
     </row>
     <row r="88">
@@ -10035,19 +10035,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>-19607584.15000001</v>
+        <v>-20253769.40000001</v>
       </c>
       <c r="H88" t="n">
         <v>2250000</v>
       </c>
       <c r="I88" t="n">
-        <v>-17357584.15000001</v>
+        <v>-18003769.40000001</v>
       </c>
       <c r="J88" t="n">
         <v>-31000000</v>
       </c>
       <c r="K88" t="n">
-        <v>13642415.84999999</v>
+        <v>12996230.59999999</v>
       </c>
       <c r="L88" t="n">
         <v>0.03915884386251234</v>
@@ -10059,10 +10059,10 @@
         <v>-0.0102268186216663</v>
       </c>
       <c r="O88" t="n">
-        <v>-46506.17081976515</v>
+        <v>-44303.36437051645</v>
       </c>
       <c r="P88" t="n">
-        <v>-46506.17081976515</v>
+        <v>-44303.36437051645</v>
       </c>
     </row>
     <row r="89">
@@ -10093,19 +10093,19 @@
         <v>0.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-15974802.4</v>
+        <v>-21268512.77</v>
       </c>
       <c r="H89" t="n">
         <v>2250000</v>
       </c>
       <c r="I89" t="n">
-        <v>-13724802.4</v>
+        <v>-19018512.77</v>
       </c>
       <c r="J89" t="n">
         <v>-31000000</v>
       </c>
       <c r="K89" t="n">
-        <v>17275197.6</v>
+        <v>11981487.23</v>
       </c>
       <c r="L89" t="n">
         <v>0.03922681220647117</v>
@@ -10117,10 +10117,10 @@
         <v>-0.01025547675463123</v>
       </c>
       <c r="O89" t="n">
-        <v>-44291.34685461532</v>
+        <v>-30718.96594329398</v>
       </c>
       <c r="P89" t="n">
-        <v>-44291.34685461532</v>
+        <v>-30718.96594329398</v>
       </c>
     </row>
     <row r="90">
@@ -10151,19 +10151,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>-4213210.100000001</v>
+        <v>-19090078.51</v>
       </c>
       <c r="H90" t="n">
         <v>2250000</v>
       </c>
       <c r="I90" t="n">
-        <v>-1963210.100000001</v>
+        <v>-16840078.51</v>
       </c>
       <c r="J90" t="n">
         <v>-31000000</v>
       </c>
       <c r="K90" t="n">
-        <v>29036789.9</v>
+        <v>14159921.49</v>
       </c>
       <c r="L90" t="n">
         <v>0.03929424848359133</v>
@@ -10175,10 +10175,10 @@
         <v>-0.01028445871969606</v>
       </c>
       <c r="O90" t="n">
-        <v>-49771.27784650621</v>
+        <v>-24271.18800634034</v>
       </c>
       <c r="P90" t="n">
-        <v>-49771.27784650621</v>
+        <v>-24271.18800634034</v>
       </c>
     </row>
     <row r="91">
@@ -10209,19 +10209,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G91" t="n">
-        <v>34560796.42</v>
+        <v>35689480.16</v>
       </c>
       <c r="H91" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I91" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>36823125.18712329</v>
+        <v>37951808.92712329</v>
       </c>
       <c r="L91" t="n">
         <v>0.03936107056455495</v>
@@ -10233,10 +10233,10 @@
         <v>-0.01031343600303951</v>
       </c>
       <c r="O91" t="n">
-        <v>-31647.74542077571</v>
+        <v>-32617.79604745581</v>
       </c>
       <c r="P91" t="n">
-        <v>-31647.74542077571</v>
+        <v>-32617.79604745581</v>
       </c>
     </row>
     <row r="92">
@@ -10267,19 +10267,19 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>67606409.5</v>
+        <v>-79556538.55</v>
       </c>
       <c r="H92" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I92" t="n">
-        <v>71651477.99315068</v>
+        <v>-75511470.05684932</v>
       </c>
       <c r="J92" t="n">
         <v>-62000000</v>
       </c>
       <c r="K92" t="n">
-        <v>133651477.9931507</v>
+        <v>-13511470.05684932</v>
       </c>
       <c r="L92" t="n">
         <v>0.03942868733737526</v>
@@ -10291,10 +10291,10 @@
         <v>-0.01034243719640493</v>
       </c>
       <c r="O92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10370,22 +10370,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D2" t="n">
-        <v>570524821.17</v>
+        <v>499832517.6</v>
       </c>
       <c r="E2" t="n">
-        <v>33204891.25999999</v>
+        <v>35717002.64000005</v>
       </c>
       <c r="F2" t="n">
-        <v>16602445.63</v>
+        <v>17858501.32000002</v>
       </c>
       <c r="G2" t="n">
-        <v>2.767074271666666</v>
+        <v>2.97641688666667</v>
       </c>
       <c r="H2" t="n">
-        <v>1.383537135833333</v>
+        <v>1.488208443333335</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -10403,22 +10403,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D3" t="n">
-        <v>500370371.04</v>
+        <v>424713058.09</v>
       </c>
       <c r="E3" t="n">
-        <v>-36949558.86999995</v>
+        <v>-39402456.87</v>
       </c>
       <c r="F3" t="n">
-        <v>-36949558.86999995</v>
+        <v>-39402456.87</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.079129905833329</v>
+        <v>-3.2835380725</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.079129905833329</v>
+        <v>-3.2835380725</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -10436,22 +10436,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D4" t="n">
-        <v>561357106.7</v>
+        <v>489070373.65</v>
       </c>
       <c r="E4" t="n">
-        <v>24037176.79000008</v>
+        <v>24954858.69</v>
       </c>
       <c r="F4" t="n">
-        <v>12018588.39500004</v>
+        <v>12477429.345</v>
       </c>
       <c r="G4" t="n">
-        <v>2.00309806583334</v>
+        <v>2.0795715575</v>
       </c>
       <c r="H4" t="n">
-        <v>1.00154903291667</v>
+        <v>1.03978577875</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -10469,22 +10469,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D5" t="n">
-        <v>512211372.01</v>
+        <v>438331502.68</v>
       </c>
       <c r="E5" t="n">
-        <v>-25108557.89999998</v>
+        <v>-25784012.27999997</v>
       </c>
       <c r="F5" t="n">
-        <v>-25108557.89999998</v>
+        <v>-25784012.27999997</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.092379824999998</v>
+        <v>-2.148667689999998</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.092379824999998</v>
+        <v>-2.148667689999998</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -10502,22 +10502,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D6" t="n">
-        <v>528761317.8</v>
+        <v>455959739.47</v>
       </c>
       <c r="E6" t="n">
-        <v>-8558612.109999955</v>
+        <v>-8155775.48999995</v>
       </c>
       <c r="F6" t="n">
-        <v>-8558612.109999955</v>
+        <v>-8155775.48999995</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7132176758333296</v>
+        <v>-0.6796479574999958</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7132176758333296</v>
+        <v>-0.6796479574999958</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -10535,22 +10535,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D7" t="n">
-        <v>542004735.38</v>
+        <v>468775395.59</v>
       </c>
       <c r="E7" t="n">
-        <v>4684805.470000029</v>
+        <v>4659880.629999995</v>
       </c>
       <c r="F7" t="n">
-        <v>2342402.735000014</v>
+        <v>2329940.314999998</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3904004558333357</v>
+        <v>0.3883233858333329</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1952002279166679</v>
+        <v>0.1941616929166665</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -10568,22 +10568,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>537319929.91</v>
+        <v>464115514.96</v>
       </c>
       <c r="D8" t="n">
-        <v>521475205.63</v>
+        <v>447267377.49</v>
       </c>
       <c r="E8" t="n">
-        <v>-15844724.27999997</v>
+        <v>-16848137.46999997</v>
       </c>
       <c r="F8" t="n">
-        <v>-15844724.27999997</v>
+        <v>-16848137.46999997</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.320393689999998</v>
+        <v>-1.404011455833331</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.320393689999998</v>
+        <v>-1.404011455833331</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>

--- a/irrbb_calc/output/eba_sot_results.xlsx
+++ b/irrbb_calc/output/eba_sot_results.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1336496145.66</v>
+        <v>-1336575420.08</v>
       </c>
       <c r="E2" t="n">
         <v>0.999906031812547</v>
@@ -495,10 +495,10 @@
         <v>1.270756758997571e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>-16983.61510471647</v>
+        <v>-16984.62248976678</v>
       </c>
       <c r="I2" t="n">
-        <v>-16983.61510471647</v>
+        <v>-16984.62248976678</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-294615437.6</v>
+        <v>-261189614.82</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983821828874917</v>
@@ -530,10 +530,10 @@
         <v>-0.001074720528931317</v>
       </c>
       <c r="H3" t="n">
-        <v>316629.2589288033</v>
+        <v>280705.8409907172</v>
       </c>
       <c r="I3" t="n">
-        <v>158314.6294644016</v>
+        <v>140352.9204953586</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-481529446.14</v>
+        <v>-447076968.15</v>
       </c>
       <c r="E4" t="n">
         <v>0.9936563817038003</v>
@@ -565,10 +565,10 @@
         <v>-0.004131807575030844</v>
       </c>
       <c r="H4" t="n">
-        <v>1989587.013161659</v>
+        <v>1847236.003623993</v>
       </c>
       <c r="I4" t="n">
-        <v>994793.5065808293</v>
+        <v>923618.0018119966</v>
       </c>
     </row>
     <row r="5">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-787008130.14</v>
+        <v>-1011098505.86</v>
       </c>
       <c r="E5" t="n">
         <v>0.9856536327098718</v>
@@ -600,10 +600,10 @@
         <v>-0.009198654711137122</v>
       </c>
       <c r="H5" t="n">
-        <v>7239416.044015528</v>
+        <v>9300746.034352794</v>
       </c>
       <c r="I5" t="n">
-        <v>3619708.022007764</v>
+        <v>4650373.017176397</v>
       </c>
     </row>
     <row r="6">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>134038813.24</v>
+        <v>192014855.79</v>
       </c>
       <c r="E6" t="n">
         <v>0.9761318955535195</v>
@@ -635,10 +635,10 @@
         <v>-0.01513456126685975</v>
       </c>
       <c r="H6" t="n">
-        <v>-2028618.631117951</v>
+        <v>-2906060.599100994</v>
       </c>
       <c r="I6" t="n">
-        <v>-2028618.631117951</v>
+        <v>-2906060.599100994</v>
       </c>
     </row>
     <row r="7">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>327140775.91</v>
+        <v>347887543.05</v>
       </c>
       <c r="E7" t="n">
         <v>0.9667342819189046</v>
@@ -670,10 +670,10 @@
         <v>-0.02091896253201642</v>
       </c>
       <c r="H7" t="n">
-        <v>-6843445.633956069</v>
+        <v>-7277446.478418198</v>
       </c>
       <c r="I7" t="n">
-        <v>-6843445.633956069</v>
+        <v>-7277446.478418198</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>597747588.01</v>
+        <v>626603273.1</v>
       </c>
       <c r="E8" t="n">
         <v>0.9524015829683793</v>
@@ -705,10 +705,10 @@
         <v>-0.02930239133147783</v>
       </c>
       <c r="H8" t="n">
-        <v>-17515433.74131601</v>
+        <v>-18360974.31796107</v>
       </c>
       <c r="I8" t="n">
-        <v>-17515433.74131601</v>
+        <v>-18360974.31796107</v>
       </c>
     </row>
     <row r="9">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>285154483.07</v>
+        <v>300401739.98</v>
       </c>
       <c r="E9" t="n">
         <v>0.9333610479054046</v>
@@ -740,10 +740,10 @@
         <v>-0.03995420556806362</v>
       </c>
       <c r="H9" t="n">
-        <v>-11393120.8352337</v>
+        <v>-12002312.87216491</v>
       </c>
       <c r="I9" t="n">
-        <v>-11393120.8352337</v>
+        <v>-12002312.87216491</v>
       </c>
     </row>
     <row r="10">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>850770561.15</v>
+        <v>977534811.54</v>
       </c>
       <c r="E10" t="n">
         <v>0.9066754799235061</v>
@@ -775,10 +775,10 @@
         <v>-0.05493320652757383</v>
       </c>
       <c r="H10" t="n">
-        <v>-46735554.94323283</v>
+        <v>-53699121.69021978</v>
       </c>
       <c r="I10" t="n">
-        <v>-46735554.94323283</v>
+        <v>-53699121.69021978</v>
       </c>
     </row>
     <row r="11">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1364232580.07</v>
+        <v>1136763875.88</v>
       </c>
       <c r="E11" t="n">
         <v>0.8730418834956067</v>
@@ -810,10 +810,10 @@
         <v>-0.07314463828611695</v>
       </c>
       <c r="H11" t="n">
-        <v>-99786298.60735622</v>
+        <v>-83148182.51796693</v>
       </c>
       <c r="I11" t="n">
-        <v>-99786298.60735622</v>
+        <v>-83148182.51796693</v>
       </c>
     </row>
     <row r="12">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>831336595.33</v>
+        <v>1030678038.27</v>
       </c>
       <c r="E12" t="n">
         <v>0.839886760163754</v>
@@ -845,10 +845,10 @@
         <v>-0.0893662269184845</v>
       </c>
       <c r="H12" t="n">
-        <v>-74293414.8239011</v>
+        <v>-92107807.44793527</v>
       </c>
       <c r="I12" t="n">
-        <v>-74293414.8239011</v>
+        <v>-92107807.44793527</v>
       </c>
     </row>
     <row r="13">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>163716720.8</v>
+        <v>164642316.19</v>
       </c>
       <c r="E13" t="n">
         <v>0.8060794216350962</v>
@@ -880,10 +880,10 @@
         <v>-0.1035535335270944</v>
       </c>
       <c r="H13" t="n">
-        <v>-16953444.93630875</v>
+        <v>-17049293.60955964</v>
       </c>
       <c r="I13" t="n">
-        <v>-16953444.93630875</v>
+        <v>-17049293.60955964</v>
       </c>
     </row>
     <row r="14">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>298627003.45</v>
+        <v>300164895.95</v>
       </c>
       <c r="E14" t="n">
         <v>0.7725125366488534</v>
@@ -915,10 +915,10 @@
         <v>-0.1158645673464029</v>
       </c>
       <c r="H14" t="n">
-        <v>-34600288.55268703</v>
+        <v>-34778475.8018248</v>
       </c>
       <c r="I14" t="n">
-        <v>-34600288.55268703</v>
+        <v>-34778475.8018248</v>
       </c>
     </row>
     <row r="15">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>293231811.97</v>
+        <v>294033463.53</v>
       </c>
       <c r="E15" t="n">
         <v>0.7390723504327896</v>
@@ -950,10 +950,10 @@
         <v>-0.1263599384343468</v>
       </c>
       <c r="H15" t="n">
-        <v>-37052753.70752116</v>
+        <v>-37154050.34928855</v>
       </c>
       <c r="I15" t="n">
-        <v>-37052753.70752116</v>
+        <v>-37154050.34928855</v>
       </c>
     </row>
     <row r="16">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>241079539.25</v>
+        <v>240382289.04</v>
       </c>
       <c r="E16" t="n">
         <v>0.7058360643204235</v>
@@ -985,10 +985,10 @@
         <v>-0.135125484853127</v>
       </c>
       <c r="H16" t="n">
-        <v>-32575989.62932472</v>
+        <v>-32481773.35663452</v>
       </c>
       <c r="I16" t="n">
-        <v>-32575989.62932472</v>
+        <v>-32481773.35663452</v>
       </c>
     </row>
     <row r="17">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>152684438.78</v>
+        <v>150566167.36</v>
       </c>
       <c r="E17" t="n">
         <v>0.6740936305925465</v>
@@ -1020,10 +1020,10 @@
         <v>-0.142505629537688</v>
       </c>
       <c r="H17" t="n">
-        <v>-21758392.06895248</v>
+        <v>-21456526.46671369</v>
       </c>
       <c r="I17" t="n">
-        <v>-21758392.06895248</v>
+        <v>-21456526.46671369</v>
       </c>
     </row>
     <row r="18">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12791711.15</v>
+        <v>12366500.87</v>
       </c>
       <c r="E18" t="n">
         <v>0.5835756277426192</v>
@@ -1055,10 +1055,10 @@
         <v>-0.1566226182330579</v>
       </c>
       <c r="H18" t="n">
-        <v>-2003471.291994</v>
+        <v>-1936873.744640789</v>
       </c>
       <c r="I18" t="n">
-        <v>-2003471.291994</v>
+        <v>-1936873.744640789</v>
       </c>
     </row>
     <row r="19">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1336496145.66</v>
+        <v>-1336575420.08</v>
       </c>
       <c r="E19" t="n">
         <v>0.999906031812547</v>
@@ -1090,10 +1090,10 @@
         <v>8.119444430232381e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-108516.0618590613</v>
+        <v>-108522.4985015406</v>
       </c>
       <c r="I19" t="n">
-        <v>-108516.0618590613</v>
+        <v>-108522.4985015406</v>
       </c>
     </row>
     <row r="20">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-294615437.6</v>
+        <v>-261189614.82</v>
       </c>
       <c r="E20" t="n">
         <v>0.9983821828874917</v>
@@ -1125,10 +1125,10 @@
         <v>0.001073618328581993</v>
       </c>
       <c r="H20" t="n">
-        <v>-316304.5336905645</v>
+        <v>-280417.957706023</v>
       </c>
       <c r="I20" t="n">
-        <v>-316304.5336905645</v>
+        <v>-280417.957706023</v>
       </c>
     </row>
     <row r="21">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-481529446.14</v>
+        <v>-447076968.15</v>
       </c>
       <c r="E21" t="n">
         <v>0.9936563817038003</v>
@@ -1160,10 +1160,10 @@
         <v>0.004148675157226389</v>
       </c>
       <c r="H21" t="n">
-        <v>-1997709.250674</v>
+        <v>-1854777.111131998</v>
       </c>
       <c r="I21" t="n">
-        <v>-1997709.250674</v>
+        <v>-1854777.111131998</v>
       </c>
     </row>
     <row r="22">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-787008130.14</v>
+        <v>-1011098505.86</v>
       </c>
       <c r="E22" t="n">
         <v>0.9856536327098718</v>
@@ -1195,10 +1195,10 @@
         <v>0.009282592027197278</v>
       </c>
       <c r="H22" t="n">
-        <v>-7305475.394177002</v>
+        <v>-9385614.929207116</v>
       </c>
       <c r="I22" t="n">
-        <v>-7305475.394177002</v>
+        <v>-9385614.929207116</v>
       </c>
     </row>
     <row r="23">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>134038813.24</v>
+        <v>192014855.79</v>
       </c>
       <c r="E23" t="n">
         <v>0.9761318955535195</v>
@@ -1230,10 +1230,10 @@
         <v>0.01537076312862229</v>
       </c>
       <c r="H23" t="n">
-        <v>2060278.848353681</v>
+        <v>2951414.865524658</v>
       </c>
       <c r="I23" t="n">
-        <v>1030139.42417684</v>
+        <v>1475707.432762329</v>
       </c>
     </row>
     <row r="24">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>327140775.91</v>
+        <v>347887543.05</v>
       </c>
       <c r="E24" t="n">
         <v>0.9667342819189046</v>
@@ -1265,10 +1265,10 @@
         <v>0.02137897737503558</v>
       </c>
       <c r="H24" t="n">
-        <v>6993935.246631475</v>
+        <v>7437479.911922666</v>
       </c>
       <c r="I24" t="n">
-        <v>3496967.623315738</v>
+        <v>3718739.955961333</v>
       </c>
     </row>
     <row r="25">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>597747588.01</v>
+        <v>626603273.1</v>
       </c>
       <c r="E25" t="n">
         <v>0.9524015829683793</v>
@@ -1300,10 +1300,10 @@
         <v>0.03023239035728253</v>
       </c>
       <c r="H25" t="n">
-        <v>18071338.41584242</v>
+        <v>18943714.75151012</v>
       </c>
       <c r="I25" t="n">
-        <v>9035669.207921209</v>
+        <v>9471857.375755059</v>
       </c>
     </row>
     <row r="26">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>285154483.07</v>
+        <v>300401739.98</v>
       </c>
       <c r="E26" t="n">
         <v>0.9333610479054046</v>
@@ -1335,10 +1335,10 @@
         <v>0.04174093883572272</v>
       </c>
       <c r="H26" t="n">
-        <v>11902615.836557</v>
+        <v>12539050.65464986</v>
       </c>
       <c r="I26" t="n">
-        <v>5951307.9182785</v>
+        <v>6269525.327324929</v>
       </c>
     </row>
     <row r="27">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>850770561.15</v>
+        <v>977534811.54</v>
       </c>
       <c r="E27" t="n">
         <v>0.9066754799235061</v>
@@ -1370,10 +1370,10 @@
         <v>0.05847495853512397</v>
       </c>
       <c r="H27" t="n">
-        <v>49748773.2861504</v>
+        <v>57161307.57144172</v>
       </c>
       <c r="I27" t="n">
-        <v>24874386.6430752</v>
+        <v>28580653.78572086</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1364232580.07</v>
+        <v>1136763875.88</v>
       </c>
       <c r="E28" t="n">
         <v>0.8730418834956067</v>
@@ -1405,10 +1405,10 @@
         <v>0.07983268361646123</v>
       </c>
       <c r="H28" t="n">
-        <v>108910347.9439969</v>
+        <v>90750910.84975024</v>
       </c>
       <c r="I28" t="n">
-        <v>54455173.97199846</v>
+        <v>45375455.42487512</v>
       </c>
     </row>
     <row r="29">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>831336595.33</v>
+        <v>1030678038.27</v>
       </c>
       <c r="E29" t="n">
         <v>0.839886760163754</v>
@@ -1440,10 +1440,10 @@
         <v>0.1000071588498553</v>
       </c>
       <c r="H29" t="n">
-        <v>83139610.94686522</v>
+        <v>103075182.2963252</v>
       </c>
       <c r="I29" t="n">
-        <v>41569805.47343261</v>
+        <v>51537591.14816258</v>
       </c>
     </row>
     <row r="30">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>163716720.8</v>
+        <v>164642316.19</v>
       </c>
       <c r="E30" t="n">
         <v>0.8060794216350962</v>
@@ -1475,10 +1475,10 @@
         <v>0.1188174585554111</v>
       </c>
       <c r="H30" t="n">
-        <v>19452404.68848182</v>
+        <v>19562381.58037222</v>
       </c>
       <c r="I30" t="n">
-        <v>9726202.344240909</v>
+        <v>9781190.790186111</v>
       </c>
     </row>
     <row r="31">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>298627003.45</v>
+        <v>300164895.95</v>
       </c>
       <c r="E31" t="n">
         <v>0.7725125366488534</v>
@@ -1510,10 +1510,10 @@
         <v>0.1363083780988569</v>
       </c>
       <c r="H31" t="n">
-        <v>40705362.49679124</v>
+        <v>40914990.12915663</v>
       </c>
       <c r="I31" t="n">
-        <v>20352681.24839562</v>
+        <v>20457495.06457832</v>
       </c>
     </row>
     <row r="32">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>293231811.97</v>
+        <v>294033463.53</v>
       </c>
       <c r="E32" t="n">
         <v>0.7390723504327896</v>
@@ -1545,10 +1545,10 @@
         <v>0.1524189448946068</v>
       </c>
       <c r="H32" t="n">
-        <v>44694083.39000115</v>
+        <v>44816270.27494946</v>
       </c>
       <c r="I32" t="n">
-        <v>22347041.69500057</v>
+        <v>22408135.13747473</v>
       </c>
     </row>
     <row r="33">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>241079539.25</v>
+        <v>240382289.04</v>
       </c>
       <c r="E33" t="n">
         <v>0.7058360643204235</v>
@@ -1580,10 +1580,10 @@
         <v>0.1671173700222426</v>
       </c>
       <c r="H33" t="n">
-        <v>40288578.565634</v>
+        <v>40172055.94429135</v>
       </c>
       <c r="I33" t="n">
-        <v>20144289.282817</v>
+        <v>20086027.97214567</v>
       </c>
     </row>
     <row r="34">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>152684438.78</v>
+        <v>150566167.36</v>
       </c>
       <c r="E34" t="n">
         <v>0.6740936305925465</v>
@@ -1615,10 +1615,10 @@
         <v>0.1807074230390667</v>
       </c>
       <c r="H34" t="n">
-        <v>27591211.47009994</v>
+        <v>27208424.10049444</v>
       </c>
       <c r="I34" t="n">
-        <v>13795605.73504997</v>
+        <v>13604212.05024722</v>
       </c>
     </row>
     <row r="35">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12791711.15</v>
+        <v>12366500.87</v>
       </c>
       <c r="E35" t="n">
         <v>0.5835756277426192</v>
@@ -1650,10 +1650,10 @@
         <v>0.2140775985160066</v>
       </c>
       <c r="H35" t="n">
-        <v>2738418.803902425</v>
+        <v>2647390.808295707</v>
       </c>
       <c r="I35" t="n">
-        <v>1369209.401951213</v>
+        <v>1323695.404147853</v>
       </c>
     </row>
     <row r="36">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-1336496145.66</v>
+        <v>-1336575420.08</v>
       </c>
       <c r="E36" t="n">
         <v>0.999906031812547</v>
@@ -1685,10 +1685,10 @@
         <v>7.797724224745117e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>-104216.2837129146</v>
+        <v>-104222.465313567</v>
       </c>
       <c r="I36" t="n">
-        <v>-104216.2837129146</v>
+        <v>-104222.465313567</v>
       </c>
     </row>
     <row r="37">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-294615437.6</v>
+        <v>-261189614.82</v>
       </c>
       <c r="E37" t="n">
         <v>0.9983821828874917</v>
@@ -1720,10 +1720,10 @@
         <v>0.000857634379940464</v>
       </c>
       <c r="H37" t="n">
-        <v>-252672.3281469644</v>
+        <v>-224005.1933530393</v>
       </c>
       <c r="I37" t="n">
-        <v>-252672.3281469644</v>
+        <v>-224005.1933530393</v>
       </c>
     </row>
     <row r="38">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-481529446.14</v>
+        <v>-447076968.15</v>
       </c>
       <c r="E38" t="n">
         <v>0.9936563817038003</v>
@@ -1755,10 +1755,10 @@
         <v>0.002842264830571484</v>
       </c>
       <c r="H38" t="n">
-        <v>-1368634.209648287</v>
+        <v>-1270711.143131272</v>
       </c>
       <c r="I38" t="n">
-        <v>-1368634.209648287</v>
+        <v>-1270711.143131272</v>
       </c>
     </row>
     <row r="39">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-787008130.14</v>
+        <v>-1011098505.86</v>
       </c>
       <c r="E39" t="n">
         <v>0.9856536327098718</v>
@@ -1790,10 +1790,10 @@
         <v>0.004190624857375314</v>
       </c>
       <c r="H39" t="n">
-        <v>-3298055.83312115</v>
+        <v>-4237134.531911955</v>
       </c>
       <c r="I39" t="n">
-        <v>-3298055.83312115</v>
+        <v>-4237134.531911955</v>
       </c>
     </row>
     <row r="40">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>134038813.24</v>
+        <v>192014855.79</v>
       </c>
       <c r="E40" t="n">
         <v>0.9761318955535195</v>
@@ -1825,10 +1825,10 @@
         <v>0.003588231255082563</v>
       </c>
       <c r="H40" t="n">
-        <v>480962.2590619425</v>
+        <v>688993.7069858491</v>
       </c>
       <c r="I40" t="n">
-        <v>240481.1295309713</v>
+        <v>344496.8534929245</v>
       </c>
     </row>
     <row r="41">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>327140775.91</v>
+        <v>347887543.05</v>
       </c>
       <c r="E41" t="n">
         <v>0.9667342819189046</v>
@@ -1860,10 +1860,10 @@
         <v>0.001347768023809648</v>
       </c>
       <c r="H41" t="n">
-        <v>440909.8770557756</v>
+        <v>468871.7064044923</v>
       </c>
       <c r="I41" t="n">
-        <v>220454.9385278878</v>
+        <v>234435.8532022462</v>
       </c>
     </row>
     <row r="42">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>597747588.01</v>
+        <v>626603273.1</v>
       </c>
       <c r="E42" t="n">
         <v>0.9524015829683793</v>
@@ -1895,10 +1895,10 @@
         <v>-0.003700723745374557</v>
       </c>
       <c r="H42" t="n">
-        <v>-2212098.692688975</v>
+        <v>-2318885.611690588</v>
       </c>
       <c r="I42" t="n">
-        <v>-2212098.692688975</v>
+        <v>-2318885.611690588</v>
       </c>
     </row>
     <row r="43">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>285154483.07</v>
+        <v>300401739.98</v>
       </c>
       <c r="E43" t="n">
         <v>0.9333610479054046</v>
@@ -1930,10 +1930,10 @@
         <v>-0.01168774742577749</v>
       </c>
       <c r="H43" t="n">
-        <v>-3332813.575450305</v>
+        <v>-3511019.663150325</v>
       </c>
       <c r="I43" t="n">
-        <v>-3332813.575450305</v>
+        <v>-3511019.663150325</v>
       </c>
     </row>
     <row r="44">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>850770561.15</v>
+        <v>977534811.54</v>
       </c>
       <c r="E44" t="n">
         <v>0.9066754799235061</v>
@@ -1965,10 +1965,10 @@
         <v>-0.02354447052112385</v>
       </c>
       <c r="H44" t="n">
-        <v>-20030942.39723617</v>
+        <v>-23015539.55367589</v>
       </c>
       <c r="I44" t="n">
-        <v>-20030942.39723617</v>
+        <v>-23015539.55367589</v>
       </c>
     </row>
     <row r="45">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1364232580.07</v>
+        <v>1136763875.88</v>
       </c>
       <c r="E45" t="n">
         <v>0.8730418834956067</v>
@@ -2000,10 +2000,10 @@
         <v>-0.03709517753986769</v>
       </c>
       <c r="H45" t="n">
-        <v>-50606449.76336841</v>
+        <v>-42168457.79667671</v>
       </c>
       <c r="I45" t="n">
-        <v>-50606449.76336841</v>
+        <v>-42168457.79667671</v>
       </c>
     </row>
     <row r="46">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>831336595.33</v>
+        <v>1030678038.27</v>
       </c>
       <c r="E46" t="n">
         <v>0.839886760163754</v>
@@ -2035,10 +2035,10 @@
         <v>-0.04807062925974992</v>
       </c>
       <c r="H46" t="n">
-        <v>-39962873.26417118</v>
+        <v>-49545341.86384351</v>
       </c>
       <c r="I46" t="n">
-        <v>-39962873.26417118</v>
+        <v>-49545341.86384351</v>
       </c>
     </row>
     <row r="47">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>163716720.8</v>
+        <v>164642316.19</v>
       </c>
       <c r="E47" t="n">
         <v>0.8060794216350962</v>
@@ -2070,10 +2070,10 @@
         <v>-0.05707337113962196</v>
       </c>
       <c r="H47" t="n">
-        <v>-9343865.167980267</v>
+        <v>-9396692.017198861</v>
       </c>
       <c r="I47" t="n">
-        <v>-9343865.167980267</v>
+        <v>-9396692.017198861</v>
       </c>
     </row>
     <row r="48">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>298627003.45</v>
+        <v>300164895.95</v>
       </c>
       <c r="E48" t="n">
         <v>0.7725125366488534</v>
@@ -2105,10 +2105,10 @@
         <v>-0.06464828621749663</v>
       </c>
       <c r="H48" t="n">
-        <v>-19305723.99130895</v>
+        <v>-19405146.10582069</v>
       </c>
       <c r="I48" t="n">
-        <v>-19305723.99130895</v>
+        <v>-19405146.10582069</v>
       </c>
     </row>
     <row r="49">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>293231811.97</v>
+        <v>294033463.53</v>
       </c>
       <c r="E49" t="n">
         <v>0.7390723504327896</v>
@@ -2140,10 +2140,10 @@
         <v>-0.07106709005817402</v>
       </c>
       <c r="H49" t="n">
-        <v>-20839131.58919354</v>
+        <v>-20896102.63280334</v>
       </c>
       <c r="I49" t="n">
-        <v>-20839131.58919354</v>
+        <v>-20896102.63280334</v>
       </c>
     </row>
     <row r="50">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>241079539.25</v>
+        <v>240382289.04</v>
       </c>
       <c r="E50" t="n">
         <v>0.7058360643204235</v>
@@ -2175,10 +2175,10 @@
         <v>-0.07648141160373034</v>
       </c>
       <c r="H50" t="n">
-        <v>-18438103.47061691</v>
+        <v>-18384776.79031512</v>
       </c>
       <c r="I50" t="n">
-        <v>-18438103.47061691</v>
+        <v>-18384776.79031512</v>
       </c>
     </row>
     <row r="51">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>152684438.78</v>
+        <v>150566167.36</v>
       </c>
       <c r="E51" t="n">
         <v>0.6740936305925465</v>
@@ -2210,10 +2210,10 @@
         <v>-0.08112320091848635</v>
       </c>
       <c r="H51" t="n">
-        <v>-12386250.40427627</v>
+        <v>-12214409.44627172</v>
       </c>
       <c r="I51" t="n">
-        <v>-12386250.40427627</v>
+        <v>-12214409.44627172</v>
       </c>
     </row>
     <row r="52">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12791711.15</v>
+        <v>12366500.87</v>
       </c>
       <c r="E52" t="n">
         <v>0.5835756277426192</v>
@@ -2245,10 +2245,10 @@
         <v>-0.09061680299551267</v>
       </c>
       <c r="H52" t="n">
-        <v>-1159143.969255053</v>
+        <v>-1120612.773080626</v>
       </c>
       <c r="I52" t="n">
-        <v>-1159143.969255053</v>
+        <v>-1120612.773080626</v>
       </c>
     </row>
     <row r="53">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1336496145.66</v>
+        <v>-1336575420.08</v>
       </c>
       <c r="E53" t="n">
         <v>0.999906031812547</v>
@@ -2280,10 +2280,10 @@
         <v>8.749858685930256e-06</v>
       </c>
       <c r="H53" t="n">
-        <v>-11694.15240881546</v>
+        <v>-11694.84604878787</v>
       </c>
       <c r="I53" t="n">
-        <v>-11694.15240881546</v>
+        <v>-11694.84604878787</v>
       </c>
     </row>
     <row r="54">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-294615437.6</v>
+        <v>-261189614.82</v>
       </c>
       <c r="E54" t="n">
         <v>0.9983821828874917</v>
@@ -2315,10 +2315,10 @@
         <v>-0.00107465764159409</v>
       </c>
       <c r="H54" t="n">
-        <v>316610.7313484268</v>
+        <v>280689.41547133</v>
       </c>
       <c r="I54" t="n">
-        <v>158305.3656742134</v>
+        <v>140344.707735665</v>
       </c>
     </row>
     <row r="55">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-481529446.14</v>
+        <v>-447076968.15</v>
       </c>
       <c r="E55" t="n">
         <v>0.9936563817038003</v>
@@ -2350,10 +2350,10 @@
         <v>-0.003624512892459575</v>
       </c>
       <c r="H55" t="n">
-        <v>1745309.685633348</v>
+        <v>1620436.234981414</v>
       </c>
       <c r="I55" t="n">
-        <v>872654.8428166742</v>
+        <v>810218.1174907068</v>
       </c>
     </row>
     <row r="56">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-787008130.14</v>
+        <v>-1011098505.86</v>
       </c>
       <c r="E56" t="n">
         <v>0.9856536327098718</v>
@@ -2385,10 +2385,10 @@
         <v>-0.00575832701755552</v>
       </c>
       <c r="H56" t="n">
-        <v>4531850.178821012</v>
+        <v>5822235.843703656</v>
       </c>
       <c r="I56" t="n">
-        <v>2265925.089410506</v>
+        <v>2911117.921851828</v>
       </c>
     </row>
     <row r="57">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>134038813.24</v>
+        <v>192014855.79</v>
       </c>
       <c r="E57" t="n">
         <v>0.9761318955535195</v>
@@ -2420,10 +2420,10 @@
         <v>-0.005916553585663675</v>
       </c>
       <c r="H57" t="n">
-        <v>-793047.8210932257</v>
+        <v>-1136066.183525018</v>
       </c>
       <c r="I57" t="n">
-        <v>-793047.8210932257</v>
+        <v>-1136066.183525018</v>
       </c>
     </row>
     <row r="58">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>327140775.91</v>
+        <v>347887543.05</v>
       </c>
       <c r="E58" t="n">
         <v>0.9667342819189046</v>
@@ -2455,10 +2455,10 @@
         <v>-0.004299740059850787</v>
       </c>
       <c r="H58" t="n">
-        <v>-1406620.299390896</v>
+        <v>-1495826.00517515</v>
       </c>
       <c r="I58" t="n">
-        <v>-1406620.299390896</v>
+        <v>-1495826.00517515</v>
       </c>
     </row>
     <row r="59">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>597747588.01</v>
+        <v>626603273.1</v>
       </c>
       <c r="E59" t="n">
         <v>0.9524015829683793</v>
@@ -2490,10 +2490,10 @@
         <v>5.935525280276188e-06</v>
       </c>
       <c r="H59" t="n">
-        <v>3547.94591985747</v>
+        <v>3719.219568188855</v>
       </c>
       <c r="I59" t="n">
-        <v>1773.972959928735</v>
+        <v>1859.609784094427</v>
       </c>
     </row>
     <row r="60">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>285154483.07</v>
+        <v>300401739.98</v>
       </c>
       <c r="E60" t="n">
         <v>0.9333610479054046</v>
@@ -2525,10 +2525,10 @@
         <v>0.007262963541339373</v>
       </c>
       <c r="H60" t="n">
-        <v>2071066.614186886</v>
+        <v>2181806.88522965</v>
       </c>
       <c r="I60" t="n">
-        <v>1035533.307093443</v>
+        <v>1090903.442614825</v>
       </c>
     </row>
     <row r="61">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>850770561.15</v>
+        <v>977534811.54</v>
       </c>
       <c r="E61" t="n">
         <v>0.9066754799235061</v>
@@ -2560,10 +2560,10 @@
         <v>0.01838001221226671</v>
       </c>
       <c r="H61" t="n">
-        <v>15637173.303774</v>
+        <v>17967101.77402103</v>
       </c>
       <c r="I61" t="n">
-        <v>7818586.651886999</v>
+        <v>8983550.887010517</v>
       </c>
     </row>
     <row r="62">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1364232580.07</v>
+        <v>1136763875.88</v>
       </c>
       <c r="E62" t="n">
         <v>0.8730418834956067</v>
@@ -2595,10 +2595,10 @@
         <v>0.03130191235040702</v>
       </c>
       <c r="H62" t="n">
-        <v>42703088.64692077</v>
+        <v>35582883.20590472</v>
       </c>
       <c r="I62" t="n">
-        <v>21351544.32346039</v>
+        <v>17791441.60295236</v>
       </c>
     </row>
     <row r="63">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>831336595.33</v>
+        <v>1030678038.27</v>
       </c>
       <c r="E63" t="n">
         <v>0.839886760163754</v>
@@ -2630,10 +2630,10 @@
         <v>0.04188199495808165</v>
       </c>
       <c r="H63" t="n">
-        <v>34818035.09407982</v>
+        <v>43166852.40222962</v>
       </c>
       <c r="I63" t="n">
-        <v>17409017.54703991</v>
+        <v>21583426.20111481</v>
       </c>
     </row>
     <row r="64">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>163716720.8</v>
+        <v>164642316.19</v>
       </c>
       <c r="E64" t="n">
         <v>0.8060794216350962</v>
@@ -2665,10 +2665,10 @@
         <v>0.05069529339115386</v>
       </c>
       <c r="H64" t="n">
-        <v>8299667.193993622</v>
+        <v>8346590.523851171</v>
       </c>
       <c r="I64" t="n">
-        <v>4149833.596996811</v>
+        <v>4173295.261925586</v>
       </c>
     </row>
     <row r="65">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>298627003.45</v>
+        <v>300164895.95</v>
       </c>
       <c r="E65" t="n">
         <v>0.7725125366488534</v>
@@ -2700,10 +2700,10 @@
         <v>0.05828777906690807</v>
       </c>
       <c r="H65" t="n">
-        <v>17406304.80050639</v>
+        <v>17495945.13877505</v>
       </c>
       <c r="I65" t="n">
-        <v>8703152.400253197</v>
+        <v>8747972.569387525</v>
       </c>
     </row>
     <row r="66">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>293231811.97</v>
+        <v>294033463.53</v>
       </c>
       <c r="E66" t="n">
         <v>0.7390723504327896</v>
@@ -2735,10 +2735,10 @@
         <v>0.06493454530509235</v>
       </c>
       <c r="H66" t="n">
-        <v>19040874.37926029</v>
+        <v>19092929.25880201</v>
       </c>
       <c r="I66" t="n">
-        <v>9520437.189630143</v>
+        <v>9546464.629401004</v>
       </c>
     </row>
     <row r="67">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>241079539.25</v>
+        <v>240382289.04</v>
       </c>
       <c r="E67" t="n">
         <v>0.7058360643204235</v>
@@ -2770,10 +2770,10 @@
         <v>0.0707747284866409</v>
       </c>
       <c r="H67" t="n">
-        <v>17062338.93410324</v>
+        <v>17012991.23980324</v>
       </c>
       <c r="I67" t="n">
-        <v>8531169.46705162</v>
+        <v>8506495.619901618</v>
       </c>
     </row>
     <row r="68">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>152684438.78</v>
+        <v>150566167.36</v>
       </c>
       <c r="E68" t="n">
         <v>0.6740936305925465</v>
@@ -2805,10 +2805,10 @@
         <v>0.07601335275394061</v>
       </c>
       <c r="H68" t="n">
-        <v>11606056.10502159</v>
+        <v>11445039.19234454</v>
       </c>
       <c r="I68" t="n">
-        <v>5803028.052510795</v>
+        <v>5722519.596172269</v>
       </c>
     </row>
     <row r="69">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12791711.15</v>
+        <v>12366500.87</v>
       </c>
       <c r="E69" t="n">
         <v>0.5835756277426192</v>
@@ -2840,10 +2840,10 @@
         <v>0.08811450570325163</v>
       </c>
       <c r="H69" t="n">
-        <v>1127135.305081022</v>
+        <v>1089668.111438881</v>
       </c>
       <c r="I69" t="n">
-        <v>563567.6525405112</v>
+        <v>544834.0557194407</v>
       </c>
     </row>
     <row r="70">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-1336496145.66</v>
+        <v>-1336575420.08</v>
       </c>
       <c r="E70" t="n">
         <v>0.999906031812547</v>
@@ -2875,10 +2875,10 @@
         <v>-8.56716656616463e-07</v>
       </c>
       <c r="H70" t="n">
-        <v>1144.998509490624</v>
+        <v>1145.066425206682</v>
       </c>
       <c r="I70" t="n">
-        <v>572.4992547453122</v>
+        <v>572.5332126033411</v>
       </c>
     </row>
     <row r="71">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-294615437.6</v>
+        <v>-261189614.82</v>
       </c>
       <c r="E71" t="n">
         <v>0.9983821828874917</v>
@@ -2910,10 +2910,10 @@
         <v>-0.001389003495161578</v>
       </c>
       <c r="H71" t="n">
-        <v>409221.8725549578</v>
+        <v>362793.2878848863</v>
       </c>
       <c r="I71" t="n">
-        <v>204610.9362774789</v>
+        <v>181396.6439424432</v>
       </c>
     </row>
     <row r="72">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-481529446.14</v>
+        <v>-447076968.15</v>
       </c>
       <c r="E72" t="n">
         <v>0.9936563817038003</v>
@@ -2945,10 +2945,10 @@
         <v>-0.004887294219023786</v>
       </c>
       <c r="H72" t="n">
-        <v>2353376.078409747</v>
+        <v>2184996.681898176</v>
       </c>
       <c r="I72" t="n">
-        <v>1176688.039204874</v>
+        <v>1092498.340949088</v>
       </c>
     </row>
     <row r="73">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-787008130.14</v>
+        <v>-1011098505.86</v>
       </c>
       <c r="E73" t="n">
         <v>0.9856536327098718</v>
@@ -2980,10 +2980,10 @@
         <v>-0.008818310314522182</v>
       </c>
       <c r="H73" t="n">
-        <v>6940081.911626377</v>
+        <v>8916180.383223206</v>
       </c>
       <c r="I73" t="n">
-        <v>3470040.955813189</v>
+        <v>4458090.191611603</v>
       </c>
     </row>
     <row r="74">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>134038813.24</v>
+        <v>192014855.79</v>
       </c>
       <c r="E74" t="n">
         <v>0.9761318955535195</v>
@@ -3015,10 +3015,10 @@
         <v>-0.01134588039219331</v>
       </c>
       <c r="H74" t="n">
-        <v>-1520788.342932577</v>
+        <v>-2178577.587317586</v>
       </c>
       <c r="I74" t="n">
-        <v>-1520788.342932577</v>
+        <v>-2178577.587317586</v>
       </c>
     </row>
     <row r="75">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>327140775.91</v>
+        <v>347887543.05</v>
       </c>
       <c r="E75" t="n">
         <v>0.9667342819189046</v>
@@ -3050,10 +3050,10 @@
         <v>-0.01225043827690986</v>
       </c>
       <c r="H75" t="n">
-        <v>-4007617.883145855</v>
+        <v>-4261774.873439847</v>
       </c>
       <c r="I75" t="n">
-        <v>-4007617.883145855</v>
+        <v>-4261774.873439847</v>
       </c>
     </row>
     <row r="76">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>597747588.01</v>
+        <v>626603273.1</v>
       </c>
       <c r="E76" t="n">
         <v>0.9524015829683793</v>
@@ -3085,10 +3085,10 @@
         <v>-0.01186315201310806</v>
       </c>
       <c r="H76" t="n">
-        <v>-7091170.502031318</v>
+        <v>-7433489.880696364</v>
       </c>
       <c r="I76" t="n">
-        <v>-7091170.502031318</v>
+        <v>-7433489.880696364</v>
       </c>
     </row>
     <row r="77">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>285154483.07</v>
+        <v>300401739.98</v>
       </c>
       <c r="E77" t="n">
         <v>0.9333610479054046</v>
@@ -3120,10 +3120,10 @@
         <v>-0.009881694503488636</v>
       </c>
       <c r="H77" t="n">
-        <v>-2817809.487997962</v>
+        <v>-2968478.222798788</v>
       </c>
       <c r="I77" t="n">
-        <v>-2817809.487997962</v>
+        <v>-2968478.222798788</v>
       </c>
     </row>
     <row r="78">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>850770561.15</v>
+        <v>977534811.54</v>
       </c>
       <c r="E78" t="n">
         <v>0.9066754799235061</v>
@@ -3155,10 +3155,10 @@
         <v>-0.006489882432710758</v>
       </c>
       <c r="H78" t="n">
-        <v>-5521400.919074859</v>
+        <v>-6344086.000776668</v>
       </c>
       <c r="I78" t="n">
-        <v>-5521400.919074859</v>
+        <v>-6344086.000776668</v>
       </c>
     </row>
     <row r="79">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1364232580.07</v>
+        <v>1136763875.88</v>
       </c>
       <c r="E79" t="n">
         <v>0.8730418834956067</v>
@@ -3190,10 +3190,10 @@
         <v>-0.003224039784762822</v>
       </c>
       <c r="H79" t="n">
-        <v>-4398340.113815312</v>
+        <v>-3664971.961718306</v>
       </c>
       <c r="I79" t="n">
-        <v>-4398340.113815312</v>
+        <v>-3664971.961718306</v>
       </c>
     </row>
     <row r="80">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>831336595.33</v>
+        <v>1030678038.27</v>
       </c>
       <c r="E80" t="n">
         <v>0.839886760163754</v>
@@ -3225,10 +3225,10 @@
         <v>-0.001468318235875343</v>
       </c>
       <c r="H80" t="n">
-        <v>-1220666.68307356</v>
+        <v>-1513363.358908066</v>
       </c>
       <c r="I80" t="n">
-        <v>-1220666.68307356</v>
+        <v>-1513363.358908066</v>
       </c>
     </row>
     <row r="81">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>163716720.8</v>
+        <v>164642316.19</v>
       </c>
       <c r="E81" t="n">
         <v>0.8060794216350962</v>
@@ -3260,10 +3260,10 @@
         <v>-0.000633919618590939</v>
       </c>
       <c r="H81" t="n">
-        <v>-103783.2412064953</v>
+        <v>-104369.9942830936</v>
       </c>
       <c r="I81" t="n">
-        <v>-103783.2412064953</v>
+        <v>-104369.9942830936</v>
       </c>
     </row>
     <row r="82">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>298627003.45</v>
+        <v>300164895.95</v>
       </c>
       <c r="E82" t="n">
         <v>0.7725125366488534</v>
@@ -3295,10 +3295,10 @@
         <v>-0.0002643337202767881</v>
       </c>
       <c r="H82" t="n">
-        <v>-78937.18679704775</v>
+        <v>-79343.70364295851</v>
       </c>
       <c r="I82" t="n">
-        <v>-78937.18679704775</v>
+        <v>-79343.70364295851</v>
       </c>
     </row>
     <row r="83">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>293231811.97</v>
+        <v>294033463.53</v>
       </c>
       <c r="E83" t="n">
         <v>0.7390723504327896</v>
@@ -3330,10 +3330,10 @@
         <v>-0.0001074027017012869</v>
       </c>
       <c r="H83" t="n">
-        <v>-31493.88883034175</v>
+        <v>-31579.9883737088</v>
       </c>
       <c r="I83" t="n">
-        <v>-31493.88883034175</v>
+        <v>-31579.9883737088</v>
       </c>
     </row>
     <row r="84">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>241079539.25</v>
+        <v>240382289.04</v>
       </c>
       <c r="E84" t="n">
         <v>0.7058360643204235</v>
@@ -3365,10 +3365,10 @@
         <v>-4.329964913651896e-05</v>
       </c>
       <c r="H84" t="n">
-        <v>-10438.65946351865</v>
+        <v>-10408.46877406529</v>
       </c>
       <c r="I84" t="n">
-        <v>-10438.65946351865</v>
+        <v>-10408.46877406529</v>
       </c>
     </row>
     <row r="85">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>152684438.78</v>
+        <v>150566167.36</v>
       </c>
       <c r="E85" t="n">
         <v>0.6740936305925465</v>
@@ -3400,10 +3400,10 @@
         <v>-1.696070784418247e-05</v>
       </c>
       <c r="H85" t="n">
-        <v>-2589.636158500543</v>
+        <v>-2553.708775811242</v>
       </c>
       <c r="I85" t="n">
-        <v>-2589.636158500543</v>
+        <v>-2553.708775811242</v>
       </c>
     </row>
     <row r="86">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12791711.15</v>
+        <v>12366500.87</v>
       </c>
       <c r="E86" t="n">
         <v>0.5835756277426192</v>
@@ -3435,10 +3435,10 @@
         <v>-1.008678731428958e-06</v>
       </c>
       <c r="H86" t="n">
-        <v>-12.90272697558766</v>
+        <v>-12.47382640976671</v>
       </c>
       <c r="I86" t="n">
-        <v>-12.90272697558766</v>
+        <v>-12.47382640976671</v>
       </c>
     </row>
     <row r="87">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-1336496145.66</v>
+        <v>-1336575420.08</v>
       </c>
       <c r="E87" t="n">
         <v>0.999906031812547</v>
@@ -3470,10 +3470,10 @@
         <v>9.39681874529974e-05</v>
       </c>
       <c r="H87" t="n">
-        <v>-125588.1203455874</v>
+        <v>-125595.5696191462</v>
       </c>
       <c r="I87" t="n">
-        <v>-125588.1203455874</v>
+        <v>-125595.5696191462</v>
       </c>
     </row>
     <row r="88">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-294615437.6</v>
+        <v>-261189614.82</v>
       </c>
       <c r="E88" t="n">
         <v>0.9983821828874917</v>
@@ -3505,10 +3505,10 @@
         <v>0.001387899570778783</v>
       </c>
       <c r="H88" t="n">
-        <v>-408896.6393898434</v>
+        <v>-362504.9543005537</v>
       </c>
       <c r="I88" t="n">
-        <v>-408896.6393898434</v>
+        <v>-362504.9543005537</v>
       </c>
     </row>
     <row r="89">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-481529446.14</v>
+        <v>-447076968.15</v>
       </c>
       <c r="E89" t="n">
         <v>0.9936563817038003</v>
@@ -3540,10 +3540,10 @@
         <v>0.004911064643535079</v>
       </c>
       <c r="H89" t="n">
-        <v>-2364822.237759183</v>
+        <v>-2195623.891220324</v>
       </c>
       <c r="I89" t="n">
-        <v>-2364822.237759183</v>
+        <v>-2195623.891220324</v>
       </c>
     </row>
     <row r="90">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-787008130.14</v>
+        <v>-1011098505.86</v>
       </c>
       <c r="E90" t="n">
         <v>0.9856536327098718</v>
@@ -3575,10 +3575,10 @@
         <v>0.008895199983645741</v>
       </c>
       <c r="H90" t="n">
-        <v>-7000594.706350393</v>
+        <v>-8993923.412790105</v>
       </c>
       <c r="I90" t="n">
-        <v>-7000594.706350393</v>
+        <v>-8993923.412790105</v>
       </c>
     </row>
     <row r="91">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>134038813.24</v>
+        <v>192014855.79</v>
       </c>
       <c r="E91" t="n">
         <v>0.9761318955535195</v>
@@ -3610,10 +3610,10 @@
         <v>0.01147716903300178</v>
       </c>
       <c r="H91" t="n">
-        <v>1538386.116538437</v>
+        <v>2203786.95674929</v>
       </c>
       <c r="I91" t="n">
-        <v>769193.0582692183</v>
+        <v>1101893.478374645</v>
       </c>
     </row>
     <row r="92">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>327140775.91</v>
+        <v>347887543.05</v>
       </c>
       <c r="E92" t="n">
         <v>0.9667342819189046</v>
@@ -3645,10 +3645,10 @@
         <v>0.01240503278375416</v>
       </c>
       <c r="H92" t="n">
-        <v>4058192.050066322</v>
+        <v>4315556.376594936</v>
       </c>
       <c r="I92" t="n">
-        <v>2029096.025033161</v>
+        <v>2157778.188297468</v>
       </c>
     </row>
     <row r="93">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>597747588.01</v>
+        <v>626603273.1</v>
       </c>
       <c r="E93" t="n">
         <v>0.9524015829683793</v>
@@ -3680,10 +3680,10 @@
         <v>0.01201262797217995</v>
       </c>
       <c r="H93" t="n">
-        <v>7180519.39603202</v>
+        <v>7527152.00590057</v>
       </c>
       <c r="I93" t="n">
-        <v>3590259.69801601</v>
+        <v>3763576.002950285</v>
       </c>
     </row>
     <row r="94">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>285154483.07</v>
+        <v>300401739.98</v>
       </c>
       <c r="E94" t="n">
         <v>0.9333610479054046</v>
@@ -3715,10 +3715,10 @@
         <v>0.009987366679108822</v>
       </c>
       <c r="H94" t="n">
-        <v>2847942.382611819</v>
+        <v>3000222.328222564</v>
       </c>
       <c r="I94" t="n">
-        <v>1423971.191305909</v>
+        <v>1500111.164111282</v>
       </c>
     </row>
     <row r="95">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>850770561.15</v>
+        <v>977534811.54</v>
       </c>
       <c r="E95" t="n">
         <v>0.9066754799235061</v>
@@ -3750,10 +3750,10 @@
         <v>0.006535572677782708</v>
       </c>
       <c r="H95" t="n">
-        <v>5560272.834513803</v>
+        <v>6388749.805882293</v>
       </c>
       <c r="I95" t="n">
-        <v>2780136.417256902</v>
+        <v>3194374.902941146</v>
       </c>
     </row>
     <row r="96">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1364232580.07</v>
+        <v>1136763875.88</v>
       </c>
       <c r="E96" t="n">
         <v>0.8730418834956067</v>
@@ -3785,10 +3785,10 @@
         <v>0.003235551599104936</v>
       </c>
       <c r="H96" t="n">
-        <v>4414044.905996541</v>
+        <v>3678058.176408258</v>
       </c>
       <c r="I96" t="n">
-        <v>2207022.45299827</v>
+        <v>1839029.088204129</v>
       </c>
     </row>
     <row r="97">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>831336595.33</v>
+        <v>1030678038.27</v>
       </c>
       <c r="E97" t="n">
         <v>0.839886760163754</v>
@@ -3820,10 +3820,10 @@
         <v>0.001470791926687531</v>
       </c>
       <c r="H97" t="n">
-        <v>1222723.152771263</v>
+        <v>1515912.937701658</v>
       </c>
       <c r="I97" t="n">
-        <v>611361.5763856317</v>
+        <v>757956.4688508292</v>
       </c>
     </row>
     <row r="98">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>163716720.8</v>
+        <v>164642316.19</v>
       </c>
       <c r="E98" t="n">
         <v>0.8060794216350962</v>
@@ -3855,10 +3855,10 @@
         <v>0.000634385103338575</v>
       </c>
       <c r="H98" t="n">
-        <v>103859.4488429606</v>
+        <v>104446.6327700955</v>
       </c>
       <c r="I98" t="n">
-        <v>51929.72442148032</v>
+        <v>52223.31638504774</v>
       </c>
     </row>
     <row r="99">
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>298627003.45</v>
+        <v>300164895.95</v>
       </c>
       <c r="E99" t="n">
         <v>0.7725125366488534</v>
@@ -3890,10 +3890,10 @@
         <v>0.0002641556154886482</v>
       </c>
       <c r="H99" t="n">
-        <v>78883.99989786542</v>
+        <v>79290.24283775828</v>
       </c>
       <c r="I99" t="n">
-        <v>39441.99994893271</v>
+        <v>39645.12141887914</v>
       </c>
     </row>
     <row r="100">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>293231811.97</v>
+        <v>294033463.53</v>
       </c>
       <c r="E100" t="n">
         <v>0.7390723504327896</v>
@@ -3925,10 +3925,10 @@
         <v>0.0001072133542818765</v>
       </c>
       <c r="H100" t="n">
-        <v>31438.36614345621</v>
+        <v>31524.31389616911</v>
       </c>
       <c r="I100" t="n">
-        <v>15719.1830717281</v>
+        <v>15762.15694808455</v>
       </c>
     </row>
     <row r="101">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>241079539.25</v>
+        <v>240382289.04</v>
       </c>
       <c r="E101" t="n">
         <v>0.7058360643204235</v>
@@ -3960,10 +3960,10 @@
         <v>4.218442338066453e-05</v>
       </c>
       <c r="H101" t="n">
-        <v>10169.80135213753</v>
+        <v>10140.38825407663</v>
       </c>
       <c r="I101" t="n">
-        <v>5084.900676068765</v>
+        <v>5070.194127038317</v>
       </c>
     </row>
     <row r="102">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>152684438.78</v>
+        <v>150566167.36</v>
       </c>
       <c r="E102" t="n">
         <v>0.6740936305925465</v>
@@ -3995,10 +3995,10 @@
         <v>1.659944883869446e-05</v>
       </c>
       <c r="H102" t="n">
-        <v>2534.477529993387</v>
+        <v>2499.315391930628</v>
       </c>
       <c r="I102" t="n">
-        <v>1267.238764996694</v>
+        <v>1249.657695965314</v>
       </c>
     </row>
     <row r="103">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12791711.15</v>
+        <v>12366500.87</v>
       </c>
       <c r="E103" t="n">
         <v>0.5835756277426192</v>
@@ -4030,10 +4030,10 @@
         <v>8.933136881328352e-07</v>
       </c>
       <c r="H103" t="n">
-        <v>11.42701066493641</v>
+        <v>11.04716450147762</v>
       </c>
       <c r="I103" t="n">
-        <v>5.713505332468205</v>
+        <v>5.523582250738808</v>
       </c>
     </row>
     <row r="104">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-1336496145.66</v>
+        <v>-1336575420.08</v>
       </c>
       <c r="E104" t="n">
         <v>0.999906031812547</v>
@@ -4065,10 +4065,10 @@
         <v>6.06503826584559e-05</v>
       </c>
       <c r="H104" t="n">
-        <v>-81059.00265583041</v>
+        <v>-81063.81067973844</v>
       </c>
       <c r="I104" t="n">
-        <v>-81059.00265583041</v>
+        <v>-81063.81067973844</v>
       </c>
     </row>
     <row r="105">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-294615437.6</v>
+        <v>-261189614.82</v>
       </c>
       <c r="E105" t="n">
         <v>0.9983821828874917</v>
@@ -4100,10 +4100,10 @@
         <v>0.0004286357166750632</v>
       </c>
       <c r="H105" t="n">
-        <v>-126282.6992392133</v>
+        <v>-111955.1977364544</v>
       </c>
       <c r="I105" t="n">
-        <v>-126282.6992392133</v>
+        <v>-111955.1977364544</v>
       </c>
     </row>
     <row r="106">
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-481529446.14</v>
+        <v>-447076968.15</v>
       </c>
       <c r="E106" t="n">
         <v>0.9936563817038003</v>
@@ -4135,10 +4135,10 @@
         <v>0.001657282796573178</v>
       </c>
       <c r="H106" t="n">
-        <v>-798030.4671312328</v>
+        <v>-740932.9680590898</v>
       </c>
       <c r="I106" t="n">
-        <v>-798030.4671312328</v>
+        <v>-740932.9680590898</v>
       </c>
     </row>
     <row r="107">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-787008130.14</v>
+        <v>-1011098505.86</v>
       </c>
       <c r="E107" t="n">
         <v>0.9856536327098718</v>
@@ -4170,10 +4170,10 @@
         <v>0.003701791136432875</v>
       </c>
       <c r="H107" t="n">
-        <v>-2913339.720452862</v>
+        <v>-3742875.487053071</v>
       </c>
       <c r="I107" t="n">
-        <v>-2913339.720452862</v>
+        <v>-3742875.487053071</v>
       </c>
     </row>
     <row r="108">
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>134038813.24</v>
+        <v>192014855.79</v>
       </c>
       <c r="E108" t="n">
         <v>0.9761318955535195</v>
@@ -4205,10 +4205,10 @@
         <v>0.00611886473883394</v>
       </c>
       <c r="H108" t="n">
-        <v>820165.3679693838</v>
+        <v>1174912.930425715</v>
       </c>
       <c r="I108" t="n">
-        <v>410082.6839846919</v>
+        <v>587456.4652128575</v>
       </c>
     </row>
     <row r="109">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>327140775.91</v>
+        <v>347887543.05</v>
       </c>
       <c r="E109" t="n">
         <v>0.9667342819189046</v>
@@ -4240,10 +4240,10 @@
         <v>0.008494727267819302</v>
       </c>
       <c r="H109" t="n">
-        <v>2778971.669538241</v>
+        <v>2955209.798081496</v>
       </c>
       <c r="I109" t="n">
-        <v>1389485.83476912</v>
+        <v>1477604.899040748</v>
       </c>
     </row>
     <row r="110">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>597747588.01</v>
+        <v>626603273.1</v>
       </c>
       <c r="E110" t="n">
         <v>0.9524015829683793</v>
@@ -4275,10 +4275,10 @@
         <v>0.01197966122818617</v>
       </c>
       <c r="H110" t="n">
-        <v>7160813.604325196</v>
+        <v>7506494.936210618</v>
       </c>
       <c r="I110" t="n">
-        <v>3580406.802162598</v>
+        <v>3753247.468105309</v>
       </c>
     </row>
     <row r="111">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>285154483.07</v>
+        <v>300401739.98</v>
       </c>
       <c r="E111" t="n">
         <v>0.9333610479054046</v>
@@ -4310,10 +4310,10 @@
         <v>0.01647754477361008</v>
       </c>
       <c r="H111" t="n">
-        <v>4698645.762181561</v>
+        <v>4949883.120590821</v>
       </c>
       <c r="I111" t="n">
-        <v>2349322.881090781</v>
+        <v>2474941.56029541</v>
       </c>
     </row>
     <row r="112">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>850770561.15</v>
+        <v>977534811.54</v>
       </c>
       <c r="E112" t="n">
         <v>0.9066754799235061</v>
@@ -4345,10 +4345,10 @@
         <v>0.02295203256100853</v>
       </c>
       <c r="H112" t="n">
-        <v>19526913.6214623</v>
+        <v>22436410.82398542</v>
       </c>
       <c r="I112" t="n">
-        <v>9763456.810731148</v>
+        <v>11218205.41199271</v>
       </c>
     </row>
     <row r="113">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1364232580.07</v>
+        <v>1136763875.88</v>
       </c>
       <c r="E113" t="n">
         <v>0.8730418834956067</v>
@@ -4380,10 +4380,10 @@
         <v>0.03109727088065561</v>
       </c>
       <c r="H113" t="n">
-        <v>42423910.08665249</v>
+        <v>35350254.17558433</v>
       </c>
       <c r="I113" t="n">
-        <v>21211955.04332624</v>
+        <v>17675127.08779217</v>
       </c>
     </row>
     <row r="114">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>831336595.33</v>
+        <v>1030678038.27</v>
       </c>
       <c r="E114" t="n">
         <v>0.839886760163754</v>
@@ -4415,10 +4415,10 @@
         <v>0.0386581374619398</v>
       </c>
       <c r="H114" t="n">
-        <v>32137924.37940816</v>
+        <v>39844093.28244411</v>
       </c>
       <c r="I114" t="n">
-        <v>16068962.18970408</v>
+        <v>19922046.64122206</v>
       </c>
     </row>
     <row r="115">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>163716720.8</v>
+        <v>164642316.19</v>
       </c>
       <c r="E115" t="n">
         <v>0.8060794216350962</v>
@@ -4450,10 +4450,10 @@
         <v>0.04557620122769612</v>
       </c>
       <c r="H115" t="n">
-        <v>7461586.211519344</v>
+        <v>7503771.333269411</v>
       </c>
       <c r="I115" t="n">
-        <v>3730793.105759672</v>
+        <v>3751885.666634705</v>
       </c>
     </row>
     <row r="116">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>298627003.45</v>
+        <v>300164895.95</v>
       </c>
       <c r="E116" t="n">
         <v>0.7725125366488534</v>
@@ -4485,10 +4485,10 @@
         <v>0.05188104408575822</v>
       </c>
       <c r="H116" t="n">
-        <v>15493080.73118732</v>
+        <v>15572868.19977898</v>
       </c>
       <c r="I116" t="n">
-        <v>7746540.365593661</v>
+        <v>7786434.099889489</v>
       </c>
     </row>
     <row r="117">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>293231811.97</v>
+        <v>294033463.53</v>
       </c>
       <c r="E117" t="n">
         <v>0.7390723504327896</v>
@@ -4520,10 +4520,10 @@
         <v>0.05756191118833565</v>
       </c>
       <c r="H117" t="n">
-        <v>16878983.51821188</v>
+        <v>16925128.11411259</v>
       </c>
       <c r="I117" t="n">
-        <v>8439491.759105939</v>
+        <v>8462564.057056295</v>
       </c>
     </row>
     <row r="118">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>241079539.25</v>
+        <v>240382289.04</v>
       </c>
       <c r="E118" t="n">
         <v>0.7058360643204235</v>
@@ -4555,10 +4555,10 @@
         <v>0.06261909581715475</v>
       </c>
       <c r="H118" t="n">
-        <v>15096182.76785127</v>
+        <v>15052521.59014275</v>
       </c>
       <c r="I118" t="n">
-        <v>7548091.383925634</v>
+        <v>7526260.795071374</v>
       </c>
     </row>
     <row r="119">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>152684438.78</v>
+        <v>150566167.36</v>
       </c>
       <c r="E119" t="n">
         <v>0.6740936305925465</v>
@@ -4590,10 +4590,10 @@
         <v>0.06717920059908133</v>
       </c>
       <c r="H119" t="n">
-        <v>10257218.54115977</v>
+        <v>10114914.76051229</v>
       </c>
       <c r="I119" t="n">
-        <v>5128609.270579887</v>
+        <v>5057457.380256145</v>
       </c>
     </row>
     <row r="120">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12791711.15</v>
+        <v>12366500.87</v>
       </c>
       <c r="E120" t="n">
         <v>0.5835756277426192</v>
@@ -4625,10 +4625,10 @@
         <v>0.07770212208989746</v>
       </c>
       <c r="H120" t="n">
-        <v>993943.1015160027</v>
+        <v>960903.3604255633</v>
       </c>
       <c r="I120" t="n">
-        <v>496971.5507580013</v>
+        <v>480451.6802127816</v>
       </c>
     </row>
   </sheetData>
@@ -4704,22 +4704,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D2" t="n">
-        <v>1794233839.47</v>
+        <v>1857625048.06</v>
       </c>
       <c r="E2" t="n">
-        <v>-122122222.0699999</v>
+        <v>-117121148.9100001</v>
       </c>
       <c r="F2" t="n">
-        <v>-122122222.0699999</v>
+        <v>-117121148.9100001</v>
       </c>
       <c r="G2" t="n">
-        <v>-10.17685183916666</v>
+        <v>-9.760095742500006</v>
       </c>
       <c r="H2" t="n">
-        <v>-10.17685183916666</v>
+        <v>-9.760095742500006</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4737,22 +4737,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D3" t="n">
-        <v>2049892910.4</v>
+        <v>2102562803.04</v>
       </c>
       <c r="E3" t="n">
-        <v>133536848.8600001</v>
+        <v>127816606.0699999</v>
       </c>
       <c r="F3" t="n">
-        <v>66768424.43000007</v>
+        <v>63908303.03499997</v>
       </c>
       <c r="G3" t="n">
-        <v>11.12807073833334</v>
+        <v>10.65138383916666</v>
       </c>
       <c r="H3" t="n">
-        <v>5.564035369166672</v>
+        <v>5.325691919583331</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4770,22 +4770,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D4" t="n">
-        <v>1870259103.15</v>
+        <v>1931849434.13</v>
       </c>
       <c r="E4" t="n">
-        <v>-46096958.38999987</v>
+        <v>-42896762.83999991</v>
       </c>
       <c r="F4" t="n">
-        <v>-46096958.38999987</v>
+        <v>-42896762.83999991</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.841413199166656</v>
+        <v>-3.574730236666659</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.841413199166656</v>
+        <v>-3.574730236666659</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4803,22 +4803,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D5" t="n">
-        <v>1951602159.12</v>
+        <v>2007074920.46</v>
       </c>
       <c r="E5" t="n">
-        <v>35246097.57999992</v>
+        <v>32328723.49000001</v>
       </c>
       <c r="F5" t="n">
-        <v>17623048.78999996</v>
+        <v>16164361.745</v>
       </c>
       <c r="G5" t="n">
-        <v>2.937174798333327</v>
+        <v>2.694060290833334</v>
       </c>
       <c r="H5" t="n">
-        <v>1.468587399166663</v>
+        <v>1.347030145416667</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4836,22 +4836,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D6" t="n">
-        <v>1895858582.06</v>
+        <v>1953863714.88</v>
       </c>
       <c r="E6" t="n">
-        <v>-20497479.48000002</v>
+        <v>-20882482.08999991</v>
       </c>
       <c r="F6" t="n">
-        <v>-20497479.48000002</v>
+        <v>-20882482.08999991</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.708123290000002</v>
+        <v>-1.740206840833326</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.708123290000002</v>
+        <v>-1.740206840833326</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4869,22 +4869,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D7" t="n">
-        <v>1937223352.26</v>
+        <v>1996023109.36</v>
       </c>
       <c r="E7" t="n">
-        <v>20867290.72000003</v>
+        <v>21276912.38999987</v>
       </c>
       <c r="F7" t="n">
-        <v>10433645.36000001</v>
+        <v>10638456.19499993</v>
       </c>
       <c r="G7" t="n">
-        <v>1.738940893333336</v>
+        <v>1.773076032499989</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8694704466666678</v>
+        <v>0.8865380162499945</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4902,22 +4902,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1916356061.54</v>
+        <v>1974746196.97</v>
       </c>
       <c r="D8" t="n">
-        <v>1968379211.04</v>
+        <v>2024574398.13</v>
       </c>
       <c r="E8" t="n">
-        <v>52023149.5</v>
+        <v>49828201.16000009</v>
       </c>
       <c r="F8" t="n">
-        <v>26011574.75</v>
+        <v>24914100.58000004</v>
       </c>
       <c r="G8" t="n">
-        <v>4.335262458333333</v>
+        <v>4.152350096666674</v>
       </c>
       <c r="H8" t="n">
-        <v>2.167631229166667</v>
+        <v>2.076175048333337</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5047,19 +5047,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G2" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="J2" t="n">
         <v>-620000000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="L2" t="n">
         <v>0.03432749872940843</v>
@@ -5071,10 +5071,10 @@
         <v>0.02500481880599148</v>
       </c>
       <c r="O2" t="n">
-        <v>-32631303.37430746</v>
+        <v>-32132037.17578087</v>
       </c>
       <c r="P2" t="n">
-        <v>-32631303.37430746</v>
+        <v>-32132037.17578087</v>
       </c>
     </row>
     <row r="3">
@@ -5105,19 +5105,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="H3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="J3" t="n">
         <v>-62000000</v>
       </c>
       <c r="K3" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="L3" t="n">
         <v>0.03782665436246635</v>
@@ -5129,10 +5129,10 @@
         <v>0.0251058158502353</v>
       </c>
       <c r="O3" t="n">
-        <v>17714781.8447465</v>
+        <v>22220135.88858093</v>
       </c>
       <c r="P3" t="n">
-        <v>8857390.922373248</v>
+        <v>11110067.94429046</v>
       </c>
     </row>
     <row r="4">
@@ -5163,19 +5163,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="H4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="L4" t="n">
         <v>0.03830470017405307</v>
@@ -5187,10 +5187,10 @@
         <v>0.02521323244800655</v>
       </c>
       <c r="O4" t="n">
-        <v>16199877.06434811</v>
+        <v>16746397.45056022</v>
       </c>
       <c r="P4" t="n">
-        <v>8099938.532174057</v>
+        <v>8373198.72528011</v>
       </c>
     </row>
     <row r="5">
@@ -5221,19 +5221,19 @@
         <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="H5" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I5" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="J5" t="n">
         <v>-124000000</v>
       </c>
       <c r="K5" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="L5" t="n">
         <v>0.03852218097221538</v>
@@ -5245,10 +5245,10 @@
         <v>0.02532026333962101</v>
       </c>
       <c r="O5" t="n">
-        <v>21234360.61087049</v>
+        <v>15363042.72671686</v>
       </c>
       <c r="P5" t="n">
-        <v>10617180.30543524</v>
+        <v>7681521.363358428</v>
       </c>
     </row>
     <row r="6">
@@ -5279,19 +5279,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="H6" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I6" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="J6" t="n">
         <v>-62000000</v>
       </c>
       <c r="K6" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="L6" t="n">
         <v>0.03873510939427094</v>
@@ -5303,10 +5303,10 @@
         <v>0.02542872476626745</v>
       </c>
       <c r="O6" t="n">
-        <v>-5671815.360242249</v>
+        <v>-9040378.857582752</v>
       </c>
       <c r="P6" t="n">
-        <v>-5671815.360242249</v>
+        <v>-9040378.857582752</v>
       </c>
     </row>
     <row r="7">
@@ -5337,19 +5337,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="H7" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I7" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="J7" t="n">
         <v>-62000000</v>
       </c>
       <c r="K7" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="L7" t="n">
         <v>0.03888939094511485</v>
@@ -5361,10 +5361,10 @@
         <v>0.02553821260711615</v>
       </c>
       <c r="O7" t="n">
-        <v>-5086871.529461038</v>
+        <v>-5711671.463205808</v>
       </c>
       <c r="P7" t="n">
-        <v>-5086871.529461038</v>
+        <v>-5711671.463205808</v>
       </c>
     </row>
     <row r="8">
@@ -5395,19 +5395,19 @@
         <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="H8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="J8" t="n">
         <v>-31000000</v>
       </c>
       <c r="K8" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="L8" t="n">
         <v>0.03901400018340251</v>
@@ -5419,10 +5419,10 @@
         <v>0.02564775160277089</v>
       </c>
       <c r="O8" t="n">
-        <v>667437.9128207581</v>
+        <v>2663465.66420105</v>
       </c>
       <c r="P8" t="n">
-        <v>333718.956410379</v>
+        <v>1331732.832100525</v>
       </c>
     </row>
     <row r="9">
@@ -5453,19 +5453,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="H9" t="n">
         <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="J9" t="n">
         <v>-31000000</v>
       </c>
       <c r="K9" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="L9" t="n">
         <v>0.03908855826627113</v>
@@ -5477,10 +5477,10 @@
         <v>0.02575828679253624</v>
       </c>
       <c r="O9" t="n">
-        <v>-526190.7388415849</v>
+        <v>644274.3512393761</v>
       </c>
       <c r="P9" t="n">
-        <v>-526190.7388415849</v>
+        <v>322137.1756196881</v>
       </c>
     </row>
     <row r="10">
@@ -5511,19 +5511,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="H10" t="n">
         <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="J10" t="n">
         <v>-31000000</v>
       </c>
       <c r="K10" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="L10" t="n">
         <v>0.03915884386251234</v>
@@ -5535,10 +5535,10 @@
         <v>0.02586772256944581</v>
       </c>
       <c r="O10" t="n">
-        <v>-155238.837347826</v>
+        <v>-136674.061501014</v>
       </c>
       <c r="P10" t="n">
-        <v>-155238.837347826</v>
+        <v>-136674.061501014</v>
       </c>
     </row>
     <row r="11">
@@ -5569,19 +5569,19 @@
         <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="H11" t="n">
         <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="J11" t="n">
         <v>-31000000</v>
       </c>
       <c r="K11" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="L11" t="n">
         <v>0.03922681220647117</v>
@@ -5593,10 +5593,10 @@
         <v>0.02597850453979926</v>
       </c>
       <c r="O11" t="n">
-        <v>-123518.1300839188</v>
+        <v>-127881.890361634</v>
       </c>
       <c r="P11" t="n">
-        <v>-123518.1300839188</v>
+        <v>-127881.890361634</v>
       </c>
     </row>
     <row r="12">
@@ -5627,19 +5627,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="H12" t="n">
         <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="J12" t="n">
         <v>-31000000</v>
       </c>
       <c r="K12" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="L12" t="n">
         <v>0.03929424848359133</v>
@@ -5651,10 +5651,10 @@
         <v>0.02608953222428303</v>
       </c>
       <c r="O12" t="n">
-        <v>-73224.96182435016</v>
+        <v>-79426.03137597056</v>
       </c>
       <c r="P12" t="n">
-        <v>-73224.96182435016</v>
+        <v>-79426.03137597056</v>
       </c>
     </row>
     <row r="13">
@@ -5685,19 +5685,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G13" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="H13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="L13" t="n">
         <v>0.03936107056455495</v>
@@ -5709,10 +5709,10 @@
         <v>0.02620112954634799</v>
       </c>
       <c r="O13" t="n">
-        <v>82865.02185148366</v>
+        <v>271017.7395883861</v>
       </c>
       <c r="P13" t="n">
-        <v>41432.51092574183</v>
+        <v>135508.869794193</v>
       </c>
     </row>
     <row r="14">
@@ -5743,19 +5743,19 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="H14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="J14" t="n">
         <v>-62000000</v>
       </c>
       <c r="K14" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="L14" t="n">
         <v>0.03942868733737526</v>
@@ -5801,19 +5801,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G15" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="J15" t="n">
         <v>-620000000</v>
       </c>
       <c r="K15" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="L15" t="n">
         <v>0.03432749872940843</v>
@@ -5825,10 +5825,10 @@
         <v>-0.02499999878494696</v>
       </c>
       <c r="O15" t="n">
-        <v>17167479.74867882</v>
+        <v>16668309.79054502</v>
       </c>
       <c r="P15" t="n">
-        <v>8583739.874339411</v>
+        <v>8334154.895272509</v>
       </c>
     </row>
     <row r="16">
@@ -5859,19 +5859,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="H16" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I16" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="J16" t="n">
         <v>-62000000</v>
       </c>
       <c r="K16" t="n">
-        <v>831750589.7910959</v>
+        <v>1027519240.111096</v>
       </c>
       <c r="L16" t="n">
         <v>0.03782665436246635</v>
@@ -5883,10 +5883,10 @@
         <v>-0.02505175249492542</v>
       </c>
       <c r="O16" t="n">
-        <v>-19100409.08687521</v>
+        <v>-23596061.21311725</v>
       </c>
       <c r="P16" t="n">
-        <v>-19100409.08687521</v>
+        <v>-23596061.21311725</v>
       </c>
     </row>
     <row r="17">
@@ -5917,19 +5917,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="H17" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I17" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="L17" t="n">
         <v>0.03830470017405307</v>
@@ -5941,10 +5941,10 @@
         <v>-0.02510607109988339</v>
       </c>
       <c r="O17" t="n">
-        <v>-16131024.30343279</v>
+        <v>-16675221.86723472</v>
       </c>
       <c r="P17" t="n">
-        <v>-16131024.30343279</v>
+        <v>-16675221.86723472</v>
       </c>
     </row>
     <row r="18">
@@ -5975,19 +5975,19 @@
         <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="H18" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I18" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="J18" t="n">
         <v>-124000000</v>
       </c>
       <c r="K18" t="n">
-        <v>1242174816.538767</v>
+        <v>932998575.3387671</v>
       </c>
       <c r="L18" t="n">
         <v>0.03852218097221538</v>
@@ -5999,10 +5999,10 @@
         <v>-0.02516160099667442</v>
       </c>
       <c r="O18" t="n">
-        <v>-23441330.32639927</v>
+        <v>-17606803.4123548</v>
       </c>
       <c r="P18" t="n">
-        <v>-23441330.32639927</v>
+        <v>-17606803.4123548</v>
       </c>
     </row>
     <row r="19">
@@ -6033,19 +6033,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="H19" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I19" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="J19" t="n">
         <v>-62000000</v>
       </c>
       <c r="K19" t="n">
-        <v>-272571360.4816439</v>
+        <v>-471277559.5716438</v>
       </c>
       <c r="L19" t="n">
         <v>0.03873510939427094</v>
@@ -6057,10 +6057,10 @@
         <v>-0.02521743137943178</v>
       </c>
       <c r="O19" t="n">
-        <v>4582366.385962811</v>
+        <v>7922939.679442667</v>
       </c>
       <c r="P19" t="n">
-        <v>2291183.192981406</v>
+        <v>3961469.839721334</v>
       </c>
     </row>
     <row r="20">
@@ -6091,19 +6091,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="H20" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I20" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="J20" t="n">
         <v>-62000000</v>
       </c>
       <c r="K20" t="n">
-        <v>-279462863.0247945</v>
+        <v>-321403370.6547946</v>
       </c>
       <c r="L20" t="n">
         <v>0.03888939094511485</v>
@@ -6115,10 +6115,10 @@
         <v>-0.02527289166469284</v>
       </c>
       <c r="O20" t="n">
-        <v>4119986.885892807</v>
+        <v>4738295.664215015</v>
       </c>
       <c r="P20" t="n">
-        <v>2059993.442946403</v>
+        <v>2369147.832107508</v>
       </c>
     </row>
     <row r="21">
@@ -6149,19 +6149,19 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="H21" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I21" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="J21" t="n">
         <v>-31000000</v>
       </c>
       <c r="K21" t="n">
-        <v>83046504.75082195</v>
+        <v>238695840.5908219</v>
       </c>
       <c r="L21" t="n">
         <v>0.03901400018340251</v>
@@ -6173,10 +6173,10 @@
         <v>-0.02532890719506886</v>
       </c>
       <c r="O21" t="n">
-        <v>-1051738.605854207</v>
+        <v>-3022952.39708694</v>
       </c>
       <c r="P21" t="n">
-        <v>-1051738.605854207</v>
+        <v>-3022952.39708694</v>
       </c>
     </row>
     <row r="22">
@@ -6207,19 +6207,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="H22" t="n">
         <v>2250000</v>
       </c>
       <c r="I22" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="J22" t="n">
         <v>-31000000</v>
       </c>
       <c r="K22" t="n">
-        <v>-18027242.50999999</v>
+        <v>91029553.03</v>
       </c>
       <c r="L22" t="n">
         <v>0.03908855826627113</v>
@@ -6231,10 +6231,10 @@
         <v>-0.02538363335203554</v>
       </c>
       <c r="O22" t="n">
-        <v>190665.3809258619</v>
+        <v>-962775.3326304983</v>
       </c>
       <c r="P22" t="n">
-        <v>95332.69046293097</v>
+        <v>-962775.3326304983</v>
       </c>
     </row>
     <row r="23">
@@ -6265,19 +6265,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="H23" t="n">
         <v>2250000</v>
       </c>
       <c r="I23" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="J23" t="n">
         <v>-31000000</v>
       </c>
       <c r="K23" t="n">
-        <v>12996230.59999999</v>
+        <v>15149273.93</v>
       </c>
       <c r="L23" t="n">
         <v>0.03915884386251234</v>
@@ -6289,10 +6289,10 @@
         <v>-0.02543993459508764</v>
       </c>
       <c r="O23" t="n">
-        <v>-110207.7521488922</v>
+        <v>-128465.5126474221</v>
       </c>
       <c r="P23" t="n">
-        <v>-110207.7521488922</v>
+        <v>-128465.5126474221</v>
       </c>
     </row>
     <row r="24">
@@ -6323,19 +6323,19 @@
         <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="H24" t="n">
         <v>2250000</v>
       </c>
       <c r="I24" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="J24" t="n">
         <v>-31000000</v>
       </c>
       <c r="K24" t="n">
-        <v>11981487.23</v>
+        <v>11309584</v>
       </c>
       <c r="L24" t="n">
         <v>0.03922681220647117</v>
@@ -6347,10 +6347,10 @@
         <v>-0.02549552338669633</v>
       </c>
       <c r="O24" t="n">
-        <v>-76368.57196996707</v>
+        <v>-72085.94084145165</v>
       </c>
       <c r="P24" t="n">
-        <v>-76368.57196996707</v>
+        <v>-72085.94084145165</v>
       </c>
     </row>
     <row r="25">
@@ -6381,19 +6381,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="H25" t="n">
         <v>2250000</v>
       </c>
       <c r="I25" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="J25" t="n">
         <v>-31000000</v>
       </c>
       <c r="K25" t="n">
-        <v>14159921.49</v>
+        <v>12733816.3</v>
       </c>
       <c r="L25" t="n">
         <v>0.03929424848359133</v>
@@ -6405,10 +6405,10 @@
         <v>-0.02555147156878314</v>
       </c>
       <c r="O25" t="n">
-        <v>-60301.13856132274</v>
+        <v>-54227.95752525954</v>
       </c>
       <c r="P25" t="n">
-        <v>-60301.13856132274</v>
+        <v>-54227.95752525954</v>
       </c>
     </row>
     <row r="26">
@@ -6439,19 +6439,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G26" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="H26" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I26" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="L26" t="n">
         <v>0.03936107056455495</v>
@@ -6463,10 +6463,10 @@
         <v>-0.02560744979333988</v>
       </c>
       <c r="O26" t="n">
-        <v>-80987.4201389782</v>
+        <v>-264876.8690425178</v>
       </c>
       <c r="P26" t="n">
-        <v>-80987.4201389782</v>
+        <v>-264876.8690425178</v>
       </c>
     </row>
     <row r="27">
@@ -6497,19 +6497,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="H27" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I27" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="J27" t="n">
         <v>-62000000</v>
       </c>
       <c r="K27" t="n">
-        <v>-13511470.05684932</v>
+        <v>-13151667.90684932</v>
       </c>
       <c r="L27" t="n">
         <v>0.03942868733737526</v>
@@ -6555,19 +6555,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G28" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="J28" t="n">
         <v>-620000000</v>
       </c>
       <c r="K28" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="L28" t="n">
         <v>0.03432749872940843</v>
@@ -6579,10 +6579,10 @@
         <v>-0.02264935222023312</v>
       </c>
       <c r="O28" t="n">
-        <v>15553292.57838485</v>
+        <v>15101057.508424</v>
       </c>
       <c r="P28" t="n">
-        <v>7776646.289192423</v>
+        <v>7550528.754212001</v>
       </c>
     </row>
     <row r="29">
@@ -6613,19 +6613,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="H29" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I29" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="J29" t="n">
         <v>-62000000</v>
       </c>
       <c r="K29" t="n">
-        <v>831750589.7910959</v>
+        <v>1027519240.111096</v>
       </c>
       <c r="L29" t="n">
         <v>0.03782665436246635</v>
@@ -6637,10 +6637,10 @@
         <v>-0.01985875398907044</v>
       </c>
       <c r="O29" t="n">
-        <v>-15141069.48101515</v>
+        <v>-18704814.15770261</v>
       </c>
       <c r="P29" t="n">
-        <v>-15141069.48101515</v>
+        <v>-18704814.15770261</v>
       </c>
     </row>
     <row r="30">
@@ -6671,19 +6671,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="H30" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I30" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="L30" t="n">
         <v>0.03830470017405307</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01722276407024426</v>
       </c>
       <c r="O30" t="n">
-        <v>-11065882.21964725</v>
+        <v>-11439201.73314953</v>
       </c>
       <c r="P30" t="n">
-        <v>-11065882.21964725</v>
+        <v>-11439201.73314953</v>
       </c>
     </row>
     <row r="31">
@@ -6729,19 +6729,19 @@
         <v>0.75</v>
       </c>
       <c r="G31" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="H31" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I31" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="J31" t="n">
         <v>-124000000</v>
       </c>
       <c r="K31" t="n">
-        <v>1242174816.538767</v>
+        <v>932998575.3387671</v>
       </c>
       <c r="L31" t="n">
         <v>0.03852218097221538</v>
@@ -6753,10 +6753,10 @@
         <v>-0.01482995615663363</v>
       </c>
       <c r="O31" t="n">
-        <v>-13816048.55110825</v>
+        <v>-10377245.97485666</v>
       </c>
       <c r="P31" t="n">
-        <v>-13816048.55110825</v>
+        <v>-10377245.97485666</v>
       </c>
     </row>
     <row r="32">
@@ -6787,19 +6787,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="H32" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I32" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="J32" t="n">
         <v>-62000000</v>
       </c>
       <c r="K32" t="n">
-        <v>-272571360.4816439</v>
+        <v>-471277559.5716438</v>
       </c>
       <c r="L32" t="n">
         <v>0.03873510939427094</v>
@@ -6811,10 +6811,10 @@
         <v>-0.01260515871784285</v>
       </c>
       <c r="O32" t="n">
-        <v>2290536.840539652</v>
+        <v>3960352.292372139</v>
       </c>
       <c r="P32" t="n">
-        <v>1145268.420269826</v>
+        <v>1980176.14618607</v>
       </c>
     </row>
     <row r="33">
@@ -6845,19 +6845,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="H33" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I33" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="J33" t="n">
         <v>-62000000</v>
       </c>
       <c r="K33" t="n">
-        <v>-279462863.0247945</v>
+        <v>-321403370.6547946</v>
       </c>
       <c r="L33" t="n">
         <v>0.03888939094511485</v>
@@ -6869,10 +6869,10 @@
         <v>-0.01053392699102673</v>
       </c>
       <c r="O33" t="n">
-        <v>1717240.814220452</v>
+        <v>1974956.457336046</v>
       </c>
       <c r="P33" t="n">
-        <v>858620.4071102258</v>
+        <v>987478.2286680231</v>
       </c>
     </row>
     <row r="34">
@@ -6903,19 +6903,19 @@
         <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="H34" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I34" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="J34" t="n">
         <v>-31000000</v>
       </c>
       <c r="K34" t="n">
-        <v>83046504.75082195</v>
+        <v>238695840.5908219</v>
       </c>
       <c r="L34" t="n">
         <v>0.03901400018340251</v>
@@ -6927,10 +6927,10 @@
         <v>-0.008630921630449429</v>
       </c>
       <c r="O34" t="n">
-        <v>-358383.9370935452</v>
+        <v>-1030082.546826817</v>
       </c>
       <c r="P34" t="n">
-        <v>-358383.9370935452</v>
+        <v>-1030082.546826817</v>
       </c>
     </row>
     <row r="35">
@@ -6961,19 +6961,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="H35" t="n">
         <v>2250000</v>
       </c>
       <c r="I35" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="J35" t="n">
         <v>-31000000</v>
       </c>
       <c r="K35" t="n">
-        <v>-18027242.50999999</v>
+        <v>91029553.03</v>
       </c>
       <c r="L35" t="n">
         <v>0.03908855826627113</v>
@@ -6985,10 +6985,10 @@
         <v>-0.006850555280960409</v>
       </c>
       <c r="O35" t="n">
-        <v>51456.925574181</v>
+        <v>-259834.5771804717</v>
       </c>
       <c r="P35" t="n">
-        <v>25728.4627870905</v>
+        <v>-259834.5771804717</v>
       </c>
     </row>
     <row r="36">
@@ -7019,19 +7019,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G36" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="H36" t="n">
         <v>2250000</v>
       </c>
       <c r="I36" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="J36" t="n">
         <v>-31000000</v>
       </c>
       <c r="K36" t="n">
-        <v>12996230.59999999</v>
+        <v>15149273.93</v>
       </c>
       <c r="L36" t="n">
         <v>0.03915884386251234</v>
@@ -7043,10 +7043,10 @@
         <v>-0.005233721067838482</v>
       </c>
       <c r="O36" t="n">
-        <v>-22672.88196456904</v>
+        <v>-26429.02470996576</v>
       </c>
       <c r="P36" t="n">
-        <v>-22672.88196456904</v>
+        <v>-26429.02470996576</v>
       </c>
     </row>
     <row r="37">
@@ -7077,19 +7077,19 @@
         <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="H37" t="n">
         <v>2250000</v>
       </c>
       <c r="I37" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="J37" t="n">
         <v>-31000000</v>
       </c>
       <c r="K37" t="n">
-        <v>11981487.23</v>
+        <v>11309584</v>
       </c>
       <c r="L37" t="n">
         <v>0.03922681220647117</v>
@@ -7101,10 +7101,10 @@
         <v>-0.003721650822949542</v>
       </c>
       <c r="O37" t="n">
-        <v>-11147.72795242223</v>
+        <v>-10522.58065020424</v>
       </c>
       <c r="P37" t="n">
-        <v>-11147.72795242223</v>
+        <v>-10522.58065020424</v>
       </c>
     </row>
     <row r="38">
@@ -7135,19 +7135,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="H38" t="n">
         <v>2250000</v>
       </c>
       <c r="I38" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="J38" t="n">
         <v>-31000000</v>
       </c>
       <c r="K38" t="n">
-        <v>14159921.49</v>
+        <v>12733816.3</v>
       </c>
       <c r="L38" t="n">
         <v>0.03929424848359133</v>
@@ -7159,10 +7159,10 @@
         <v>-0.002324803196355599</v>
       </c>
       <c r="O38" t="n">
-        <v>-5486.505123349388</v>
+        <v>-4933.936139340835</v>
       </c>
       <c r="P38" t="n">
-        <v>-5486.505123349388</v>
+        <v>-4933.936139340835</v>
       </c>
     </row>
     <row r="39">
@@ -7193,19 +7193,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G39" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="H39" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I39" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="L39" t="n">
         <v>0.03936107056455495</v>
@@ -7217,10 +7217,10 @@
         <v>-0.001029519969532107</v>
       </c>
       <c r="O39" t="n">
-        <v>-3256.01209752836</v>
+        <v>-10649.08955585796</v>
       </c>
       <c r="P39" t="n">
-        <v>-3256.01209752836</v>
+        <v>-10649.08955585796</v>
       </c>
     </row>
     <row r="40">
@@ -7251,19 +7251,19 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="H40" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I40" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="J40" t="n">
         <v>-62000000</v>
       </c>
       <c r="K40" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="L40" t="n">
         <v>0.03942868733737526</v>
@@ -7309,19 +7309,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G41" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="J41" t="n">
         <v>-620000000</v>
       </c>
       <c r="K41" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="L41" t="n">
         <v>0.03432749872940843</v>
@@ -7333,10 +7333,10 @@
         <v>0.02789279458488503</v>
       </c>
       <c r="O41" t="n">
-        <v>-36400113.47886805</v>
+        <v>-35843183.64759321</v>
       </c>
       <c r="P41" t="n">
-        <v>-36400113.47886805</v>
+        <v>-35843183.64759321</v>
       </c>
     </row>
     <row r="42">
@@ -7367,19 +7367,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G42" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="H42" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I42" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="J42" t="n">
         <v>-62000000</v>
       </c>
       <c r="K42" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="L42" t="n">
         <v>0.03782665436246635</v>
@@ -7391,10 +7391,10 @@
         <v>0.02492545821291703</v>
       </c>
       <c r="O42" t="n">
-        <v>17587520.64685568</v>
+        <v>22060508.68372681</v>
       </c>
       <c r="P42" t="n">
-        <v>8793760.323427841</v>
+        <v>11030254.3418634</v>
       </c>
     </row>
     <row r="43">
@@ -7425,19 +7425,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="H43" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I43" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="L43" t="n">
         <v>0.03830470017405307</v>
@@ -7449,10 +7449,10 @@
         <v>0.02210627144826827</v>
       </c>
       <c r="O43" t="n">
-        <v>14203608.38506325</v>
+        <v>14682782.48677873</v>
       </c>
       <c r="P43" t="n">
-        <v>7101804.192531625</v>
+        <v>7341391.243389367</v>
       </c>
     </row>
     <row r="44">
@@ -7483,19 +7483,19 @@
         <v>0.75</v>
       </c>
       <c r="G44" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="H44" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I44" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="J44" t="n">
         <v>-124000000</v>
       </c>
       <c r="K44" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="L44" t="n">
         <v>0.03852218097221538</v>
@@ -7507,10 +7507,10 @@
         <v>0.01953451299207831</v>
       </c>
       <c r="O44" t="n">
-        <v>16382250.36081849</v>
+        <v>11852544.88539599</v>
       </c>
       <c r="P44" t="n">
-        <v>8191125.180409247</v>
+        <v>5926272.442697996</v>
       </c>
     </row>
     <row r="45">
@@ -7541,19 +7541,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="H45" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I45" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="J45" t="n">
         <v>-62000000</v>
       </c>
       <c r="K45" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="L45" t="n">
         <v>0.03873510939427094</v>
@@ -7565,10 +7565,10 @@
         <v>0.01713582153361681</v>
       </c>
       <c r="O45" t="n">
-        <v>-3822103.415648551</v>
+        <v>-6092099.392468265</v>
       </c>
       <c r="P45" t="n">
-        <v>-3822103.415648551</v>
+        <v>-6092099.392468265</v>
       </c>
     </row>
     <row r="46">
@@ -7599,19 +7599,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="H46" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I46" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="J46" t="n">
         <v>-62000000</v>
       </c>
       <c r="K46" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="L46" t="n">
         <v>0.03888939094511485</v>
@@ -7623,10 +7623,10 @@
         <v>0.01489823429388384</v>
       </c>
       <c r="O46" t="n">
-        <v>-2967529.679335522</v>
+        <v>-3332019.392963285</v>
       </c>
       <c r="P46" t="n">
-        <v>-2967529.679335522</v>
+        <v>-3332019.392963285</v>
       </c>
     </row>
     <row r="47">
@@ -7657,19 +7657,19 @@
         <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="H47" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I47" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="J47" t="n">
         <v>-31000000</v>
       </c>
       <c r="K47" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="L47" t="n">
         <v>0.03901400018340251</v>
@@ -7681,10 +7681,10 @@
         <v>0.01283846298538327</v>
       </c>
       <c r="O47" t="n">
-        <v>334098.562381001</v>
+        <v>1333247.680821666</v>
       </c>
       <c r="P47" t="n">
-        <v>167049.2811905005</v>
+        <v>666623.8404108328</v>
       </c>
     </row>
     <row r="48">
@@ -7715,19 +7715,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="H48" t="n">
         <v>2250000</v>
       </c>
       <c r="I48" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="J48" t="n">
         <v>-31000000</v>
       </c>
       <c r="K48" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="L48" t="n">
         <v>0.03908855826627113</v>
@@ -7739,10 +7739,10 @@
         <v>0.01091166853486086</v>
       </c>
       <c r="O48" t="n">
-        <v>-222903.7581030664</v>
+        <v>272926.0770663384</v>
       </c>
       <c r="P48" t="n">
-        <v>-222903.7581030664</v>
+        <v>136463.0385331692</v>
       </c>
     </row>
     <row r="49">
@@ -7773,19 +7773,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G49" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="H49" t="n">
         <v>2250000</v>
       </c>
       <c r="I49" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="J49" t="n">
         <v>-31000000</v>
       </c>
       <c r="K49" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="L49" t="n">
         <v>0.03915884386251234</v>
@@ -7797,10 +7797,10 @@
         <v>0.009159039096315102</v>
       </c>
       <c r="O49" t="n">
-        <v>-54965.74260521386</v>
+        <v>-48392.47326003701</v>
       </c>
       <c r="P49" t="n">
-        <v>-54965.74260521386</v>
+        <v>-48392.47326003701</v>
       </c>
     </row>
     <row r="50">
@@ -7831,19 +7831,19 @@
         <v>0.25</v>
       </c>
       <c r="G50" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="H50" t="n">
         <v>2250000</v>
       </c>
       <c r="I50" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="J50" t="n">
         <v>-31000000</v>
       </c>
       <c r="K50" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="L50" t="n">
         <v>0.03922681220647117</v>
@@ -7855,10 +7855,10 @@
         <v>0.007522420693245678</v>
       </c>
       <c r="O50" t="n">
-        <v>-35766.3135039513</v>
+        <v>-37029.89819425395</v>
       </c>
       <c r="P50" t="n">
-        <v>-35766.3135039513</v>
+        <v>-37029.89819425395</v>
       </c>
     </row>
     <row r="51">
@@ -7889,19 +7889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="H51" t="n">
         <v>2250000</v>
       </c>
       <c r="I51" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="J51" t="n">
         <v>-31000000</v>
       </c>
       <c r="K51" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="L51" t="n">
         <v>0.03929424848359133</v>
@@ -7913,10 +7913,10 @@
         <v>0.006011768704670392</v>
       </c>
       <c r="O51" t="n">
-        <v>-16873.10949510173</v>
+        <v>-18302.01192023674</v>
       </c>
       <c r="P51" t="n">
-        <v>-16873.10949510173</v>
+        <v>-18302.01192023674</v>
       </c>
     </row>
     <row r="52">
@@ -7947,19 +7947,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G52" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="H52" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I52" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="L52" t="n">
         <v>0.03936107056455495</v>
@@ -7971,10 +7971,10 @@
         <v>0.004613431737291229</v>
       </c>
       <c r="O52" t="n">
-        <v>14590.67331600027</v>
+        <v>47720.15034597104</v>
       </c>
       <c r="P52" t="n">
-        <v>7295.336658000136</v>
+        <v>23860.07517298552</v>
       </c>
     </row>
     <row r="53">
@@ -8005,19 +8005,19 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="H53" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I53" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="J53" t="n">
         <v>-62000000</v>
       </c>
       <c r="K53" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="L53" t="n">
         <v>0.03942868733737526</v>
@@ -8063,19 +8063,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G54" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="J54" t="n">
         <v>-620000000</v>
       </c>
       <c r="K54" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="L54" t="n">
         <v>0.03432749872940843</v>
@@ -8087,10 +8087,10 @@
         <v>0.0349083460781352</v>
       </c>
       <c r="O54" t="n">
-        <v>-45555412.33908088</v>
+        <v>-44858404.39919109</v>
       </c>
       <c r="P54" t="n">
-        <v>-45555412.33908088</v>
+        <v>-44858404.39919109</v>
       </c>
     </row>
     <row r="55">
@@ -8121,19 +8121,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G55" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="H55" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I55" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="J55" t="n">
         <v>-62000000</v>
       </c>
       <c r="K55" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="L55" t="n">
         <v>0.03782665436246635</v>
@@ -8145,10 +8145,10 @@
         <v>0.03231037168362505</v>
       </c>
       <c r="O55" t="n">
-        <v>22798350.35485325</v>
+        <v>28596595.05604066</v>
       </c>
       <c r="P55" t="n">
-        <v>11399175.17742662</v>
+        <v>14298297.52802033</v>
       </c>
     </row>
     <row r="56">
@@ -8179,19 +8179,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="H56" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I56" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="L56" t="n">
         <v>0.03830470017405307</v>
@@ -8203,10 +8203,10 @@
         <v>0.02984617139370105</v>
       </c>
       <c r="O56" t="n">
-        <v>19176609.28310079</v>
+        <v>19823552.95248848</v>
       </c>
       <c r="P56" t="n">
-        <v>9588304.641550394</v>
+        <v>9911776.476244241</v>
       </c>
     </row>
     <row r="57">
@@ -8237,19 +8237,19 @@
         <v>0.75</v>
       </c>
       <c r="G57" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="H57" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I57" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="J57" t="n">
         <v>-124000000</v>
       </c>
       <c r="K57" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="L57" t="n">
         <v>0.03852218097221538</v>
@@ -8261,10 +8261,10 @@
         <v>0.02759968737635887</v>
       </c>
       <c r="O57" t="n">
-        <v>23145956.52644055</v>
+        <v>16746080.82545226</v>
       </c>
       <c r="P57" t="n">
-        <v>11572978.26322027</v>
+        <v>8373040.41272613</v>
       </c>
     </row>
     <row r="58">
@@ -8295,19 +8295,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="H58" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I58" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="J58" t="n">
         <v>-62000000</v>
       </c>
       <c r="K58" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="L58" t="n">
         <v>0.03873510939427094</v>
@@ -8319,10 +8319,10 @@
         <v>0.02550527570343863</v>
       </c>
       <c r="O58" t="n">
-        <v>-5688889.861039254</v>
+        <v>-9067594.122221133</v>
       </c>
       <c r="P58" t="n">
-        <v>-5688889.861039254</v>
+        <v>-9067594.122221133</v>
       </c>
     </row>
     <row r="59">
@@ -8353,19 +8353,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G59" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="H59" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I59" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="J59" t="n">
         <v>-62000000</v>
       </c>
       <c r="K59" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="L59" t="n">
         <v>0.03888939094511485</v>
@@ -8377,10 +8377,10 @@
         <v>0.02355207664351209</v>
       </c>
       <c r="O59" t="n">
-        <v>-4691259.720509267</v>
+        <v>-5267468.249774846</v>
       </c>
       <c r="P59" t="n">
-        <v>-4691259.720509267</v>
+        <v>-5267468.249774846</v>
       </c>
     </row>
     <row r="60">
@@ -8411,19 +8411,19 @@
         <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="H60" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I60" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="J60" t="n">
         <v>-31000000</v>
       </c>
       <c r="K60" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="L60" t="n">
         <v>0.03901400018340251</v>
@@ -8435,10 +8435,10 @@
         <v>0.02175522406292973</v>
       </c>
       <c r="O60" t="n">
-        <v>566141.6862732342</v>
+        <v>2259234.774495934</v>
       </c>
       <c r="P60" t="n">
-        <v>283070.8431366171</v>
+        <v>1129617.387247967</v>
       </c>
     </row>
     <row r="61">
@@ -8469,19 +8469,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="H61" t="n">
         <v>2250000</v>
       </c>
       <c r="I61" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="J61" t="n">
         <v>-31000000</v>
       </c>
       <c r="K61" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="L61" t="n">
         <v>0.03908855826627113</v>
@@ -8493,10 +8493,10 @@
         <v>0.02007474611606698</v>
       </c>
       <c r="O61" t="n">
-        <v>-410087.2692329567</v>
+        <v>502115.8485575956</v>
       </c>
       <c r="P61" t="n">
-        <v>-410087.2692329567</v>
+        <v>251057.9242787978</v>
       </c>
     </row>
     <row r="62">
@@ -8527,19 +8527,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="H62" t="n">
         <v>2250000</v>
       </c>
       <c r="I62" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="J62" t="n">
         <v>-31000000</v>
       </c>
       <c r="K62" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="L62" t="n">
         <v>0.03915884386251234</v>
@@ -8551,10 +8551,10 @@
         <v>0.01854770837490727</v>
       </c>
       <c r="O62" t="n">
-        <v>-111309.5548267598</v>
+        <v>-97998.21489229999</v>
       </c>
       <c r="P62" t="n">
-        <v>-111309.5548267598</v>
+        <v>-97998.21489229999</v>
       </c>
     </row>
     <row r="63">
@@ -8585,19 +8585,19 @@
         <v>0.25</v>
       </c>
       <c r="G63" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="H63" t="n">
         <v>2250000</v>
       </c>
       <c r="I63" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="J63" t="n">
         <v>-31000000</v>
       </c>
       <c r="K63" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="L63" t="n">
         <v>0.03922681220647117</v>
@@ -8609,10 +8609,10 @@
         <v>0.01712251280817986</v>
       </c>
       <c r="O63" t="n">
-        <v>-81411.18212421431</v>
+        <v>-84287.3500395974</v>
       </c>
       <c r="P63" t="n">
-        <v>-81411.18212421431</v>
+        <v>-84287.3500395974</v>
       </c>
     </row>
     <row r="64">
@@ -8643,19 +8643,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="H64" t="n">
         <v>2250000</v>
       </c>
       <c r="I64" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="J64" t="n">
         <v>-31000000</v>
       </c>
       <c r="K64" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="L64" t="n">
         <v>0.03929424848359133</v>
@@ -8667,10 +8667,10 @@
         <v>0.01580817291864865</v>
       </c>
       <c r="O64" t="n">
-        <v>-44368.47884161649</v>
+        <v>-48125.83174890021</v>
       </c>
       <c r="P64" t="n">
-        <v>-44368.47884161649</v>
+        <v>-48125.83174890021</v>
       </c>
     </row>
     <row r="65">
@@ -8701,19 +8701,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G65" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="H65" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I65" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="L65" t="n">
         <v>0.03936107056455495</v>
@@ -8725,10 +8725,10 @@
         <v>0.01459272426401294</v>
       </c>
       <c r="O65" t="n">
-        <v>46151.69024950127</v>
+        <v>150943.3834702989</v>
       </c>
       <c r="P65" t="n">
-        <v>23075.84512475063</v>
+        <v>75471.69173514945</v>
       </c>
     </row>
     <row r="66">
@@ -8759,19 +8759,19 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="H66" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I66" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="J66" t="n">
         <v>-62000000</v>
       </c>
       <c r="K66" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="L66" t="n">
         <v>0.03942868733737526</v>
@@ -8817,19 +8817,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G67" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="J67" t="n">
         <v>-620000000</v>
       </c>
       <c r="K67" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="L67" t="n">
         <v>0.03432749872940843</v>
@@ -8841,10 +8841,10 @@
         <v>-0.03432359322008915</v>
       </c>
       <c r="O67" t="n">
-        <v>23569984.80586207</v>
+        <v>22884652.50892653</v>
       </c>
       <c r="P67" t="n">
-        <v>11784992.40293104</v>
+        <v>11442326.25446326</v>
       </c>
     </row>
     <row r="68">
@@ -8875,19 +8875,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G68" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="H68" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I68" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="J68" t="n">
         <v>-62000000</v>
       </c>
       <c r="K68" t="n">
-        <v>831750589.7910959</v>
+        <v>1027519240.111096</v>
       </c>
       <c r="L68" t="n">
         <v>0.03782665436246635</v>
@@ -8899,10 +8899,10 @@
         <v>-0.03222210497938605</v>
       </c>
       <c r="O68" t="n">
-        <v>-24567358.5858387</v>
+        <v>-30349763.42126547</v>
       </c>
       <c r="P68" t="n">
-        <v>-24567358.5858387</v>
+        <v>-30349763.42126547</v>
       </c>
     </row>
     <row r="69">
@@ -8933,19 +8933,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="H69" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I69" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="L69" t="n">
         <v>0.03830470017405307</v>
@@ -8957,10 +8957,10 @@
         <v>-0.02969704733354739</v>
       </c>
       <c r="O69" t="n">
-        <v>-19080794.85522814</v>
+        <v>-19724506.12118971</v>
       </c>
       <c r="P69" t="n">
-        <v>-19080794.85522814</v>
+        <v>-19724506.12118971</v>
       </c>
     </row>
     <row r="70">
@@ -8991,19 +8991,19 @@
         <v>0.75</v>
       </c>
       <c r="G70" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="H70" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I70" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="J70" t="n">
         <v>-124000000</v>
       </c>
       <c r="K70" t="n">
-        <v>1242174816.538767</v>
+        <v>932998575.3387671</v>
       </c>
       <c r="L70" t="n">
         <v>0.03852218097221538</v>
@@ -9015,10 +9015,10 @@
         <v>-0.0274114503343057</v>
       </c>
       <c r="O70" t="n">
-        <v>-25537359.96755828</v>
+        <v>-19181133.08240744</v>
       </c>
       <c r="P70" t="n">
-        <v>-25537359.96755828</v>
+        <v>-19181133.08240744</v>
       </c>
     </row>
     <row r="71">
@@ -9049,19 +9049,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="H71" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I71" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="J71" t="n">
         <v>-62000000</v>
       </c>
       <c r="K71" t="n">
-        <v>-272571360.4816439</v>
+        <v>-471277559.5716438</v>
       </c>
       <c r="L71" t="n">
         <v>0.03873510939427094</v>
@@ -9073,10 +9073,10 @@
         <v>-0.0252927177134521</v>
       </c>
       <c r="O71" t="n">
-        <v>4596046.984955874</v>
+        <v>7946593.519286795</v>
       </c>
       <c r="P71" t="n">
-        <v>2298023.492477937</v>
+        <v>3973296.759643397</v>
       </c>
     </row>
     <row r="72">
@@ -9107,19 +9107,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G72" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="H72" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I72" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="J72" t="n">
         <v>-62000000</v>
       </c>
       <c r="K72" t="n">
-        <v>-279462863.0247945</v>
+        <v>-321403370.6547946</v>
       </c>
       <c r="L72" t="n">
         <v>0.03888939094511485</v>
@@ -9131,10 +9131,10 @@
         <v>-0.02332613375362271</v>
       </c>
       <c r="O72" t="n">
-        <v>3802626.404550575</v>
+        <v>4373307.174109367</v>
       </c>
       <c r="P72" t="n">
-        <v>1901313.202275287</v>
+        <v>2186653.587054683</v>
       </c>
     </row>
     <row r="73">
@@ -9165,19 +9165,19 @@
         <v>0.5</v>
       </c>
       <c r="G73" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="H73" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I73" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="J73" t="n">
         <v>-31000000</v>
       </c>
       <c r="K73" t="n">
-        <v>83046504.75082195</v>
+        <v>238695840.5908219</v>
       </c>
       <c r="L73" t="n">
         <v>0.03901400018340251</v>
@@ -9189,10 +9189,10 @@
         <v>-0.02152530442995682</v>
       </c>
       <c r="O73" t="n">
-        <v>-893800.6483026487</v>
+        <v>-2569000.317440942</v>
       </c>
       <c r="P73" t="n">
-        <v>-893800.6483026487</v>
+        <v>-2569000.317440942</v>
       </c>
     </row>
     <row r="74">
@@ -9223,19 +9223,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G74" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="H74" t="n">
         <v>2250000</v>
       </c>
       <c r="I74" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="J74" t="n">
         <v>-31000000</v>
       </c>
       <c r="K74" t="n">
-        <v>-18027242.50999999</v>
+        <v>91029553.03</v>
       </c>
       <c r="L74" t="n">
         <v>0.03908855826627113</v>
@@ -9247,10 +9247,10 @@
         <v>-0.01984578814143261</v>
       </c>
       <c r="O74" t="n">
-        <v>149068.6815115365</v>
+        <v>-752730.5100177852</v>
       </c>
       <c r="P74" t="n">
-        <v>74534.34075576825</v>
+        <v>-752730.5100177852</v>
       </c>
     </row>
     <row r="75">
@@ -9281,19 +9281,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G75" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="H75" t="n">
         <v>2250000</v>
       </c>
       <c r="I75" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="J75" t="n">
         <v>-31000000</v>
       </c>
       <c r="K75" t="n">
-        <v>12996230.59999999</v>
+        <v>15149273.93</v>
       </c>
       <c r="L75" t="n">
         <v>0.03915884386251234</v>
@@ -9305,10 +9305,10 @@
         <v>-0.01832662273584051</v>
       </c>
       <c r="O75" t="n">
-        <v>-79392.33839806204</v>
+        <v>-92545.00934567132</v>
       </c>
       <c r="P75" t="n">
-        <v>-79392.33839806204</v>
+        <v>-92545.00934567132</v>
       </c>
     </row>
     <row r="76">
@@ -9339,19 +9339,19 @@
         <v>0.25</v>
       </c>
       <c r="G76" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="H76" t="n">
         <v>2250000</v>
       </c>
       <c r="I76" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="J76" t="n">
         <v>-31000000</v>
       </c>
       <c r="K76" t="n">
-        <v>11981487.23</v>
+        <v>11309584</v>
       </c>
       <c r="L76" t="n">
         <v>0.03922681220647117</v>
@@ -9363,10 +9363,10 @@
         <v>-0.01691110693903308</v>
       </c>
       <c r="O76" t="n">
-        <v>-50655.0529587973</v>
+        <v>-47814.39611499438</v>
       </c>
       <c r="P76" t="n">
-        <v>-50655.0529587973</v>
+        <v>-47814.39611499438</v>
       </c>
     </row>
     <row r="77">
@@ -9397,19 +9397,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="H77" t="n">
         <v>2250000</v>
       </c>
       <c r="I77" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="J77" t="n">
         <v>-31000000</v>
       </c>
       <c r="K77" t="n">
-        <v>14159921.49</v>
+        <v>12733816.3</v>
       </c>
       <c r="L77" t="n">
         <v>0.03929424848359133</v>
@@ -9421,10 +9421,10 @@
         <v>-0.01560891224971384</v>
       </c>
       <c r="O77" t="n">
-        <v>-36836.82866670786</v>
+        <v>-33126.83687177927</v>
       </c>
       <c r="P77" t="n">
-        <v>-36836.82866670786</v>
+        <v>-33126.83687177927</v>
       </c>
     </row>
     <row r="78">
@@ -9455,19 +9455,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G78" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="H78" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I78" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="L78" t="n">
         <v>0.03936107056455495</v>
@@ -9479,10 +9479,10 @@
         <v>-0.01440665719067059</v>
       </c>
       <c r="O78" t="n">
-        <v>-45563.22508157478</v>
+        <v>-149018.7535592156</v>
       </c>
       <c r="P78" t="n">
-        <v>-45563.22508157478</v>
+        <v>-149018.7535592156</v>
       </c>
     </row>
     <row r="79">
@@ -9513,19 +9513,19 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="H79" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I79" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="J79" t="n">
         <v>-62000000</v>
       </c>
       <c r="K79" t="n">
-        <v>-13511470.05684932</v>
+        <v>-13151667.90684932</v>
       </c>
       <c r="L79" t="n">
         <v>0.03942868733737526</v>
@@ -9571,19 +9571,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="G80" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>-1308585759.65</v>
+        <v>-1288564106.51</v>
       </c>
       <c r="J80" t="n">
         <v>-620000000</v>
       </c>
       <c r="K80" t="n">
-        <v>-688585759.6500001</v>
+        <v>-668564106.51</v>
       </c>
       <c r="L80" t="n">
         <v>0.03432749872940843</v>
@@ -9595,10 +9595,10 @@
         <v>-0.01000145066733071</v>
       </c>
       <c r="O80" t="n">
-        <v>6867988.405351218</v>
+        <v>6668291.447209972</v>
       </c>
       <c r="P80" t="n">
-        <v>3433994.202675609</v>
+        <v>3334145.723604986</v>
       </c>
     </row>
     <row r="81">
@@ -9629,19 +9629,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>859293400.75</v>
+        <v>1055062051.07</v>
       </c>
       <c r="H81" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I81" t="n">
-        <v>769750589.7910959</v>
+        <v>965519240.1110955</v>
       </c>
       <c r="J81" t="n">
         <v>-62000000</v>
       </c>
       <c r="K81" t="n">
-        <v>831750589.7910959</v>
+        <v>1027519240.111096</v>
       </c>
       <c r="L81" t="n">
         <v>0.03782665436246635</v>
@@ -9653,10 +9653,10 @@
         <v>-0.01002646052209499</v>
       </c>
       <c r="O81" t="n">
-        <v>-7644554.915038845</v>
+        <v>-9443849.338611366</v>
       </c>
       <c r="P81" t="n">
-        <v>-7644554.915038845</v>
+        <v>-9443849.338611366</v>
       </c>
     </row>
     <row r="82">
@@ -9687,19 +9687,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>821952611.5000001</v>
+        <v>847963733.4300001</v>
       </c>
       <c r="H82" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I82" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>771017858.0753425</v>
+        <v>797028980.0053425</v>
       </c>
       <c r="L82" t="n">
         <v>0.03830470017405307</v>
@@ -9711,10 +9711,10 @@
         <v>-0.01005429630576771</v>
       </c>
       <c r="O82" t="n">
-        <v>-6460035.001773206</v>
+        <v>-6677971.274381265</v>
       </c>
       <c r="P82" t="n">
-        <v>-6460035.001773206</v>
+        <v>-6677971.274381265</v>
       </c>
     </row>
     <row r="83">
@@ -9745,19 +9745,19 @@
         <v>0.75</v>
       </c>
       <c r="G83" t="n">
-        <v>1248487704.21</v>
+        <v>939311463.0099999</v>
       </c>
       <c r="H83" t="n">
         <v>-130312887.6712329</v>
       </c>
       <c r="I83" t="n">
-        <v>1118174816.538767</v>
+        <v>808998575.3387671</v>
       </c>
       <c r="J83" t="n">
         <v>-124000000</v>
       </c>
       <c r="K83" t="n">
-        <v>1242174816.538767</v>
+        <v>932998575.3387671</v>
       </c>
       <c r="L83" t="n">
         <v>0.03852218097221538</v>
@@ -9769,10 +9769,10 @@
         <v>-0.01008322673507944</v>
       </c>
       <c r="O83" t="n">
-        <v>-9393847.739824571</v>
+        <v>-7055727.133985166</v>
       </c>
       <c r="P83" t="n">
-        <v>-9393847.739824571</v>
+        <v>-7055727.133985166</v>
       </c>
     </row>
     <row r="84">
@@ -9803,19 +9803,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="G84" t="n">
-        <v>-244620576.92</v>
+        <v>-443326776.01</v>
       </c>
       <c r="H84" t="n">
         <v>-89950783.56164384</v>
       </c>
       <c r="I84" t="n">
-        <v>-334571360.4816439</v>
+        <v>-533277559.5716438</v>
       </c>
       <c r="J84" t="n">
         <v>-62000000</v>
       </c>
       <c r="K84" t="n">
-        <v>-272571360.4816439</v>
+        <v>-471277559.5716438</v>
       </c>
       <c r="L84" t="n">
         <v>0.03873510939427094</v>
@@ -9827,10 +9827,10 @@
         <v>-0.0101121147124088</v>
       </c>
       <c r="O84" t="n">
-        <v>1837515.243005143</v>
+        <v>3177075.162515025</v>
       </c>
       <c r="P84" t="n">
-        <v>918757.6215025715</v>
+        <v>1588537.581257512</v>
       </c>
     </row>
     <row r="85">
@@ -9861,19 +9861,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="G85" t="n">
-        <v>-251489410.97</v>
+        <v>-293429918.6</v>
       </c>
       <c r="H85" t="n">
         <v>-89973452.05479452</v>
       </c>
       <c r="I85" t="n">
-        <v>-341462863.0247945</v>
+        <v>-383403370.6547946</v>
       </c>
       <c r="J85" t="n">
         <v>-62000000</v>
       </c>
       <c r="K85" t="n">
-        <v>-279462863.0247945</v>
+        <v>-321403370.6547946</v>
       </c>
       <c r="L85" t="n">
         <v>0.03888939094511485</v>
@@ -9885,10 +9885,10 @@
         <v>-0.0101405708492285</v>
       </c>
       <c r="O85" t="n">
-        <v>1653115.894634848</v>
+        <v>1901207.963261712</v>
       </c>
       <c r="P85" t="n">
-        <v>826557.9473174242</v>
+        <v>950603.9816308562</v>
       </c>
     </row>
     <row r="86">
@@ -9919,19 +9919,19 @@
         <v>0.5</v>
       </c>
       <c r="G86" t="n">
-        <v>142015112.97</v>
+        <v>297664448.81</v>
       </c>
       <c r="H86" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I86" t="n">
-        <v>52046504.75082195</v>
+        <v>207695840.5908219</v>
       </c>
       <c r="J86" t="n">
         <v>-31000000</v>
       </c>
       <c r="K86" t="n">
-        <v>83046504.75082195</v>
+        <v>238695840.5908219</v>
       </c>
       <c r="L86" t="n">
         <v>0.03901400018340251</v>
@@ -9943,10 +9943,10 @@
         <v>-0.01016949446707605</v>
       </c>
       <c r="O86" t="n">
-        <v>-422270.4852867442</v>
+        <v>-1213708.015101215</v>
       </c>
       <c r="P86" t="n">
-        <v>-422270.4852867442</v>
+        <v>-1213708.015101215</v>
       </c>
     </row>
     <row r="87">
@@ -9977,19 +9977,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>-51277242.50999999</v>
+        <v>57779553.03000001</v>
       </c>
       <c r="H87" t="n">
         <v>2250000</v>
       </c>
       <c r="I87" t="n">
-        <v>-49027242.50999999</v>
+        <v>60029553.03000001</v>
       </c>
       <c r="J87" t="n">
         <v>-31000000</v>
       </c>
       <c r="K87" t="n">
-        <v>-18027242.50999999</v>
+        <v>91029553.03</v>
       </c>
       <c r="L87" t="n">
         <v>0.03908855826627113</v>
@@ -10001,10 +10001,10 @@
         <v>-0.01019737062440143</v>
       </c>
       <c r="O87" t="n">
-        <v>76596.03050434779</v>
+        <v>-386775.870841881</v>
       </c>
       <c r="P87" t="n">
-        <v>38298.01525217389</v>
+        <v>-386775.870841881</v>
       </c>
     </row>
     <row r="88">
@@ -10035,19 +10035,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>-20253769.40000001</v>
+        <v>-18100726.07</v>
       </c>
       <c r="H88" t="n">
         <v>2250000</v>
       </c>
       <c r="I88" t="n">
-        <v>-18003769.40000001</v>
+        <v>-15850726.07</v>
       </c>
       <c r="J88" t="n">
         <v>-31000000</v>
       </c>
       <c r="K88" t="n">
-        <v>12996230.59999999</v>
+        <v>15149273.93</v>
       </c>
       <c r="L88" t="n">
         <v>0.03915884386251234</v>
@@ -10059,10 +10059,10 @@
         <v>-0.0102268186216663</v>
       </c>
       <c r="O88" t="n">
-        <v>-44303.36437051645</v>
+        <v>-51642.95891068261</v>
       </c>
       <c r="P88" t="n">
-        <v>-44303.36437051645</v>
+        <v>-51642.95891068261</v>
       </c>
     </row>
     <row r="89">
@@ -10093,19 +10093,19 @@
         <v>0.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-21268512.77</v>
+        <v>-21940416</v>
       </c>
       <c r="H89" t="n">
         <v>2250000</v>
       </c>
       <c r="I89" t="n">
-        <v>-19018512.77</v>
+        <v>-19690416</v>
       </c>
       <c r="J89" t="n">
         <v>-31000000</v>
       </c>
       <c r="K89" t="n">
-        <v>11981487.23</v>
+        <v>11309584</v>
       </c>
       <c r="L89" t="n">
         <v>0.03922681220647117</v>
@@ -10117,10 +10117,10 @@
         <v>-0.01025547675463123</v>
       </c>
       <c r="O89" t="n">
-        <v>-30718.96594329398</v>
+        <v>-28996.29395413733</v>
       </c>
       <c r="P89" t="n">
-        <v>-30718.96594329398</v>
+        <v>-28996.29395413733</v>
       </c>
     </row>
     <row r="90">
@@ -10151,19 +10151,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="G90" t="n">
-        <v>-19090078.51</v>
+        <v>-20516183.7</v>
       </c>
       <c r="H90" t="n">
         <v>2250000</v>
       </c>
       <c r="I90" t="n">
-        <v>-16840078.51</v>
+        <v>-18266183.7</v>
       </c>
       <c r="J90" t="n">
         <v>-31000000</v>
       </c>
       <c r="K90" t="n">
-        <v>14159921.49</v>
+        <v>12733816.3</v>
       </c>
       <c r="L90" t="n">
         <v>0.03929424848359133</v>
@@ -10175,10 +10175,10 @@
         <v>-0.01028445871969606</v>
       </c>
       <c r="O90" t="n">
-        <v>-24271.18800634034</v>
+        <v>-21826.73468025712</v>
       </c>
       <c r="P90" t="n">
-        <v>-24271.18800634034</v>
+        <v>-21826.73468025712</v>
       </c>
     </row>
     <row r="91">
@@ -10209,19 +10209,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="G91" t="n">
-        <v>35689480.16</v>
+        <v>121862582.31</v>
       </c>
       <c r="H91" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I91" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>37951808.92712329</v>
+        <v>124124911.0771233</v>
       </c>
       <c r="L91" t="n">
         <v>0.03936107056455495</v>
@@ -10233,10 +10233,10 @@
         <v>-0.01031343600303951</v>
       </c>
       <c r="O91" t="n">
-        <v>-32617.79604745581</v>
+        <v>-106679.5272314068</v>
       </c>
       <c r="P91" t="n">
-        <v>-32617.79604745581</v>
+        <v>-106679.5272314068</v>
       </c>
     </row>
     <row r="92">
@@ -10267,19 +10267,19 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>-79556538.55</v>
+        <v>-79196736.40000001</v>
       </c>
       <c r="H92" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I92" t="n">
-        <v>-75511470.05684932</v>
+        <v>-75151667.90684932</v>
       </c>
       <c r="J92" t="n">
         <v>-62000000</v>
       </c>
       <c r="K92" t="n">
-        <v>-13511470.05684932</v>
+        <v>-13151667.90684932</v>
       </c>
       <c r="L92" t="n">
         <v>0.03942868733737526</v>
@@ -10370,22 +10370,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D2" t="n">
-        <v>499832517.6</v>
+        <v>503296385.94</v>
       </c>
       <c r="E2" t="n">
-        <v>35717002.64000005</v>
+        <v>33974881.98000002</v>
       </c>
       <c r="F2" t="n">
-        <v>17858501.32000002</v>
+        <v>16987440.99000001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.97641688666667</v>
+        <v>2.831240165000002</v>
       </c>
       <c r="H2" t="n">
-        <v>1.488208443333335</v>
+        <v>1.415620082500001</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -10403,22 +10403,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D3" t="n">
-        <v>424713058.09</v>
+        <v>431761757.49</v>
       </c>
       <c r="E3" t="n">
-        <v>-39402456.87</v>
+        <v>-37559746.46999997</v>
       </c>
       <c r="F3" t="n">
-        <v>-39402456.87</v>
+        <v>-37559746.46999997</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.2835380725</v>
+        <v>-3.129978872499997</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.2835380725</v>
+        <v>-3.129978872499997</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -10436,22 +10436,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D4" t="n">
-        <v>489070373.65</v>
+        <v>494146007.63</v>
       </c>
       <c r="E4" t="n">
-        <v>24954858.69</v>
+        <v>24824503.67000002</v>
       </c>
       <c r="F4" t="n">
-        <v>12477429.345</v>
+        <v>12412251.83500001</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0795715575</v>
+        <v>2.068708639166668</v>
       </c>
       <c r="H4" t="n">
-        <v>1.03978577875</v>
+        <v>1.034354319583334</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -10469,22 +10469,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D5" t="n">
-        <v>438331502.68</v>
+        <v>443546752.7</v>
       </c>
       <c r="E5" t="n">
-        <v>-25784012.27999997</v>
+        <v>-25774751.25999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-25784012.27999997</v>
+        <v>-25774751.25999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.148667689999998</v>
+        <v>-2.147895938333332</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.148667689999998</v>
+        <v>-2.147895938333332</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -10502,22 +10502,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D6" t="n">
-        <v>455959739.47</v>
+        <v>460461623.41</v>
       </c>
       <c r="E6" t="n">
-        <v>-8155775.48999995</v>
+        <v>-8859880.549999952</v>
       </c>
       <c r="F6" t="n">
-        <v>-8155775.48999995</v>
+        <v>-8859880.549999952</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6796479574999958</v>
+        <v>-0.7383233791666627</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6796479574999958</v>
+        <v>-0.7383233791666627</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -10535,22 +10535,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D7" t="n">
-        <v>468775395.59</v>
+        <v>474806744.03</v>
       </c>
       <c r="E7" t="n">
-        <v>4659880.629999995</v>
+        <v>5485240.069999993</v>
       </c>
       <c r="F7" t="n">
-        <v>2329940.314999998</v>
+        <v>2742620.034999996</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3883233858333329</v>
+        <v>0.4571033391666661</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1941616929166665</v>
+        <v>0.228551669583333</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -10568,22 +10568,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>464115514.96</v>
+        <v>469321503.96</v>
       </c>
       <c r="D8" t="n">
-        <v>447267377.49</v>
+        <v>453243451.72</v>
       </c>
       <c r="E8" t="n">
-        <v>-16848137.46999997</v>
+        <v>-16078052.23999995</v>
       </c>
       <c r="F8" t="n">
-        <v>-16848137.46999997</v>
+        <v>-16078052.23999995</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.404011455833331</v>
+        <v>-1.339837686666663</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.404011455833331</v>
+        <v>-1.339837686666663</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
